--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Desktop\ANO 3\ANO 3 SEM 2\PIC\Financial-Markets-Prediction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:10000001_{187F5E1B-DBB3-4DA8-BD87-D160D7FBC334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3506A505-C5E0-4320-B997-64C9714DC4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -925,19 +925,94 @@
     <xf numFmtId="164" fontId="0" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -974,30 +1049,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1013,70 +1064,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1126,6 +1126,35 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-PT"/>
+              <a:t>ABS</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-PT" baseline="0"/>
+              <a:t> AVG</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1290,19 +1319,19 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.16562650636596546</c:v>
+                  <c:v>0.130167169295241</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.5484478771713241E-3</c:v>
+                  <c:v>5.3669333445252694E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1640354173885189</c:v>
+                  <c:v>0.12912372015400433</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.9070923434570615E-3</c:v>
+                  <c:v>5.5213967295835919E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.16437372396588582</c:v>
+                  <c:v>0.12555312369212876</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1441,19 +1470,19 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.10722202342334754</c:v>
+                  <c:v>0.11815919350437008</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.1791066851724887E-3</c:v>
+                  <c:v>4.0144838116363381E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.10536782143871931</c:v>
+                  <c:v>0.11658479721638716</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.3766136751378823E-3</c:v>
+                  <c:v>4.3725639207581333E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.10165541517862074</c:v>
+                  <c:v>0.10299876208610644</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1518,19 +1547,19 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>5.9682965378486989E-2</c:v>
+                  <c:v>5.4821890430214487E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9053262849441227E-3</c:v>
+                  <c:v>1.7264471176856864E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.8787022517720826E-2</c:v>
+                  <c:v>5.4183547798500049E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.9288789392539083E-3</c:v>
+                  <c:v>1.7571768166273812E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.2353531524908447E-2</c:v>
+                  <c:v>5.9392464248066379E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1710,19 +1739,19 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.6611418247179177</c:v>
+                  <c:v>1.0265439941037653</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.6171126308932747E-2</c:v>
+                  <c:v>2.3603105615269012E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5702437267527654</c:v>
+                  <c:v>0.97926702621680883</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.4423915874920311E-2</c:v>
+                  <c:v>3.6161156765879422E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.94916744185995283</c:v>
+                  <c:v>0.69414892117823801</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1919,6 +1948,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1417241871"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -2562,16 +2592,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>825533</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>179393</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>169314</xdr:rowOff>
+      <xdr:rowOff>94693</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>86623</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>122361</xdr:rowOff>
+      <xdr:colOff>417763</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>66842</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2877,197 +2907,198 @@
     <col min="28" max="28" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="11.453125" customWidth="1"/>
     <col min="39" max="40" width="9.1796875" customWidth="1"/>
+    <col min="49" max="49" width="10.26953125" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="10.54296875" customWidth="1"/>
     <col min="52" max="52" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="95" t="s">
+      <c r="B1" s="127"/>
+      <c r="C1" s="120" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="98" t="s">
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="100"/>
-      <c r="AA1" s="103" t="s">
+      <c r="P1" s="124"/>
+      <c r="Q1" s="124"/>
+      <c r="R1" s="124"/>
+      <c r="S1" s="124"/>
+      <c r="T1" s="124"/>
+      <c r="U1" s="124"/>
+      <c r="V1" s="124"/>
+      <c r="W1" s="124"/>
+      <c r="X1" s="124"/>
+      <c r="Y1" s="124"/>
+      <c r="Z1" s="125"/>
+      <c r="AA1" s="108" t="s">
         <v>44</v>
       </c>
-      <c r="AB1" s="104"/>
-      <c r="AC1" s="104"/>
-      <c r="AD1" s="104"/>
-      <c r="AE1" s="104"/>
-      <c r="AF1" s="104"/>
-      <c r="AG1" s="104"/>
-      <c r="AH1" s="104"/>
-      <c r="AI1" s="104"/>
-      <c r="AJ1" s="104"/>
-      <c r="AK1" s="104"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="122" t="s">
+      <c r="AB1" s="109"/>
+      <c r="AC1" s="109"/>
+      <c r="AD1" s="109"/>
+      <c r="AE1" s="109"/>
+      <c r="AF1" s="109"/>
+      <c r="AG1" s="109"/>
+      <c r="AH1" s="109"/>
+      <c r="AI1" s="109"/>
+      <c r="AJ1" s="109"/>
+      <c r="AK1" s="109"/>
+      <c r="AL1" s="110"/>
+      <c r="AM1" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="AN1" s="123"/>
-      <c r="AO1" s="123"/>
-      <c r="AP1" s="123"/>
-      <c r="AQ1" s="123"/>
-      <c r="AR1" s="123"/>
-      <c r="AS1" s="123"/>
-      <c r="AT1" s="123"/>
-      <c r="AU1" s="123"/>
-      <c r="AV1" s="123"/>
-      <c r="AW1" s="123"/>
-      <c r="AX1" s="124"/>
-      <c r="AY1" s="130" t="s">
+      <c r="AN1" s="96"/>
+      <c r="AO1" s="96"/>
+      <c r="AP1" s="96"/>
+      <c r="AQ1" s="96"/>
+      <c r="AR1" s="96"/>
+      <c r="AS1" s="96"/>
+      <c r="AT1" s="96"/>
+      <c r="AU1" s="96"/>
+      <c r="AV1" s="96"/>
+      <c r="AW1" s="96"/>
+      <c r="AX1" s="97"/>
+      <c r="AY1" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="AZ1" s="131"/>
-      <c r="BA1" s="131"/>
-      <c r="BB1" s="131"/>
-      <c r="BC1" s="131"/>
-      <c r="BD1" s="131"/>
-      <c r="BE1" s="131"/>
-      <c r="BF1" s="131"/>
-      <c r="BG1" s="131"/>
-      <c r="BH1" s="131"/>
-      <c r="BI1" s="131"/>
-      <c r="BJ1" s="132"/>
+      <c r="AZ1" s="88"/>
+      <c r="BA1" s="88"/>
+      <c r="BB1" s="88"/>
+      <c r="BC1" s="88"/>
+      <c r="BD1" s="88"/>
+      <c r="BE1" s="88"/>
+      <c r="BF1" s="88"/>
+      <c r="BG1" s="88"/>
+      <c r="BH1" s="88"/>
+      <c r="BI1" s="88"/>
+      <c r="BJ1" s="89"/>
     </row>
     <row r="2" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="126" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="121" t="s">
+      <c r="B2" s="127"/>
+      <c r="C2" s="133" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="111" t="s">
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="128" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="112"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="111" t="s">
+      <c r="G2" s="129"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="112"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="111" t="s">
+      <c r="J2" s="129"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="128" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="112"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="115" t="s">
+      <c r="M2" s="129"/>
+      <c r="N2" s="131"/>
+      <c r="O2" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="93"/>
-      <c r="R2" s="91" t="s">
+      <c r="P2" s="117"/>
+      <c r="Q2" s="118"/>
+      <c r="R2" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="92"/>
-      <c r="T2" s="93"/>
-      <c r="U2" s="91" t="s">
+      <c r="S2" s="117"/>
+      <c r="T2" s="118"/>
+      <c r="U2" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="V2" s="92"/>
-      <c r="W2" s="93"/>
-      <c r="X2" s="91" t="s">
+      <c r="V2" s="117"/>
+      <c r="W2" s="118"/>
+      <c r="X2" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="Y2" s="92"/>
-      <c r="Z2" s="94"/>
-      <c r="AA2" s="106" t="s">
+      <c r="Y2" s="117"/>
+      <c r="Z2" s="119"/>
+      <c r="AA2" s="111" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="107"/>
-      <c r="AC2" s="108"/>
-      <c r="AD2" s="109" t="s">
+      <c r="AB2" s="112"/>
+      <c r="AC2" s="113"/>
+      <c r="AD2" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="107"/>
-      <c r="AF2" s="108"/>
-      <c r="AG2" s="109" t="s">
+      <c r="AE2" s="112"/>
+      <c r="AF2" s="113"/>
+      <c r="AG2" s="114" t="s">
         <v>38</v>
       </c>
-      <c r="AH2" s="107"/>
-      <c r="AI2" s="108"/>
-      <c r="AJ2" s="109" t="s">
+      <c r="AH2" s="112"/>
+      <c r="AI2" s="113"/>
+      <c r="AJ2" s="114" t="s">
         <v>39</v>
       </c>
-      <c r="AK2" s="107"/>
-      <c r="AL2" s="110"/>
-      <c r="AM2" s="125" t="s">
+      <c r="AK2" s="112"/>
+      <c r="AL2" s="115"/>
+      <c r="AM2" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="AN2" s="126"/>
-      <c r="AO2" s="127"/>
-      <c r="AP2" s="128" t="s">
+      <c r="AN2" s="99"/>
+      <c r="AO2" s="100"/>
+      <c r="AP2" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="AQ2" s="126"/>
-      <c r="AR2" s="127"/>
-      <c r="AS2" s="128" t="s">
+      <c r="AQ2" s="99"/>
+      <c r="AR2" s="100"/>
+      <c r="AS2" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="AT2" s="126"/>
-      <c r="AU2" s="127"/>
-      <c r="AV2" s="128" t="s">
+      <c r="AT2" s="99"/>
+      <c r="AU2" s="100"/>
+      <c r="AV2" s="101" t="s">
         <v>39</v>
       </c>
-      <c r="AW2" s="126"/>
-      <c r="AX2" s="129"/>
-      <c r="AY2" s="133" t="s">
+      <c r="AW2" s="99"/>
+      <c r="AX2" s="102"/>
+      <c r="AY2" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="AZ2" s="134"/>
-      <c r="BA2" s="135"/>
-      <c r="BB2" s="136" t="s">
+      <c r="AZ2" s="91"/>
+      <c r="BA2" s="92"/>
+      <c r="BB2" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="BC2" s="134"/>
-      <c r="BD2" s="135"/>
-      <c r="BE2" s="136" t="s">
+      <c r="BC2" s="91"/>
+      <c r="BD2" s="92"/>
+      <c r="BE2" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="BF2" s="134"/>
-      <c r="BG2" s="135"/>
-      <c r="BH2" s="136" t="s">
+      <c r="BF2" s="91"/>
+      <c r="BG2" s="92"/>
+      <c r="BH2" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="BI2" s="134"/>
-      <c r="BJ2" s="137"/>
+      <c r="BI2" s="91"/>
+      <c r="BJ2" s="94"/>
     </row>
     <row r="3" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="120"/>
+      <c r="B3" s="107"/>
       <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
@@ -3250,7 +3281,7 @@
       </c>
     </row>
     <row r="4" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="103" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -3458,24 +3489,24 @@
       </c>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A5" s="117"/>
+      <c r="A5" s="104"/>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="52">
         <v>9229.9</v>
       </c>
-      <c r="D5" s="86">
+      <c r="D5" s="134">
         <v>13076.75</v>
       </c>
       <c r="E5" s="20">
         <f>(D5-C5)/C5</f>
         <v>0.41678133024193115</v>
       </c>
-      <c r="F5" s="87">
+      <c r="F5" s="135">
         <v>3115.9</v>
       </c>
-      <c r="G5" s="87">
+      <c r="G5" s="135">
         <v>3295.31</v>
       </c>
       <c r="H5" s="24">
@@ -3485,7 +3516,7 @@
       <c r="I5" s="70">
         <v>1779.9</v>
       </c>
-      <c r="J5" s="88">
+      <c r="J5" s="136">
         <v>1587.4</v>
       </c>
       <c r="K5" s="28">
@@ -3495,7 +3526,7 @@
       <c r="L5" s="79">
         <v>1.125</v>
       </c>
-      <c r="M5" s="89">
+      <c r="M5" s="137">
         <v>1.1234999999999999</v>
       </c>
       <c r="N5" s="32">
@@ -3505,17 +3536,17 @@
       <c r="O5" s="52">
         <v>9229.9</v>
       </c>
-      <c r="P5" s="86">
+      <c r="P5" s="134">
         <v>9152.48</v>
       </c>
       <c r="Q5" s="20">
         <f>(P5-O5)/O5</f>
         <v>-8.3879565325734925E-3</v>
       </c>
-      <c r="R5" s="87">
+      <c r="R5" s="135">
         <v>3115.9</v>
       </c>
-      <c r="S5" s="87">
+      <c r="S5" s="135">
         <v>3096</v>
       </c>
       <c r="T5" s="24">
@@ -3525,7 +3556,7 @@
       <c r="U5" s="70">
         <v>1779.9</v>
       </c>
-      <c r="V5" s="88">
+      <c r="V5" s="136">
         <v>1800.77</v>
       </c>
       <c r="W5" s="28">
@@ -3535,7 +3566,7 @@
       <c r="X5" s="79">
         <v>1.125</v>
       </c>
-      <c r="Y5" s="89">
+      <c r="Y5" s="137">
         <v>1.1231</v>
       </c>
       <c r="Z5" s="37">
@@ -3545,17 +3576,17 @@
       <c r="AA5" s="52">
         <v>9229.9</v>
       </c>
-      <c r="AB5" s="86">
+      <c r="AB5" s="134">
         <v>12768.7</v>
       </c>
       <c r="AC5" s="20">
         <f>(AB5-AA5)/AA5</f>
         <v>0.38340610407480052</v>
       </c>
-      <c r="AD5" s="87">
+      <c r="AD5" s="135">
         <v>3115.9</v>
       </c>
-      <c r="AE5" s="87">
+      <c r="AE5" s="135">
         <v>3295</v>
       </c>
       <c r="AF5" s="24">
@@ -3565,7 +3596,7 @@
       <c r="AG5" s="70">
         <v>1779.9</v>
       </c>
-      <c r="AH5" s="88">
+      <c r="AH5" s="136">
         <v>1589.24</v>
       </c>
       <c r="AI5" s="28">
@@ -3575,7 +3606,7 @@
       <c r="AJ5" s="79">
         <v>1.125</v>
       </c>
-      <c r="AK5" s="89">
+      <c r="AK5" s="137">
         <v>1.1232</v>
       </c>
       <c r="AL5" s="37">
@@ -3585,17 +3616,17 @@
       <c r="AM5" s="52">
         <v>9229.9</v>
       </c>
-      <c r="AN5" s="86">
+      <c r="AN5" s="134">
         <v>9143.9599999999991</v>
       </c>
       <c r="AO5" s="20">
         <f>(AN5-AM5)/AM5</f>
         <v>-9.3110434565922186E-3</v>
       </c>
-      <c r="AP5" s="87">
+      <c r="AP5" s="135">
         <v>3115.9</v>
       </c>
-      <c r="AQ5" s="87">
+      <c r="AQ5" s="135">
         <v>3094.3</v>
       </c>
       <c r="AR5" s="24">
@@ -3605,7 +3636,7 @@
       <c r="AS5" s="70">
         <v>1779.9</v>
       </c>
-      <c r="AT5" s="88">
+      <c r="AT5" s="136">
         <v>1801.02</v>
       </c>
       <c r="AU5" s="28">
@@ -3615,7 +3646,7 @@
       <c r="AV5" s="79">
         <v>1.125</v>
       </c>
-      <c r="AW5" s="89">
+      <c r="AW5" s="137">
         <v>1.1232</v>
       </c>
       <c r="AX5" s="37">
@@ -3625,17 +3656,17 @@
       <c r="AY5" s="52">
         <v>9229.9</v>
       </c>
-      <c r="AZ5" s="86">
+      <c r="AZ5" s="134">
         <v>7011.87</v>
       </c>
       <c r="BA5" s="20">
         <f>(AZ5-AY5)/AY5</f>
         <v>-0.24030921245083911</v>
       </c>
-      <c r="BB5" s="87">
+      <c r="BB5" s="135">
         <v>3115.9</v>
       </c>
-      <c r="BC5" s="87">
+      <c r="BC5" s="135">
         <v>3297.88</v>
       </c>
       <c r="BD5" s="24">
@@ -3645,7 +3676,7 @@
       <c r="BE5" s="70">
         <v>1779.9</v>
       </c>
-      <c r="BF5" s="88">
+      <c r="BF5" s="136">
         <v>1601.16</v>
       </c>
       <c r="BG5" s="28">
@@ -3655,7 +3686,7 @@
       <c r="BH5" s="79">
         <v>1.125</v>
       </c>
-      <c r="BI5" s="89">
+      <c r="BI5" s="137">
         <v>1.0956999999999999</v>
       </c>
       <c r="BJ5" s="37">
@@ -3664,14 +3695,14 @@
       </c>
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A6" s="117"/>
+      <c r="A6" s="104"/>
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="52">
         <v>10620.5</v>
       </c>
-      <c r="D6" s="86">
+      <c r="D6" s="134">
         <v>17613.099999999999</v>
       </c>
       <c r="E6" s="20">
@@ -3681,7 +3712,7 @@
       <c r="F6" s="61">
         <v>3380.8</v>
       </c>
-      <c r="G6" s="87">
+      <c r="G6" s="135">
         <v>3328.59</v>
       </c>
       <c r="H6" s="24">
@@ -3691,7 +3722,7 @@
       <c r="I6" s="70">
         <v>1912.3</v>
       </c>
-      <c r="J6" s="88">
+      <c r="J6" s="136">
         <v>1620.75</v>
       </c>
       <c r="K6" s="28">
@@ -3701,7 +3732,7 @@
       <c r="L6" s="79">
         <v>1.1747000000000001</v>
       </c>
-      <c r="M6" s="89">
+      <c r="M6" s="137">
         <v>1.1247</v>
       </c>
       <c r="N6" s="32">
@@ -3711,7 +3742,7 @@
       <c r="O6" s="52">
         <v>10620.5</v>
       </c>
-      <c r="P6" s="86">
+      <c r="P6" s="134">
         <v>10791.47</v>
       </c>
       <c r="Q6" s="20">
@@ -3721,7 +3752,7 @@
       <c r="R6" s="61">
         <v>3380.8</v>
       </c>
-      <c r="S6" s="87">
+      <c r="S6" s="135">
         <v>3361.39</v>
       </c>
       <c r="T6" s="24">
@@ -3731,7 +3762,7 @@
       <c r="U6" s="70">
         <v>1912.3</v>
       </c>
-      <c r="V6" s="88">
+      <c r="V6" s="136">
         <v>1892.64</v>
       </c>
       <c r="W6" s="28">
@@ -3741,7 +3772,7 @@
       <c r="X6" s="79">
         <v>1.1747000000000001</v>
       </c>
-      <c r="Y6" s="89">
+      <c r="Y6" s="137">
         <v>1.1719999999999999</v>
       </c>
       <c r="Z6" s="37">
@@ -3751,7 +3782,7 @@
       <c r="AA6" s="52">
         <v>10620.5</v>
       </c>
-      <c r="AB6" s="86">
+      <c r="AB6" s="134">
         <v>17024.11</v>
       </c>
       <c r="AC6" s="20">
@@ -3761,7 +3792,7 @@
       <c r="AD6" s="61">
         <v>3380.8</v>
       </c>
-      <c r="AE6" s="87">
+      <c r="AE6" s="135">
         <v>3327.08</v>
       </c>
       <c r="AF6" s="24">
@@ -3771,7 +3802,7 @@
       <c r="AG6" s="70">
         <v>1912.3</v>
       </c>
-      <c r="AH6" s="88">
+      <c r="AH6" s="136">
         <v>1626.89</v>
       </c>
       <c r="AI6" s="28">
@@ -3781,7 +3812,7 @@
       <c r="AJ6" s="79">
         <v>1.1747000000000001</v>
       </c>
-      <c r="AK6" s="89">
+      <c r="AK6" s="137">
         <v>1.1251</v>
       </c>
       <c r="AL6" s="37">
@@ -3791,7 +3822,7 @@
       <c r="AM6" s="52">
         <v>10620.5</v>
       </c>
-      <c r="AN6" s="86">
+      <c r="AN6" s="134">
         <v>10811.04</v>
       </c>
       <c r="AO6" s="20">
@@ -3801,7 +3832,7 @@
       <c r="AP6" s="61">
         <v>3380.8</v>
       </c>
-      <c r="AQ6" s="87">
+      <c r="AQ6" s="135">
         <v>3358.77</v>
       </c>
       <c r="AR6" s="24">
@@ -3811,7 +3842,7 @@
       <c r="AS6" s="70">
         <v>1912.3</v>
       </c>
-      <c r="AT6" s="88">
+      <c r="AT6" s="136">
         <v>1888.44</v>
       </c>
       <c r="AU6" s="28">
@@ -3821,7 +3852,7 @@
       <c r="AV6" s="79">
         <v>1.1747000000000001</v>
       </c>
-      <c r="AW6" s="89">
+      <c r="AW6" s="137">
         <v>1.1727000000000001</v>
       </c>
       <c r="AX6" s="37">
@@ -3831,7 +3862,7 @@
       <c r="AY6" s="52">
         <v>10620.5</v>
       </c>
-      <c r="AZ6" s="86">
+      <c r="AZ6" s="134">
         <v>7549.37</v>
       </c>
       <c r="BA6" s="20">
@@ -3841,7 +3872,7 @@
       <c r="BB6" s="61">
         <v>3380.8</v>
       </c>
-      <c r="BC6" s="87">
+      <c r="BC6" s="135">
         <v>3354.58</v>
       </c>
       <c r="BD6" s="24">
@@ -3851,7 +3882,7 @@
       <c r="BE6" s="70">
         <v>1912.3</v>
       </c>
-      <c r="BF6" s="88">
+      <c r="BF6" s="136">
         <v>1688.72</v>
       </c>
       <c r="BG6" s="28">
@@ -3861,7 +3892,7 @@
       <c r="BH6" s="79">
         <v>1.1747000000000001</v>
       </c>
-      <c r="BI6" s="89">
+      <c r="BI6" s="137">
         <v>1.0964</v>
       </c>
       <c r="BJ6" s="37">
@@ -3870,7 +3901,7 @@
       </c>
     </row>
     <row r="7" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="118"/>
+      <c r="A7" s="105"/>
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -4076,7 +4107,7 @@
       </c>
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A8" s="116" t="s">
+      <c r="A8" s="103" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -4284,14 +4315,14 @@
       </c>
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A9" s="117"/>
+      <c r="A9" s="104"/>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="52">
         <v>33543.599999999999</v>
       </c>
-      <c r="D9" s="86">
+      <c r="D9" s="134">
         <v>52360.58</v>
       </c>
       <c r="E9" s="20">
@@ -4301,7 +4332,7 @@
       <c r="F9" s="61">
         <v>4319.8999999999996</v>
       </c>
-      <c r="G9" s="87">
+      <c r="G9" s="135">
         <v>3839.61</v>
       </c>
       <c r="H9" s="24">
@@ -4311,7 +4342,7 @@
       <c r="I9" s="70">
         <v>1776.8</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="136">
         <v>1980.93</v>
       </c>
       <c r="K9" s="28">
@@ -4321,7 +4352,7 @@
       <c r="L9" s="79">
         <v>1.1848000000000001</v>
       </c>
-      <c r="M9" s="89">
+      <c r="M9" s="137">
         <v>1.2262999999999999</v>
       </c>
       <c r="N9" s="32">
@@ -4331,7 +4362,7 @@
       <c r="O9" s="52">
         <v>33543.599999999999</v>
       </c>
-      <c r="P9" s="86">
+      <c r="P9" s="134">
         <v>35154.36</v>
       </c>
       <c r="Q9" s="20">
@@ -4341,7 +4372,7 @@
       <c r="R9" s="61">
         <v>4319.8999999999996</v>
       </c>
-      <c r="S9" s="87">
+      <c r="S9" s="135">
         <v>4297.72</v>
       </c>
       <c r="T9" s="24">
@@ -4351,7 +4382,7 @@
       <c r="U9" s="70">
         <v>1776.8</v>
       </c>
-      <c r="V9" s="88">
+      <c r="V9" s="136">
         <v>1771.76</v>
       </c>
       <c r="W9" s="28">
@@ -4361,7 +4392,7 @@
       <c r="X9" s="79">
         <v>1.1848000000000001</v>
       </c>
-      <c r="Y9" s="89">
+      <c r="Y9" s="137">
         <v>1.1855</v>
       </c>
       <c r="Z9" s="37">
@@ -4371,7 +4402,7 @@
       <c r="AA9" s="52">
         <v>33543.599999999999</v>
       </c>
-      <c r="AB9" s="86">
+      <c r="AB9" s="134">
         <v>52320.87</v>
       </c>
       <c r="AC9" s="20">
@@ -4381,7 +4412,7 @@
       <c r="AD9" s="61">
         <v>4319.8999999999996</v>
       </c>
-      <c r="AE9" s="87">
+      <c r="AE9" s="135">
         <v>3843</v>
       </c>
       <c r="AF9" s="24">
@@ -4391,7 +4422,7 @@
       <c r="AG9" s="70">
         <v>1776.8</v>
       </c>
-      <c r="AH9" s="88">
+      <c r="AH9" s="136">
         <v>1978.43</v>
       </c>
       <c r="AI9" s="28">
@@ -4401,7 +4432,7 @@
       <c r="AJ9" s="79">
         <v>1.1848000000000001</v>
       </c>
-      <c r="AK9" s="89">
+      <c r="AK9" s="137">
         <v>1.2257</v>
       </c>
       <c r="AL9" s="37">
@@ -4411,7 +4442,7 @@
       <c r="AM9" s="52">
         <v>33543.599999999999</v>
       </c>
-      <c r="AN9" s="86">
+      <c r="AN9" s="134">
         <v>35273.660000000003</v>
       </c>
       <c r="AO9" s="20">
@@ -4421,7 +4452,7 @@
       <c r="AP9" s="61">
         <v>4319.8999999999996</v>
       </c>
-      <c r="AQ9" s="87">
+      <c r="AQ9" s="135">
         <v>4298.6099999999997</v>
       </c>
       <c r="AR9" s="24">
@@ -4431,7 +4462,7 @@
       <c r="AS9" s="70">
         <v>1776.8</v>
       </c>
-      <c r="AT9" s="88">
+      <c r="AT9" s="136">
         <v>1771.59</v>
       </c>
       <c r="AU9" s="28">
@@ -4441,7 +4472,7 @@
       <c r="AV9" s="79">
         <v>1.1848000000000001</v>
       </c>
-      <c r="AW9" s="89">
+      <c r="AW9" s="137">
         <v>1.1849000000000001</v>
       </c>
       <c r="AX9" s="37">
@@ -4451,7 +4482,7 @@
       <c r="AY9" s="52">
         <v>33543.599999999999</v>
       </c>
-      <c r="AZ9" s="86">
+      <c r="AZ9" s="134">
         <v>49554.71</v>
       </c>
       <c r="BA9" s="20">
@@ -4461,7 +4492,7 @@
       <c r="BB9" s="61">
         <v>4319.8999999999996</v>
       </c>
-      <c r="BC9" s="87">
+      <c r="BC9" s="135">
         <v>4107.6000000000004</v>
       </c>
       <c r="BD9" s="24">
@@ -4471,7 +4502,7 @@
       <c r="BE9" s="70">
         <v>1776.8</v>
       </c>
-      <c r="BF9" s="88">
+      <c r="BF9" s="136">
         <v>2064.7800000000002</v>
       </c>
       <c r="BG9" s="28">
@@ -4481,7 +4512,7 @@
       <c r="BH9" s="79">
         <v>1.1848000000000001</v>
       </c>
-      <c r="BI9" s="89">
+      <c r="BI9" s="137">
         <v>1.2362</v>
       </c>
       <c r="BJ9" s="37">
@@ -4490,14 +4521,14 @@
       </c>
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A10" s="117"/>
+      <c r="A10" s="104"/>
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="52">
         <v>48146</v>
       </c>
-      <c r="D10" s="86">
+      <c r="D10" s="134">
         <v>70857.75</v>
       </c>
       <c r="E10" s="20">
@@ -4507,7 +4538,7 @@
       <c r="F10" s="61">
         <v>4357</v>
       </c>
-      <c r="G10" s="87">
+      <c r="G10" s="135">
         <v>3883.54</v>
       </c>
       <c r="H10" s="24">
@@ -4517,7 +4548,7 @@
       <c r="I10" s="70">
         <v>1757.7</v>
       </c>
-      <c r="J10" s="88">
+      <c r="J10" s="136">
         <v>2025.77</v>
       </c>
       <c r="K10" s="28">
@@ -4527,7 +4558,7 @@
       <c r="L10" s="79">
         <v>1.1594</v>
       </c>
-      <c r="M10" s="89">
+      <c r="M10" s="137">
         <v>1.2287999999999999</v>
       </c>
       <c r="N10" s="32">
@@ -4537,7 +4568,7 @@
       <c r="O10" s="52">
         <v>48146</v>
       </c>
-      <c r="P10" s="86">
+      <c r="P10" s="134">
         <v>43904.76</v>
       </c>
       <c r="Q10" s="20">
@@ -4547,7 +4578,7 @@
       <c r="R10" s="61">
         <v>4357</v>
       </c>
-      <c r="S10" s="87">
+      <c r="S10" s="135">
         <v>4312.01</v>
       </c>
       <c r="T10" s="24">
@@ -4557,7 +4588,7 @@
       <c r="U10" s="70">
         <v>1757.7</v>
       </c>
-      <c r="V10" s="88">
+      <c r="V10" s="136">
         <v>1756.18</v>
       </c>
       <c r="W10" s="28">
@@ -4567,7 +4598,7 @@
       <c r="X10" s="79">
         <v>1.1594</v>
       </c>
-      <c r="Y10" s="89">
+      <c r="Y10" s="137">
         <v>1.1579999999999999</v>
       </c>
       <c r="Z10" s="37">
@@ -4577,7 +4608,7 @@
       <c r="AA10" s="52">
         <v>48146</v>
       </c>
-      <c r="AB10" s="86">
+      <c r="AB10" s="134">
         <v>70617.490000000005</v>
       </c>
       <c r="AC10" s="20">
@@ -4587,7 +4618,7 @@
       <c r="AD10" s="61">
         <v>4357</v>
       </c>
-      <c r="AE10" s="87">
+      <c r="AE10" s="135">
         <v>3897.21</v>
       </c>
       <c r="AF10" s="24">
@@ -4597,7 +4628,7 @@
       <c r="AG10" s="70">
         <v>1757.7</v>
       </c>
-      <c r="AH10" s="88">
+      <c r="AH10" s="136">
         <v>2020.66</v>
       </c>
       <c r="AI10" s="28">
@@ -4607,7 +4638,7 @@
       <c r="AJ10" s="79">
         <v>1.1594</v>
       </c>
-      <c r="AK10" s="89">
+      <c r="AK10" s="137">
         <v>1.2274</v>
       </c>
       <c r="AL10" s="37">
@@ -4617,7 +4648,7 @@
       <c r="AM10" s="52">
         <v>48146</v>
       </c>
-      <c r="AN10" s="86">
+      <c r="AN10" s="134">
         <v>43750.81</v>
       </c>
       <c r="AO10" s="20">
@@ -4627,7 +4658,7 @@
       <c r="AP10" s="61">
         <v>4357</v>
       </c>
-      <c r="AQ10" s="87">
+      <c r="AQ10" s="135">
         <v>4323.62</v>
       </c>
       <c r="AR10" s="24">
@@ -4637,7 +4668,7 @@
       <c r="AS10" s="70">
         <v>1757.7</v>
       </c>
-      <c r="AT10" s="88">
+      <c r="AT10" s="136">
         <v>1755.85</v>
       </c>
       <c r="AU10" s="28">
@@ -4647,7 +4678,7 @@
       <c r="AV10" s="79">
         <v>1.1594</v>
       </c>
-      <c r="AW10" s="89">
+      <c r="AW10" s="137">
         <v>1.157</v>
       </c>
       <c r="AX10" s="37">
@@ -4657,7 +4688,7 @@
       <c r="AY10" s="52">
         <v>48146</v>
       </c>
-      <c r="AZ10" s="86">
+      <c r="AZ10" s="134">
         <v>58153.93</v>
       </c>
       <c r="BA10" s="20">
@@ -4667,7 +4698,7 @@
       <c r="BB10" s="61">
         <v>4357</v>
       </c>
-      <c r="BC10" s="87">
+      <c r="BC10" s="135">
         <v>4335.79</v>
       </c>
       <c r="BD10" s="24">
@@ -4677,7 +4708,7 @@
       <c r="BE10" s="70">
         <v>1757.7</v>
       </c>
-      <c r="BF10" s="88">
+      <c r="BF10" s="136">
         <v>2116.5</v>
       </c>
       <c r="BG10" s="28">
@@ -4687,7 +4718,7 @@
       <c r="BH10" s="79">
         <v>1.1594</v>
       </c>
-      <c r="BI10" s="89">
+      <c r="BI10" s="137">
         <v>1.2437</v>
       </c>
       <c r="BJ10" s="37">
@@ -4696,7 +4727,7 @@
       </c>
     </row>
     <row r="11" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="118"/>
+      <c r="A11" s="105"/>
       <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
@@ -4902,7 +4933,7 @@
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A12" s="116" t="s">
+      <c r="A12" s="103" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -5110,14 +5141,14 @@
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A13" s="117"/>
+      <c r="A13" s="104"/>
       <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="52">
         <v>19262.900000000001</v>
       </c>
-      <c r="D13" s="86">
+      <c r="D13" s="134">
         <v>81272.17</v>
       </c>
       <c r="E13" s="20">
@@ -5127,7 +5158,7 @@
       <c r="F13" s="61">
         <v>3825.33</v>
       </c>
-      <c r="G13" s="87">
+      <c r="G13" s="135">
         <v>4896.72</v>
       </c>
       <c r="H13" s="24">
@@ -5137,7 +5168,7 @@
       <c r="I13" s="70">
         <v>1807.3</v>
       </c>
-      <c r="J13" s="88">
+      <c r="J13" s="136">
         <v>1907.09</v>
       </c>
       <c r="K13" s="28">
@@ -5147,7 +5178,7 @@
       <c r="L13" s="79">
         <v>1.0427999999999999</v>
       </c>
-      <c r="M13" s="89">
+      <c r="M13" s="137">
         <v>1.1393</v>
       </c>
       <c r="N13" s="32">
@@ -5157,7 +5188,7 @@
       <c r="O13" s="52">
         <v>19262.900000000001</v>
       </c>
-      <c r="P13" s="86">
+      <c r="P13" s="134">
         <v>19991.560000000001</v>
       </c>
       <c r="Q13" s="20">
@@ -5167,7 +5198,7 @@
       <c r="R13" s="61">
         <v>3825.33</v>
       </c>
-      <c r="S13" s="87">
+      <c r="S13" s="135">
         <v>3787.62</v>
       </c>
       <c r="T13" s="24">
@@ -5177,7 +5208,7 @@
       <c r="U13" s="70">
         <v>1807.3</v>
       </c>
-      <c r="V13" s="88">
+      <c r="V13" s="136">
         <v>1807.85</v>
       </c>
       <c r="W13" s="28">
@@ -5187,7 +5218,7 @@
       <c r="X13" s="79">
         <v>1.0427999999999999</v>
       </c>
-      <c r="Y13" s="89">
+      <c r="Y13" s="137">
         <v>1.0479000000000001</v>
       </c>
       <c r="Z13" s="37">
@@ -5197,7 +5228,7 @@
       <c r="AA13" s="52">
         <v>19262.900000000001</v>
       </c>
-      <c r="AB13" s="86">
+      <c r="AB13" s="134">
         <v>79741.679999999993</v>
       </c>
       <c r="AC13" s="20">
@@ -5207,7 +5238,7 @@
       <c r="AD13" s="61">
         <v>3825.33</v>
       </c>
-      <c r="AE13" s="87">
+      <c r="AE13" s="135">
         <v>4890.1000000000004</v>
       </c>
       <c r="AF13" s="24">
@@ -5217,7 +5248,7 @@
       <c r="AG13" s="70">
         <v>1807.3</v>
       </c>
-      <c r="AH13" s="88">
+      <c r="AH13" s="136">
         <v>1906.97</v>
       </c>
       <c r="AI13" s="28">
@@ -5227,7 +5258,7 @@
       <c r="AJ13" s="79">
         <v>1.0427999999999999</v>
       </c>
-      <c r="AK13" s="89">
+      <c r="AK13" s="137">
         <v>1.1384000000000001</v>
       </c>
       <c r="AL13" s="37">
@@ -5237,7 +5268,7 @@
       <c r="AM13" s="52">
         <v>19262.900000000001</v>
       </c>
-      <c r="AN13" s="86">
+      <c r="AN13" s="134">
         <v>19909.41</v>
       </c>
       <c r="AO13" s="20">
@@ -5247,7 +5278,7 @@
       <c r="AP13" s="61">
         <v>3825.33</v>
       </c>
-      <c r="AQ13" s="87">
+      <c r="AQ13" s="135">
         <v>3786.85</v>
       </c>
       <c r="AR13" s="24">
@@ -5257,7 +5288,7 @@
       <c r="AS13" s="70">
         <v>1807.3</v>
       </c>
-      <c r="AT13" s="88">
+      <c r="AT13" s="136">
         <v>1807.93</v>
       </c>
       <c r="AU13" s="28">
@@ -5267,7 +5298,7 @@
       <c r="AV13" s="79">
         <v>1.0427999999999999</v>
       </c>
-      <c r="AW13" s="89">
+      <c r="AW13" s="137">
         <v>1.0486</v>
       </c>
       <c r="AX13" s="37">
@@ -5277,7 +5308,7 @@
       <c r="AY13" s="52">
         <v>19262.900000000001</v>
       </c>
-      <c r="AZ13" s="86">
+      <c r="AZ13" s="134">
         <v>67559.95</v>
       </c>
       <c r="BA13" s="20">
@@ -5287,7 +5318,7 @@
       <c r="BB13" s="61">
         <v>3825.33</v>
       </c>
-      <c r="BC13" s="87">
+      <c r="BC13" s="135">
         <v>5243.09</v>
       </c>
       <c r="BD13" s="24">
@@ -5297,7 +5328,7 @@
       <c r="BE13" s="70">
         <v>1807.3</v>
       </c>
-      <c r="BF13" s="88">
+      <c r="BF13" s="136">
         <v>1892.46</v>
       </c>
       <c r="BG13" s="28">
@@ -5307,7 +5338,7 @@
       <c r="BH13" s="79">
         <v>1.0427999999999999</v>
       </c>
-      <c r="BI13" s="89">
+      <c r="BI13" s="137">
         <v>1.1371</v>
       </c>
       <c r="BJ13" s="37">
@@ -5316,14 +5347,14 @@
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A14" s="117"/>
+      <c r="A14" s="104"/>
       <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C14" s="52">
         <v>19311.900000000001</v>
       </c>
-      <c r="D14" s="86">
+      <c r="D14" s="134">
         <v>108232.08</v>
       </c>
       <c r="E14" s="20">
@@ -5333,7 +5364,7 @@
       <c r="F14" s="61">
         <v>3585.62</v>
       </c>
-      <c r="G14" s="87">
+      <c r="G14" s="135">
         <v>4963.71</v>
       </c>
       <c r="H14" s="24">
@@ -5343,7 +5374,7 @@
       <c r="I14" s="70">
         <v>1663.6</v>
       </c>
-      <c r="J14" s="88">
+      <c r="J14" s="136">
         <v>1948.08</v>
       </c>
       <c r="K14" s="28">
@@ -5353,7 +5384,7 @@
       <c r="L14" s="79">
         <v>0.97989999999999999</v>
       </c>
-      <c r="M14" s="89">
+      <c r="M14" s="137">
         <v>1.1406000000000001</v>
       </c>
       <c r="N14" s="32">
@@ -5363,7 +5394,7 @@
       <c r="O14" s="52">
         <v>19311.900000000001</v>
       </c>
-      <c r="P14" s="86">
+      <c r="P14" s="134">
         <v>19471.509999999998</v>
       </c>
       <c r="Q14" s="20">
@@ -5373,7 +5404,7 @@
       <c r="R14" s="61">
         <v>3585.62</v>
       </c>
-      <c r="S14" s="87">
+      <c r="S14" s="135">
         <v>3592.93</v>
       </c>
       <c r="T14" s="24">
@@ -5383,7 +5414,7 @@
       <c r="U14" s="70">
         <v>1663.6</v>
       </c>
-      <c r="V14" s="88">
+      <c r="V14" s="136">
         <v>1663.93</v>
       </c>
       <c r="W14" s="28">
@@ -5393,7 +5424,7 @@
       <c r="X14" s="79">
         <v>0.97989999999999999</v>
       </c>
-      <c r="Y14" s="89">
+      <c r="Y14" s="137">
         <v>0.98019999999999996</v>
       </c>
       <c r="Z14" s="37">
@@ -5403,7 +5434,7 @@
       <c r="AA14" s="52">
         <v>19311.900000000001</v>
       </c>
-      <c r="AB14" s="86">
+      <c r="AB14" s="134">
         <v>103914.82</v>
       </c>
       <c r="AC14" s="20">
@@ -5413,7 +5444,7 @@
       <c r="AD14" s="61">
         <v>3585.62</v>
       </c>
-      <c r="AE14" s="87">
+      <c r="AE14" s="135">
         <v>4955.55</v>
       </c>
       <c r="AF14" s="24">
@@ -5423,7 +5454,7 @@
       <c r="AG14" s="70">
         <v>1663.6</v>
       </c>
-      <c r="AH14" s="88">
+      <c r="AH14" s="136">
         <v>1945.91</v>
       </c>
       <c r="AI14" s="28">
@@ -5433,7 +5464,7 @@
       <c r="AJ14" s="79">
         <v>0.97989999999999999</v>
       </c>
-      <c r="AK14" s="89">
+      <c r="AK14" s="137">
         <v>1.1389</v>
       </c>
       <c r="AL14" s="37">
@@ -5443,7 +5474,7 @@
       <c r="AM14" s="52">
         <v>19311.900000000001</v>
       </c>
-      <c r="AN14" s="86">
+      <c r="AN14" s="134">
         <v>19388.490000000002</v>
       </c>
       <c r="AO14" s="20">
@@ -5453,7 +5484,7 @@
       <c r="AP14" s="61">
         <v>3585.62</v>
       </c>
-      <c r="AQ14" s="87">
+      <c r="AQ14" s="135">
         <v>3593.35</v>
       </c>
       <c r="AR14" s="24">
@@ -5463,7 +5494,7 @@
       <c r="AS14" s="70">
         <v>1663.6</v>
       </c>
-      <c r="AT14" s="88">
+      <c r="AT14" s="136">
         <v>1662.95</v>
       </c>
       <c r="AU14" s="28">
@@ -5473,7 +5504,7 @@
       <c r="AV14" s="79">
         <v>0.97989999999999999</v>
       </c>
-      <c r="AW14" s="89">
+      <c r="AW14" s="137">
         <v>0.9798</v>
       </c>
       <c r="AX14" s="37">
@@ -5483,7 +5514,7 @@
       <c r="AY14" s="52">
         <v>19311.900000000001</v>
       </c>
-      <c r="AZ14" s="86">
+      <c r="AZ14" s="134">
         <v>72169.69</v>
       </c>
       <c r="BA14" s="20">
@@ -5493,7 +5524,7 @@
       <c r="BB14" s="61">
         <v>3585.62</v>
       </c>
-      <c r="BC14" s="87">
+      <c r="BC14" s="135">
         <v>5363.7</v>
       </c>
       <c r="BD14" s="24">
@@ -5503,7 +5534,7 @@
       <c r="BE14" s="70">
         <v>1663.6</v>
       </c>
-      <c r="BF14" s="88">
+      <c r="BF14" s="136">
         <v>1867.68</v>
       </c>
       <c r="BG14" s="28">
@@ -5513,7 +5544,7 @@
       <c r="BH14" s="79">
         <v>0.97989999999999999</v>
       </c>
-      <c r="BI14" s="89">
+      <c r="BI14" s="137">
         <v>1.1193</v>
       </c>
       <c r="BJ14" s="37">
@@ -5522,7 +5553,7 @@
       </c>
     </row>
     <row r="15" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="118"/>
+      <c r="A15" s="105"/>
       <c r="B15" s="3" t="s">
         <v>22</v>
       </c>
@@ -5728,1521 +5759,2481 @@
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A16" s="116" t="s">
+      <c r="A16" s="103" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="21" t="e">
+      <c r="C16" s="55">
+        <v>28456.1</v>
+      </c>
+      <c r="D16" s="56">
+        <v>21036.2</v>
+      </c>
+      <c r="E16" s="21">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="25" t="e">
+        <v>-0.26074901339255901</v>
+      </c>
+      <c r="F16" s="64">
+        <v>4109.3100000000004</v>
+      </c>
+      <c r="G16" s="65">
+        <v>3881.18</v>
+      </c>
+      <c r="H16" s="25">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I16" s="73"/>
-      <c r="J16" s="74"/>
-      <c r="K16" s="29" t="e">
+        <v>-5.5515402829185566E-2</v>
+      </c>
+      <c r="I16" s="73">
+        <v>1988.5</v>
+      </c>
+      <c r="J16" s="74">
+        <v>1863.02</v>
+      </c>
+      <c r="K16" s="29">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L16" s="82"/>
-      <c r="M16" s="83"/>
-      <c r="N16" s="33" t="e">
+        <v>-6.3102841337691742E-2</v>
+      </c>
+      <c r="L16" s="82">
+        <v>1.0839000000000001</v>
+      </c>
+      <c r="M16" s="83">
+        <v>1.0707</v>
+      </c>
+      <c r="N16" s="33">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O16" s="55"/>
-      <c r="P16" s="56"/>
-      <c r="Q16" s="21" t="e">
+        <v>-1.2178245225574407E-2</v>
+      </c>
+      <c r="O16" s="55">
+        <v>28456.1</v>
+      </c>
+      <c r="P16" s="56">
+        <v>28538.720000000001</v>
+      </c>
+      <c r="Q16" s="21">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R16" s="64"/>
-      <c r="S16" s="65"/>
-      <c r="T16" s="25" t="e">
-        <f>(S16-R16)/R16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U16" s="73"/>
-      <c r="V16" s="74"/>
-      <c r="W16" s="29" t="e">
+        <v>2.9034196534311668E-3</v>
+      </c>
+      <c r="R16" s="64">
+        <v>4109.3100000000004</v>
+      </c>
+      <c r="S16" s="65">
+        <v>4105.2</v>
+      </c>
+      <c r="T16" s="25">
+        <f t="shared" si="5"/>
+        <v>-1.0001679114013257E-3</v>
+      </c>
+      <c r="U16" s="73">
+        <v>1988.5</v>
+      </c>
+      <c r="V16" s="74">
+        <v>1988.27</v>
+      </c>
+      <c r="W16" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X16" s="82"/>
-      <c r="Y16" s="83"/>
-      <c r="Z16" s="38" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA16" s="55"/>
-      <c r="AB16" s="56"/>
-      <c r="AC16" s="21" t="e">
+        <v>-1.1566507417652411E-4</v>
+      </c>
+      <c r="X16" s="82">
+        <v>1.0839000000000001</v>
+      </c>
+      <c r="Y16" s="83">
+        <v>1.0840000000000001</v>
+      </c>
+      <c r="Z16" s="33">
+        <f t="shared" ref="Z16:Z27" si="20">(Y16-X16)/X16</f>
+        <v>9.2259433527067976E-5</v>
+      </c>
+      <c r="AA16" s="55">
+        <v>28456.1</v>
+      </c>
+      <c r="AB16" s="56">
+        <v>21232.53</v>
+      </c>
+      <c r="AC16" s="21">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD16" s="64"/>
-      <c r="AE16" s="65"/>
-      <c r="AF16" s="25" t="e">
+        <v>-0.25384961396677691</v>
+      </c>
+      <c r="AD16" s="64">
+        <v>4109.3100000000004</v>
+      </c>
+      <c r="AE16" s="65">
+        <v>3874.08</v>
+      </c>
+      <c r="AF16" s="25">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG16" s="73"/>
-      <c r="AH16" s="74"/>
-      <c r="AI16" s="29" t="e">
+        <v>-5.7243186812384668E-2</v>
+      </c>
+      <c r="AG16" s="73">
+        <v>1988.5</v>
+      </c>
+      <c r="AH16" s="74">
+        <v>1862.53</v>
+      </c>
+      <c r="AI16" s="29">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ16" s="82"/>
-      <c r="AK16" s="83"/>
-      <c r="AL16" s="38" t="e">
+        <v>-6.3349258234850409E-2</v>
+      </c>
+      <c r="AJ16" s="82">
+        <v>1.0839000000000001</v>
+      </c>
+      <c r="AK16" s="83">
+        <v>1.0709</v>
+      </c>
+      <c r="AL16" s="33">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM16" s="55"/>
-      <c r="AN16" s="56"/>
-      <c r="AO16" s="21" t="e">
+        <v>-1.199372635852027E-2</v>
+      </c>
+      <c r="AM16" s="55">
+        <v>28456.1</v>
+      </c>
+      <c r="AN16" s="56">
+        <v>28422.71</v>
+      </c>
+      <c r="AO16" s="21">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AP16" s="64"/>
-      <c r="AQ16" s="65"/>
-      <c r="AR16" s="25" t="e">
+        <v>-1.1733863740990304E-3</v>
+      </c>
+      <c r="AP16" s="64">
+        <v>4109.3100000000004</v>
+      </c>
+      <c r="AQ16" s="65">
+        <v>4107.01</v>
+      </c>
+      <c r="AR16" s="25">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AS16" s="73"/>
-      <c r="AT16" s="74"/>
-      <c r="AU16" s="29" t="e">
+        <v>-5.5970467061384555E-4</v>
+      </c>
+      <c r="AS16" s="73">
+        <v>1988.5</v>
+      </c>
+      <c r="AT16" s="74">
+        <v>1985.48</v>
+      </c>
+      <c r="AU16" s="29">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AV16" s="82"/>
-      <c r="AW16" s="83"/>
-      <c r="AX16" s="38" t="e">
+        <v>-1.5187327131003178E-3</v>
+      </c>
+      <c r="AV16" s="82">
+        <v>1.0839000000000001</v>
+      </c>
+      <c r="AW16" s="83">
+        <v>1.0834999999999999</v>
+      </c>
+      <c r="AX16" s="33">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AY16" s="55"/>
-      <c r="AZ16" s="56"/>
-      <c r="BA16" s="21" t="e">
+        <v>-3.6903773410847676E-4</v>
+      </c>
+      <c r="AY16" s="55">
+        <v>28456.1</v>
+      </c>
+      <c r="AZ16" s="56">
+        <v>15127.29</v>
+      </c>
+      <c r="BA16" s="21">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BB16" s="64"/>
-      <c r="BC16" s="65"/>
-      <c r="BD16" s="25" t="e">
+        <v>-0.4683990427360038</v>
+      </c>
+      <c r="BB16" s="64">
+        <v>4109.3100000000004</v>
+      </c>
+      <c r="BC16" s="65">
+        <v>3856.45</v>
+      </c>
+      <c r="BD16" s="25">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BE16" s="73"/>
-      <c r="BF16" s="74"/>
-      <c r="BG16" s="29" t="e">
+        <v>-6.1533444787567879E-2</v>
+      </c>
+      <c r="BE16" s="73">
+        <v>1988.5</v>
+      </c>
+      <c r="BF16" s="74">
+        <v>1827.48</v>
+      </c>
+      <c r="BG16" s="29">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BH16" s="82"/>
-      <c r="BI16" s="83"/>
-      <c r="BJ16" s="38" t="e">
+        <v>-8.097560975609755E-2</v>
+      </c>
+      <c r="BH16" s="82">
+        <v>1.0839000000000001</v>
+      </c>
+      <c r="BI16" s="83">
+        <v>1.0532999999999999</v>
+      </c>
+      <c r="BJ16" s="38">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-2.8231386659286078E-2</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A17" s="117"/>
+      <c r="A17" s="104"/>
       <c r="B17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="20" t="e">
+      <c r="C17" s="52">
+        <v>30586.799999999999</v>
+      </c>
+      <c r="D17" s="134">
+        <v>26742.12</v>
+      </c>
+      <c r="E17" s="20">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F17" s="61"/>
-      <c r="G17" s="87"/>
-      <c r="H17" s="24" t="e">
+        <v>-0.12569735964533721</v>
+      </c>
+      <c r="F17" s="61">
+        <v>4450.38</v>
+      </c>
+      <c r="G17" s="135">
+        <v>3922.19</v>
+      </c>
+      <c r="H17" s="24">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I17" s="70"/>
-      <c r="J17" s="88"/>
-      <c r="K17" s="28" t="e">
+        <v>-0.11868424718788059</v>
+      </c>
+      <c r="I17" s="70">
+        <v>1917.9</v>
+      </c>
+      <c r="J17" s="136">
+        <v>1900.8</v>
+      </c>
+      <c r="K17" s="28">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L17" s="79"/>
-      <c r="M17" s="89"/>
-      <c r="N17" s="32" t="e">
+        <v>-8.9160018770530966E-3</v>
+      </c>
+      <c r="L17" s="79">
+        <v>1.091</v>
+      </c>
+      <c r="M17" s="137">
+        <v>1.0711999999999999</v>
+      </c>
+      <c r="N17" s="32">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O17" s="52"/>
-      <c r="P17" s="86"/>
-      <c r="Q17" s="20" t="e">
+        <v>-1.81484876260312E-2</v>
+      </c>
+      <c r="O17" s="52">
+        <v>30586.799999999999</v>
+      </c>
+      <c r="P17" s="134">
+        <v>30549.919999999998</v>
+      </c>
+      <c r="Q17" s="20">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R17" s="61"/>
-      <c r="S17" s="87"/>
-      <c r="T17" s="24" t="e">
+        <v>-1.2057488851400283E-3</v>
+      </c>
+      <c r="R17" s="61">
+        <v>4450.38</v>
+      </c>
+      <c r="S17" s="135">
+        <v>4445.8900000000003</v>
+      </c>
+      <c r="T17" s="24">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U17" s="70"/>
-      <c r="V17" s="88"/>
-      <c r="W17" s="28" t="e">
+        <v>-1.0089026105635432E-3</v>
+      </c>
+      <c r="U17" s="70">
+        <v>1917.9</v>
+      </c>
+      <c r="V17" s="136">
+        <v>1918.35</v>
+      </c>
+      <c r="W17" s="28">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X17" s="79"/>
-      <c r="Y17" s="89"/>
-      <c r="Z17" s="37" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA17" s="52"/>
-      <c r="AB17" s="86"/>
-      <c r="AC17" s="20" t="e">
+        <v>2.3463162834340585E-4</v>
+      </c>
+      <c r="X17" s="79">
+        <v>1.091</v>
+      </c>
+      <c r="Y17" s="137">
+        <v>1.0908</v>
+      </c>
+      <c r="Z17" s="32">
+        <f t="shared" si="20"/>
+        <v>-1.8331805682857743E-4</v>
+      </c>
+      <c r="AA17" s="52">
+        <v>30586.799999999999</v>
+      </c>
+      <c r="AB17" s="134">
+        <v>27310.98</v>
+      </c>
+      <c r="AC17" s="20">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD17" s="61"/>
-      <c r="AE17" s="87"/>
-      <c r="AF17" s="24" t="e">
+        <v>-0.10709914080583781</v>
+      </c>
+      <c r="AD17" s="61">
+        <v>4450.38</v>
+      </c>
+      <c r="AE17" s="135">
+        <v>3917.3</v>
+      </c>
+      <c r="AF17" s="24">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG17" s="70"/>
-      <c r="AH17" s="88"/>
-      <c r="AI17" s="28" t="e">
+        <v>-0.11978302976375049</v>
+      </c>
+      <c r="AG17" s="70">
+        <v>1917.9</v>
+      </c>
+      <c r="AH17" s="136">
+        <v>1901.01</v>
+      </c>
+      <c r="AI17" s="28">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ17" s="79"/>
-      <c r="AK17" s="89"/>
-      <c r="AL17" s="37" t="e">
+        <v>-8.8065071171594452E-3</v>
+      </c>
+      <c r="AJ17" s="79">
+        <v>1.091</v>
+      </c>
+      <c r="AK17" s="137">
+        <v>1.0712999999999999</v>
+      </c>
+      <c r="AL17" s="32">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM17" s="52"/>
-      <c r="AN17" s="86"/>
-      <c r="AO17" s="20" t="e">
+        <v>-1.8056828597616911E-2</v>
+      </c>
+      <c r="AM17" s="52">
+        <v>30586.799999999999</v>
+      </c>
+      <c r="AN17" s="134">
+        <v>30468.25</v>
+      </c>
+      <c r="AO17" s="20">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AP17" s="61"/>
-      <c r="AQ17" s="87"/>
-      <c r="AR17" s="24" t="e">
+        <v>-3.8758549439627315E-3</v>
+      </c>
+      <c r="AP17" s="61">
+        <v>4450.38</v>
+      </c>
+      <c r="AQ17" s="135">
+        <v>4449.25</v>
+      </c>
+      <c r="AR17" s="24">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AS17" s="70"/>
-      <c r="AT17" s="88"/>
-      <c r="AU17" s="28" t="e">
+        <v>-2.5391090199041637E-4</v>
+      </c>
+      <c r="AS17" s="70">
+        <v>1917.9</v>
+      </c>
+      <c r="AT17" s="136">
+        <v>1918.81</v>
+      </c>
+      <c r="AU17" s="28">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AV17" s="79"/>
-      <c r="AW17" s="89"/>
-      <c r="AX17" s="37" t="e">
+        <v>4.7447729287233663E-4</v>
+      </c>
+      <c r="AV17" s="79">
+        <v>1.091</v>
+      </c>
+      <c r="AW17" s="137">
+        <v>1.091</v>
+      </c>
+      <c r="AX17" s="32">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AY17" s="52"/>
-      <c r="AZ17" s="86"/>
-      <c r="BA17" s="20" t="e">
+        <v>0</v>
+      </c>
+      <c r="AY17" s="52">
+        <v>30586.799999999999</v>
+      </c>
+      <c r="AZ17" s="134">
+        <v>14090.44</v>
+      </c>
+      <c r="BA17" s="20">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BB17" s="61"/>
-      <c r="BC17" s="87"/>
-      <c r="BD17" s="24" t="e">
+        <v>-0.53932938391724539</v>
+      </c>
+      <c r="BB17" s="61">
+        <v>4450.38</v>
+      </c>
+      <c r="BC17" s="135">
+        <v>3858.16</v>
+      </c>
+      <c r="BD17" s="24">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BE17" s="70"/>
-      <c r="BF17" s="88"/>
-      <c r="BG17" s="28" t="e">
+        <v>-0.13307178263429195</v>
+      </c>
+      <c r="BE17" s="70">
+        <v>1917.9</v>
+      </c>
+      <c r="BF17" s="136">
+        <v>1849.97</v>
+      </c>
+      <c r="BG17" s="28">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BH17" s="79"/>
-      <c r="BI17" s="89"/>
-      <c r="BJ17" s="37" t="e">
+        <v>-3.5418947807497818E-2</v>
+      </c>
+      <c r="BH17" s="79">
+        <v>1.091</v>
+      </c>
+      <c r="BI17" s="137">
+        <v>1.0405</v>
+      </c>
+      <c r="BJ17" s="37">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-4.6287809349220888E-2</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A18" s="117"/>
+      <c r="A18" s="104"/>
       <c r="B18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="20" t="e">
+      <c r="C18" s="52">
+        <v>27974.5</v>
+      </c>
+      <c r="D18" s="134">
+        <v>34085.5</v>
+      </c>
+      <c r="E18" s="20">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F18" s="61"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="24" t="e">
+        <v>0.21844894457452321</v>
+      </c>
+      <c r="F18" s="61">
+        <v>4288.05</v>
+      </c>
+      <c r="G18" s="135">
+        <v>3964.1</v>
+      </c>
+      <c r="H18" s="24">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I18" s="70"/>
-      <c r="J18" s="88"/>
-      <c r="K18" s="28" t="e">
+        <v>-7.5547160131061969E-2</v>
+      </c>
+      <c r="I18" s="70">
+        <v>1869.5</v>
+      </c>
+      <c r="J18" s="136">
+        <v>1939.78</v>
+      </c>
+      <c r="K18" s="28">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L18" s="79"/>
-      <c r="M18" s="89"/>
-      <c r="N18" s="32" t="e">
+        <v>3.7592939288579819E-2</v>
+      </c>
+      <c r="L18" s="79">
+        <v>1.0569999999999999</v>
+      </c>
+      <c r="M18" s="137">
+        <v>1.0716000000000001</v>
+      </c>
+      <c r="N18" s="32">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O18" s="52"/>
-      <c r="P18" s="86"/>
-      <c r="Q18" s="20" t="e">
+        <v>1.381267738883649E-2</v>
+      </c>
+      <c r="O18" s="52">
+        <v>27974.5</v>
+      </c>
+      <c r="P18" s="134">
+        <v>27044.13</v>
+      </c>
+      <c r="Q18" s="20">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R18" s="61"/>
-      <c r="S18" s="87"/>
-      <c r="T18" s="24" t="e">
+        <v>-3.3257788342955154E-2</v>
+      </c>
+      <c r="R18" s="61">
+        <v>4288.05</v>
+      </c>
+      <c r="S18" s="135">
+        <v>4289.28</v>
+      </c>
+      <c r="T18" s="24">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U18" s="70"/>
-      <c r="V18" s="88"/>
-      <c r="W18" s="28" t="e">
+        <v>2.8684367019963933E-4</v>
+      </c>
+      <c r="U18" s="70">
+        <v>1869.5</v>
+      </c>
+      <c r="V18" s="136">
+        <v>1869.9</v>
+      </c>
+      <c r="W18" s="28">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X18" s="79"/>
-      <c r="Y18" s="89"/>
-      <c r="Z18" s="37" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA18" s="52"/>
-      <c r="AB18" s="86"/>
-      <c r="AC18" s="20" t="e">
+        <v>2.139609521262856E-4</v>
+      </c>
+      <c r="X18" s="79">
+        <v>1.0569999999999999</v>
+      </c>
+      <c r="Y18" s="137">
+        <v>1.0570999999999999</v>
+      </c>
+      <c r="Z18" s="32">
+        <f t="shared" si="20"/>
+        <v>9.4607379375580888E-5</v>
+      </c>
+      <c r="AA18" s="52">
+        <v>27974.5</v>
+      </c>
+      <c r="AB18" s="134">
+        <v>35189.949999999997</v>
+      </c>
+      <c r="AC18" s="20">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD18" s="61"/>
-      <c r="AE18" s="87"/>
-      <c r="AF18" s="24" t="e">
+        <v>0.25792954297663934</v>
+      </c>
+      <c r="AD18" s="61">
+        <v>4288.05</v>
+      </c>
+      <c r="AE18" s="135">
+        <v>3968.35</v>
+      </c>
+      <c r="AF18" s="24">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG18" s="70"/>
-      <c r="AH18" s="88"/>
-      <c r="AI18" s="28" t="e">
+        <v>-7.4556033628339277E-2</v>
+      </c>
+      <c r="AG18" s="70">
+        <v>1869.5</v>
+      </c>
+      <c r="AH18" s="136">
+        <v>1940.1</v>
+      </c>
+      <c r="AI18" s="28">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ18" s="79"/>
-      <c r="AK18" s="89"/>
-      <c r="AL18" s="37" t="e">
+        <v>3.7764108050280777E-2</v>
+      </c>
+      <c r="AJ18" s="79">
+        <v>1.0569999999999999</v>
+      </c>
+      <c r="AK18" s="137">
+        <v>1.0722</v>
+      </c>
+      <c r="AL18" s="32">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM18" s="52"/>
-      <c r="AN18" s="86"/>
-      <c r="AO18" s="20" t="e">
+        <v>1.4380321665089974E-2</v>
+      </c>
+      <c r="AM18" s="52">
+        <v>27974.5</v>
+      </c>
+      <c r="AN18" s="134">
+        <v>26927.06</v>
+      </c>
+      <c r="AO18" s="20">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AP18" s="61"/>
-      <c r="AQ18" s="87"/>
-      <c r="AR18" s="24" t="e">
+        <v>-3.7442671003949976E-2</v>
+      </c>
+      <c r="AP18" s="61">
+        <v>4288.05</v>
+      </c>
+      <c r="AQ18" s="135">
+        <v>4292.1099999999997</v>
+      </c>
+      <c r="AR18" s="24">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AS18" s="70"/>
-      <c r="AT18" s="88"/>
-      <c r="AU18" s="28" t="e">
+        <v>9.4681731789496174E-4</v>
+      </c>
+      <c r="AS18" s="70">
+        <v>1869.5</v>
+      </c>
+      <c r="AT18" s="136">
+        <v>1873.08</v>
+      </c>
+      <c r="AU18" s="28">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AV18" s="79"/>
-      <c r="AW18" s="89"/>
-      <c r="AX18" s="37" t="e">
+        <v>1.9149505215297819E-3</v>
+      </c>
+      <c r="AV18" s="79">
+        <v>1.0569999999999999</v>
+      </c>
+      <c r="AW18" s="137">
+        <v>1.0569</v>
+      </c>
+      <c r="AX18" s="32">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AY18" s="52"/>
-      <c r="AZ18" s="86"/>
-      <c r="BA18" s="20" t="e">
+        <v>-9.4607379375580888E-5</v>
+      </c>
+      <c r="AY18" s="52">
+        <v>27974.5</v>
+      </c>
+      <c r="AZ18" s="134">
+        <v>13445.56</v>
+      </c>
+      <c r="BA18" s="20">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BB18" s="61"/>
-      <c r="BC18" s="87"/>
-      <c r="BD18" s="24" t="e">
+        <v>-0.51936370623246175</v>
+      </c>
+      <c r="BB18" s="61">
+        <v>4288.05</v>
+      </c>
+      <c r="BC18" s="135">
+        <v>3873.06</v>
+      </c>
+      <c r="BD18" s="24">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BE18" s="70"/>
-      <c r="BF18" s="88"/>
-      <c r="BG18" s="28" t="e">
+        <v>-9.677825585056149E-2</v>
+      </c>
+      <c r="BE18" s="70">
+        <v>1869.5</v>
+      </c>
+      <c r="BF18" s="136">
+        <v>1866.45</v>
+      </c>
+      <c r="BG18" s="28">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BH18" s="79"/>
-      <c r="BI18" s="89"/>
-      <c r="BJ18" s="37" t="e">
+        <v>-1.6314522599625324E-3</v>
+      </c>
+      <c r="BH18" s="79">
+        <v>1.0569999999999999</v>
+      </c>
+      <c r="BI18" s="137">
+        <v>1.0299</v>
+      </c>
+      <c r="BJ18" s="37">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-2.5638599810785149E-2</v>
       </c>
     </row>
     <row r="19" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="118"/>
+      <c r="A19" s="105"/>
       <c r="B19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="53"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="20" t="e">
+      <c r="C19" s="53">
+        <v>44183.4</v>
+      </c>
+      <c r="D19" s="54">
+        <v>43445.38</v>
+      </c>
+      <c r="E19" s="20">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F19" s="62"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="24" t="e">
+        <v>-1.6703558349968631E-2</v>
+      </c>
+      <c r="F19" s="62">
+        <v>4769.83</v>
+      </c>
+      <c r="G19" s="63">
+        <v>4006.46</v>
+      </c>
+      <c r="H19" s="24">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I19" s="71"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="28" t="e">
+        <v>-0.16004134319252467</v>
+      </c>
+      <c r="I19" s="71">
+        <v>2083.5</v>
+      </c>
+      <c r="J19" s="72">
+        <v>1979.55</v>
+      </c>
+      <c r="K19" s="28">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L19" s="80"/>
-      <c r="M19" s="81"/>
-      <c r="N19" s="32" t="e">
+        <v>-4.9892008639308878E-2</v>
+      </c>
+      <c r="L19" s="80">
+        <v>1.1044</v>
+      </c>
+      <c r="M19" s="81">
+        <v>1.0721000000000001</v>
+      </c>
+      <c r="N19" s="32">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O19" s="53"/>
-      <c r="P19" s="54"/>
-      <c r="Q19" s="20" t="e">
+        <v>-2.9246649764578046E-2</v>
+      </c>
+      <c r="O19" s="53">
+        <v>44183.4</v>
+      </c>
+      <c r="P19" s="54">
+        <v>42388.9</v>
+      </c>
+      <c r="Q19" s="20">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R19" s="62"/>
-      <c r="S19" s="63"/>
-      <c r="T19" s="24" t="e">
+        <v>-4.0614801033872446E-2</v>
+      </c>
+      <c r="R19" s="62">
+        <v>4769.83</v>
+      </c>
+      <c r="S19" s="63">
+        <v>4770.22</v>
+      </c>
+      <c r="T19" s="24">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U19" s="71"/>
-      <c r="V19" s="72"/>
-      <c r="W19" s="28" t="e">
+        <v>8.1763920307500979E-5</v>
+      </c>
+      <c r="U19" s="71">
+        <v>2083.5</v>
+      </c>
+      <c r="V19" s="72">
+        <v>2083.9699999999998</v>
+      </c>
+      <c r="W19" s="28">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X19" s="80"/>
-      <c r="Y19" s="81"/>
-      <c r="Z19" s="37" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA19" s="53"/>
-      <c r="AB19" s="54"/>
-      <c r="AC19" s="20" t="e">
+        <v>2.2558195344362847E-4</v>
+      </c>
+      <c r="X19" s="80">
+        <v>1.1044</v>
+      </c>
+      <c r="Y19" s="81">
+        <v>1.1035999999999999</v>
+      </c>
+      <c r="Z19" s="32">
+        <f t="shared" si="20"/>
+        <v>-7.2437522636737946E-4</v>
+      </c>
+      <c r="AA19" s="53">
+        <v>44183.4</v>
+      </c>
+      <c r="AB19" s="54">
+        <v>44912.28</v>
+      </c>
+      <c r="AC19" s="20">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD19" s="62"/>
-      <c r="AE19" s="63"/>
-      <c r="AF19" s="24" t="e">
+        <v>1.6496693328263496E-2</v>
+      </c>
+      <c r="AD19" s="62">
+        <v>4769.83</v>
+      </c>
+      <c r="AE19" s="63">
+        <v>4012.23</v>
+      </c>
+      <c r="AF19" s="24">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG19" s="71"/>
-      <c r="AH19" s="72"/>
-      <c r="AI19" s="28" t="e">
+        <v>-0.15883165647413008</v>
+      </c>
+      <c r="AG19" s="71">
+        <v>2083.5</v>
+      </c>
+      <c r="AH19" s="72">
+        <v>1980.44</v>
+      </c>
+      <c r="AI19" s="28">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ19" s="80"/>
-      <c r="AK19" s="81"/>
-      <c r="AL19" s="37" t="e">
+        <v>-4.9464842812574968E-2</v>
+      </c>
+      <c r="AJ19" s="80">
+        <v>1.1044</v>
+      </c>
+      <c r="AK19" s="81">
+        <v>1.0726</v>
+      </c>
+      <c r="AL19" s="32">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM19" s="53"/>
-      <c r="AN19" s="54"/>
-      <c r="AO19" s="20" t="e">
+        <v>-2.8793915248098559E-2</v>
+      </c>
+      <c r="AM19" s="53">
+        <v>44183.4</v>
+      </c>
+      <c r="AN19" s="54">
+        <v>42253.35</v>
+      </c>
+      <c r="AO19" s="20">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AP19" s="62"/>
-      <c r="AQ19" s="63"/>
-      <c r="AR19" s="24" t="e">
+        <v>-4.3682695310908688E-2</v>
+      </c>
+      <c r="AP19" s="62">
+        <v>4769.83</v>
+      </c>
+      <c r="AQ19" s="63">
+        <v>4768.49</v>
+      </c>
+      <c r="AR19" s="24">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AS19" s="71"/>
-      <c r="AT19" s="72"/>
-      <c r="AU19" s="28" t="e">
+        <v>-2.8093244413325959E-4</v>
+      </c>
+      <c r="AS19" s="71">
+        <v>2083.5</v>
+      </c>
+      <c r="AT19" s="72">
+        <v>2083.83</v>
+      </c>
+      <c r="AU19" s="28">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AV19" s="80"/>
-      <c r="AW19" s="81"/>
-      <c r="AX19" s="37" t="e">
+        <v>1.5838732901364398E-4</v>
+      </c>
+      <c r="AV19" s="80">
+        <v>1.1044</v>
+      </c>
+      <c r="AW19" s="81">
+        <v>1.1032999999999999</v>
+      </c>
+      <c r="AX19" s="32">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AY19" s="53"/>
-      <c r="AZ19" s="54"/>
-      <c r="BA19" s="20" t="e">
+        <v>-9.9601593625507135E-4</v>
+      </c>
+      <c r="AY19" s="53">
+        <v>44183.4</v>
+      </c>
+      <c r="AZ19" s="54">
+        <v>12467.87</v>
+      </c>
+      <c r="BA19" s="20">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BB19" s="62"/>
-      <c r="BC19" s="63"/>
-      <c r="BD19" s="24" t="e">
+        <v>-0.71781551442396918</v>
+      </c>
+      <c r="BB19" s="62">
+        <v>4769.83</v>
+      </c>
+      <c r="BC19" s="63">
+        <v>3846.89</v>
+      </c>
+      <c r="BD19" s="24">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BE19" s="71"/>
-      <c r="BF19" s="72"/>
-      <c r="BG19" s="28" t="e">
+        <v>-0.19349536566292722</v>
+      </c>
+      <c r="BE19" s="71">
+        <v>2083.5</v>
+      </c>
+      <c r="BF19" s="72">
+        <v>1888.02</v>
+      </c>
+      <c r="BG19" s="28">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BH19" s="80"/>
-      <c r="BI19" s="81"/>
-      <c r="BJ19" s="37" t="e">
+        <v>-9.3822894168466536E-2</v>
+      </c>
+      <c r="BH19" s="80">
+        <v>1.1044</v>
+      </c>
+      <c r="BI19" s="81">
+        <v>1.0207999999999999</v>
+      </c>
+      <c r="BJ19" s="37">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-7.5697211155378585E-2</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A20" s="116" t="s">
+      <c r="A20" s="103" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="55"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="21" t="e">
+      <c r="C20" s="55">
+        <v>69664.399999999994</v>
+      </c>
+      <c r="D20" s="56">
+        <v>53807.040000000001</v>
+      </c>
+      <c r="E20" s="21">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F20" s="64"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="25" t="e">
+        <v>-0.22762501363680723</v>
+      </c>
+      <c r="F20" s="64">
+        <v>5243.77</v>
+      </c>
+      <c r="G20" s="65">
+        <v>4829.41</v>
+      </c>
+      <c r="H20" s="25">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I20" s="73"/>
-      <c r="J20" s="74"/>
-      <c r="K20" s="29" t="e">
+        <v>-7.9019484073481583E-2</v>
+      </c>
+      <c r="I20" s="73">
+        <v>2245.9</v>
+      </c>
+      <c r="J20" s="74">
+        <v>2127.46</v>
+      </c>
+      <c r="K20" s="29">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L20" s="82"/>
-      <c r="M20" s="83"/>
-      <c r="N20" s="33" t="e">
+        <v>-5.2736096887661982E-2</v>
+      </c>
+      <c r="L20" s="82">
+        <v>1.0743</v>
+      </c>
+      <c r="M20" s="83">
+        <v>1.1044</v>
+      </c>
+      <c r="N20" s="33">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O20" s="55"/>
-      <c r="P20" s="56"/>
-      <c r="Q20" s="21" t="e">
+        <v>2.8018244438238867E-2</v>
+      </c>
+      <c r="O20" s="55">
+        <v>69664.399999999994</v>
+      </c>
+      <c r="P20" s="56">
+        <v>71570.740000000005</v>
+      </c>
+      <c r="Q20" s="21">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R20" s="64"/>
-      <c r="S20" s="65"/>
-      <c r="T20" s="25" t="e">
+        <v>2.7364622389628147E-2</v>
+      </c>
+      <c r="R20" s="64">
+        <v>5243.77</v>
+      </c>
+      <c r="S20" s="65">
+        <v>5255.05</v>
+      </c>
+      <c r="T20" s="25">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U20" s="73"/>
-      <c r="V20" s="74"/>
-      <c r="W20" s="29" t="e">
+        <v>2.1511240958317669E-3</v>
+      </c>
+      <c r="U20" s="73">
+        <v>2245.9</v>
+      </c>
+      <c r="V20" s="74">
+        <v>2201.92</v>
+      </c>
+      <c r="W20" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X20" s="82"/>
-      <c r="Y20" s="83"/>
-      <c r="Z20" s="38" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA20" s="55"/>
-      <c r="AB20" s="56"/>
-      <c r="AC20" s="21" t="e">
+        <v>-1.9582350060109541E-2</v>
+      </c>
+      <c r="X20" s="82">
+        <v>1.0743</v>
+      </c>
+      <c r="Y20" s="83">
+        <v>1.0792999999999999</v>
+      </c>
+      <c r="Z20" s="33">
+        <f t="shared" si="20"/>
+        <v>4.6541934282787797E-3</v>
+      </c>
+      <c r="AA20" s="55">
+        <v>69664.399999999994</v>
+      </c>
+      <c r="AB20" s="56">
+        <v>53844.160000000003</v>
+      </c>
+      <c r="AC20" s="21">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD20" s="64"/>
-      <c r="AE20" s="65"/>
-      <c r="AF20" s="25" t="e">
+        <v>-0.22709217333386914</v>
+      </c>
+      <c r="AD20" s="64">
+        <v>5243.77</v>
+      </c>
+      <c r="AE20" s="65">
+        <v>4834.97</v>
+      </c>
+      <c r="AF20" s="25">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG20" s="73"/>
-      <c r="AH20" s="74"/>
-      <c r="AI20" s="29" t="e">
+        <v>-7.7959178224826828E-2</v>
+      </c>
+      <c r="AG20" s="73">
+        <v>2245.9</v>
+      </c>
+      <c r="AH20" s="74">
+        <v>2126.9699999999998</v>
+      </c>
+      <c r="AI20" s="29">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ20" s="82"/>
-      <c r="AK20" s="83"/>
-      <c r="AL20" s="38" t="e">
+        <v>-5.2954272229395916E-2</v>
+      </c>
+      <c r="AJ20" s="82">
+        <v>1.0743</v>
+      </c>
+      <c r="AK20" s="83">
+        <v>1.1043000000000001</v>
+      </c>
+      <c r="AL20" s="33">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM20" s="55"/>
-      <c r="AN20" s="56"/>
-      <c r="AO20" s="21" t="e">
+        <v>2.7925160569673299E-2</v>
+      </c>
+      <c r="AM20" s="55">
+        <v>69664.399999999994</v>
+      </c>
+      <c r="AN20" s="56">
+        <v>71257.13</v>
+      </c>
+      <c r="AO20" s="21">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AP20" s="64"/>
-      <c r="AQ20" s="65"/>
-      <c r="AR20" s="25" t="e">
+        <v>2.2862896974638561E-2</v>
+      </c>
+      <c r="AP20" s="64">
+        <v>5243.77</v>
+      </c>
+      <c r="AQ20" s="65">
+        <v>5252.94</v>
+      </c>
+      <c r="AR20" s="25">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AS20" s="73"/>
-      <c r="AT20" s="74"/>
-      <c r="AU20" s="29" t="e">
+        <v>1.7487418403170168E-3</v>
+      </c>
+      <c r="AS20" s="73">
+        <v>2245.9</v>
+      </c>
+      <c r="AT20" s="74">
+        <v>2202.5</v>
+      </c>
+      <c r="AU20" s="29">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AV20" s="82"/>
-      <c r="AW20" s="83"/>
-      <c r="AX20" s="38" t="e">
+        <v>-1.9324101696424636E-2</v>
+      </c>
+      <c r="AV20" s="82">
+        <v>1.0743</v>
+      </c>
+      <c r="AW20" s="83">
+        <v>1.0791999999999999</v>
+      </c>
+      <c r="AX20" s="33">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AY20" s="55"/>
-      <c r="AZ20" s="56"/>
-      <c r="BA20" s="21" t="e">
+        <v>4.5611095597132122E-3</v>
+      </c>
+      <c r="AY20" s="55">
+        <v>69664.399999999994</v>
+      </c>
+      <c r="AZ20" s="56">
+        <v>43049.69</v>
+      </c>
+      <c r="BA20" s="21">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BB20" s="64"/>
-      <c r="BC20" s="65"/>
-      <c r="BD20" s="25" t="e">
+        <v>-0.38204176021037994</v>
+      </c>
+      <c r="BB20" s="64">
+        <v>5243.77</v>
+      </c>
+      <c r="BC20" s="65">
+        <v>4808.3</v>
+      </c>
+      <c r="BD20" s="25">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BE20" s="73"/>
-      <c r="BF20" s="74"/>
-      <c r="BG20" s="29" t="e">
+        <v>-8.3045213653535566E-2</v>
+      </c>
+      <c r="BE20" s="73">
+        <v>2245.9</v>
+      </c>
+      <c r="BF20" s="74">
+        <v>2112.9299999999998</v>
+      </c>
+      <c r="BG20" s="29">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BH20" s="82"/>
-      <c r="BI20" s="83"/>
-      <c r="BJ20" s="38" t="e">
+        <v>-5.9205663653769204E-2</v>
+      </c>
+      <c r="BH20" s="82">
+        <v>1.0743</v>
+      </c>
+      <c r="BI20" s="83">
+        <v>1.0986</v>
+      </c>
+      <c r="BJ20" s="38">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>2.2619380061435341E-2</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A21" s="117"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="86"/>
-      <c r="E21" s="20" t="e">
+      <c r="C21" s="52">
+        <v>62890.1</v>
+      </c>
+      <c r="D21" s="134">
+        <v>68383.38</v>
+      </c>
+      <c r="E21" s="20">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F21" s="61"/>
-      <c r="G21" s="87"/>
-      <c r="H21" s="24" t="e">
+        <v>8.7347293135167633E-2</v>
+      </c>
+      <c r="F21" s="61">
+        <v>5475.09</v>
+      </c>
+      <c r="G21" s="135">
+        <v>4889.32</v>
+      </c>
+      <c r="H21" s="24">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I21" s="70"/>
-      <c r="J21" s="88"/>
-      <c r="K21" s="28" t="e">
+        <v>-0.1069881956278345</v>
+      </c>
+      <c r="I21" s="70">
+        <v>2338.9</v>
+      </c>
+      <c r="J21" s="136">
+        <v>2171.86</v>
+      </c>
+      <c r="K21" s="28">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L21" s="79"/>
-      <c r="M21" s="89"/>
-      <c r="N21" s="32" t="e">
+        <v>-7.1418188037111446E-2</v>
+      </c>
+      <c r="L21" s="79">
+        <v>1.0738000000000001</v>
+      </c>
+      <c r="M21" s="137">
+        <v>1.1052999999999999</v>
+      </c>
+      <c r="N21" s="32">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O21" s="52"/>
-      <c r="P21" s="86"/>
-      <c r="Q21" s="20" t="e">
+        <v>2.9335071707952933E-2</v>
+      </c>
+      <c r="O21" s="52">
+        <v>62890.1</v>
+      </c>
+      <c r="P21" s="134">
+        <v>62899.29</v>
+      </c>
+      <c r="Q21" s="20">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R21" s="61"/>
-      <c r="S21" s="87"/>
-      <c r="T21" s="24" t="e">
-        <f>(S21-R21)/R21</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U21" s="70"/>
-      <c r="V21" s="88"/>
-      <c r="W21" s="28" t="e">
+        <v>1.4612792792509995E-4</v>
+      </c>
+      <c r="R21" s="61">
+        <v>5475.09</v>
+      </c>
+      <c r="S21" s="135">
+        <v>5460.88</v>
+      </c>
+      <c r="T21" s="24">
+        <f t="shared" si="5"/>
+        <v>-2.5953911259906297E-3</v>
+      </c>
+      <c r="U21" s="70">
+        <v>2338.9</v>
+      </c>
+      <c r="V21" s="136">
+        <v>2337.15</v>
+      </c>
+      <c r="W21" s="28">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X21" s="79"/>
-      <c r="Y21" s="89"/>
-      <c r="Z21" s="37" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA21" s="52"/>
-      <c r="AB21" s="86"/>
-      <c r="AC21" s="20" t="e">
+        <v>-7.4821497285048526E-4</v>
+      </c>
+      <c r="X21" s="79">
+        <v>1.0738000000000001</v>
+      </c>
+      <c r="Y21" s="137">
+        <v>1.0712999999999999</v>
+      </c>
+      <c r="Z21" s="32">
+        <f t="shared" si="20"/>
+        <v>-2.328180294282146E-3</v>
+      </c>
+      <c r="AA21" s="52">
+        <v>62890.1</v>
+      </c>
+      <c r="AB21" s="134">
+        <v>68781.67</v>
+      </c>
+      <c r="AC21" s="20">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD21" s="61"/>
-      <c r="AE21" s="87"/>
-      <c r="AF21" s="24" t="e">
+        <v>9.3680404387972024E-2</v>
+      </c>
+      <c r="AD21" s="61">
+        <v>5475.09</v>
+      </c>
+      <c r="AE21" s="135">
+        <v>4899.67</v>
+      </c>
+      <c r="AF21" s="24">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG21" s="70"/>
-      <c r="AH21" s="88"/>
-      <c r="AI21" s="28" t="e">
+        <v>-0.10509781574366815</v>
+      </c>
+      <c r="AG21" s="70">
+        <v>2338.9</v>
+      </c>
+      <c r="AH21" s="136">
+        <v>2173.4699999999998</v>
+      </c>
+      <c r="AI21" s="28">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ21" s="79"/>
-      <c r="AK21" s="89"/>
-      <c r="AL21" s="37" t="e">
+        <v>-7.0729830262089136E-2</v>
+      </c>
+      <c r="AJ21" s="79">
+        <v>1.0738000000000001</v>
+      </c>
+      <c r="AK21" s="137">
+        <v>1.1049</v>
+      </c>
+      <c r="AL21" s="32">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM21" s="52"/>
-      <c r="AN21" s="86"/>
-      <c r="AO21" s="20" t="e">
+        <v>2.8962562860867857E-2</v>
+      </c>
+      <c r="AM21" s="52">
+        <v>62890.1</v>
+      </c>
+      <c r="AN21" s="134">
+        <v>62754.65</v>
+      </c>
+      <c r="AO21" s="20">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AP21" s="61"/>
-      <c r="AQ21" s="87"/>
-      <c r="AR21" s="24" t="e">
+        <v>-2.1537571096245209E-3</v>
+      </c>
+      <c r="AP21" s="61">
+        <v>5475.09</v>
+      </c>
+      <c r="AQ21" s="135">
+        <v>5461.32</v>
+      </c>
+      <c r="AR21" s="24">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AS21" s="70"/>
-      <c r="AT21" s="88"/>
-      <c r="AU21" s="28" t="e">
+        <v>-2.515027150238706E-3</v>
+      </c>
+      <c r="AS21" s="70">
+        <v>2338.9</v>
+      </c>
+      <c r="AT21" s="136">
+        <v>2337.16</v>
+      </c>
+      <c r="AU21" s="28">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AV21" s="79"/>
-      <c r="AW21" s="89"/>
-      <c r="AX21" s="37" t="e">
+        <v>-7.4393945872001216E-4</v>
+      </c>
+      <c r="AV21" s="79">
+        <v>1.0738000000000001</v>
+      </c>
+      <c r="AW21" s="137">
+        <v>1.0713999999999999</v>
+      </c>
+      <c r="AX21" s="32">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AY21" s="52"/>
-      <c r="AZ21" s="86"/>
-      <c r="BA21" s="20" t="e">
+        <v>-2.2350530825108769E-3</v>
+      </c>
+      <c r="AY21" s="52">
+        <v>62890.1</v>
+      </c>
+      <c r="AZ21" s="134">
+        <v>46018.02</v>
+      </c>
+      <c r="BA21" s="20">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BB21" s="61"/>
-      <c r="BC21" s="87"/>
-      <c r="BD21" s="24" t="e">
+        <v>-0.26827879109748598</v>
+      </c>
+      <c r="BB21" s="61">
+        <v>5475.09</v>
+      </c>
+      <c r="BC21" s="135">
+        <v>4926.2</v>
+      </c>
+      <c r="BD21" s="24">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BE21" s="70"/>
-      <c r="BF21" s="88"/>
-      <c r="BG21" s="28" t="e">
+        <v>-0.10025223329662167</v>
+      </c>
+      <c r="BE21" s="70">
+        <v>2338.9</v>
+      </c>
+      <c r="BF21" s="136">
+        <v>2164.02</v>
+      </c>
+      <c r="BG21" s="28">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BH21" s="79"/>
-      <c r="BI21" s="89"/>
-      <c r="BJ21" s="37" t="e">
+        <v>-7.477019111548168E-2</v>
+      </c>
+      <c r="BH21" s="79">
+        <v>1.0738000000000001</v>
+      </c>
+      <c r="BI21" s="137">
+        <v>1.0984</v>
+      </c>
+      <c r="BJ21" s="37">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>2.2909294095734729E-2</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A22" s="117"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="20" t="e">
+      <c r="C22" s="52">
+        <v>60835.5</v>
+      </c>
+      <c r="D22" s="134">
+        <v>87137.72</v>
+      </c>
+      <c r="E22" s="20">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F22" s="61"/>
-      <c r="G22" s="87"/>
-      <c r="H22" s="24" t="e">
+        <v>0.43234986151178179</v>
+      </c>
+      <c r="F22" s="61">
+        <v>5708.75</v>
+      </c>
+      <c r="G22" s="135">
+        <v>4950.6400000000003</v>
+      </c>
+      <c r="H22" s="24">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I22" s="70"/>
-      <c r="J22" s="88"/>
-      <c r="K22" s="28" t="e">
+        <v>-0.13279789796365224</v>
+      </c>
+      <c r="I22" s="70">
+        <v>2678.5</v>
+      </c>
+      <c r="J22" s="136">
+        <v>2217.69</v>
+      </c>
+      <c r="K22" s="28">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L22" s="79"/>
-      <c r="M22" s="89"/>
-      <c r="N22" s="32" t="e">
+        <v>-0.17204032107522865</v>
+      </c>
+      <c r="L22" s="79">
+        <v>1.1067</v>
+      </c>
+      <c r="M22" s="137">
+        <v>1.1061000000000001</v>
+      </c>
+      <c r="N22" s="32">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O22" s="52"/>
-      <c r="P22" s="86"/>
-      <c r="Q22" s="20" t="e">
+        <v>-5.4215234480883162E-4</v>
+      </c>
+      <c r="O22" s="52">
+        <v>60835.5</v>
+      </c>
+      <c r="P22" s="134">
+        <v>63717.07</v>
+      </c>
+      <c r="Q22" s="20">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R22" s="61"/>
-      <c r="S22" s="87"/>
-      <c r="T22" s="24" t="e">
+        <v>4.7366586943478721E-2</v>
+      </c>
+      <c r="R22" s="61">
+        <v>5708.75</v>
+      </c>
+      <c r="S22" s="135">
+        <v>5761.03</v>
+      </c>
+      <c r="T22" s="24">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U22" s="70"/>
-      <c r="V22" s="88"/>
-      <c r="W22" s="28" t="e">
+        <v>9.1578716881978977E-3</v>
+      </c>
+      <c r="U22" s="70">
+        <v>2678.5</v>
+      </c>
+      <c r="V22" s="136">
+        <v>2648.85</v>
+      </c>
+      <c r="W22" s="28">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X22" s="79"/>
-      <c r="Y22" s="89"/>
-      <c r="Z22" s="37" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA22" s="52"/>
-      <c r="AB22" s="86"/>
-      <c r="AC22" s="20" t="e">
+        <v>-1.1069628523427326E-2</v>
+      </c>
+      <c r="X22" s="79">
+        <v>1.1067</v>
+      </c>
+      <c r="Y22" s="137">
+        <v>1.1133999999999999</v>
+      </c>
+      <c r="Z22" s="32">
+        <f t="shared" si="20"/>
+        <v>6.0540345170325546E-3</v>
+      </c>
+      <c r="AA22" s="52">
+        <v>60835.5</v>
+      </c>
+      <c r="AB22" s="134">
+        <v>87709.21</v>
+      </c>
+      <c r="AC22" s="20">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD22" s="61"/>
-      <c r="AE22" s="87"/>
-      <c r="AF22" s="24" t="e">
+        <v>0.4417438830945748</v>
+      </c>
+      <c r="AD22" s="61">
+        <v>5708.75</v>
+      </c>
+      <c r="AE22" s="135">
+        <v>4960.33</v>
+      </c>
+      <c r="AF22" s="24">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG22" s="70"/>
-      <c r="AH22" s="88"/>
-      <c r="AI22" s="28" t="e">
+        <v>-0.13110050361287498</v>
+      </c>
+      <c r="AG22" s="70">
+        <v>2678.5</v>
+      </c>
+      <c r="AH22" s="136">
+        <v>2221.94</v>
+      </c>
+      <c r="AI22" s="28">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ22" s="79"/>
-      <c r="AK22" s="89"/>
-      <c r="AL22" s="37" t="e">
+        <v>-0.17045361209632254</v>
+      </c>
+      <c r="AJ22" s="79">
+        <v>1.1067</v>
+      </c>
+      <c r="AK22" s="137">
+        <v>1.1054999999999999</v>
+      </c>
+      <c r="AL22" s="32">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM22" s="52"/>
-      <c r="AN22" s="86"/>
-      <c r="AO22" s="20" t="e">
+        <v>-1.0843046896178638E-3</v>
+      </c>
+      <c r="AM22" s="52">
+        <v>60835.5</v>
+      </c>
+      <c r="AN22" s="134">
+        <v>63512.62</v>
+      </c>
+      <c r="AO22" s="20">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AP22" s="61"/>
-      <c r="AQ22" s="87"/>
-      <c r="AR22" s="24" t="e">
+        <v>4.4005884721914058E-2</v>
+      </c>
+      <c r="AP22" s="61">
+        <v>5708.75</v>
+      </c>
+      <c r="AQ22" s="135">
+        <v>5765.81</v>
+      </c>
+      <c r="AR22" s="24">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AS22" s="70"/>
-      <c r="AT22" s="88"/>
-      <c r="AU22" s="28" t="e">
+        <v>9.9951828333698974E-3</v>
+      </c>
+      <c r="AS22" s="70">
+        <v>2678.5</v>
+      </c>
+      <c r="AT22" s="136">
+        <v>2649.99</v>
+      </c>
+      <c r="AU22" s="28">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AV22" s="79"/>
-      <c r="AW22" s="89"/>
-      <c r="AX22" s="37" t="e">
+        <v>-1.0644017173791383E-2</v>
+      </c>
+      <c r="AV22" s="79">
+        <v>1.1067</v>
+      </c>
+      <c r="AW22" s="137">
+        <v>1.1136999999999999</v>
+      </c>
+      <c r="AX22" s="32">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AY22" s="52"/>
-      <c r="AZ22" s="86"/>
-      <c r="BA22" s="20" t="e">
+        <v>6.3251106894369703E-3</v>
+      </c>
+      <c r="AY22" s="52">
+        <v>60835.5</v>
+      </c>
+      <c r="AZ22" s="134">
+        <v>52969.62</v>
+      </c>
+      <c r="BA22" s="20">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BB22" s="61"/>
-      <c r="BC22" s="87"/>
-      <c r="BD22" s="24" t="e">
+        <v>-0.12929753186872792</v>
+      </c>
+      <c r="BB22" s="61">
+        <v>5708.75</v>
+      </c>
+      <c r="BC22" s="135">
+        <v>5070.21</v>
+      </c>
+      <c r="BD22" s="24">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BE22" s="70"/>
-      <c r="BF22" s="88"/>
-      <c r="BG22" s="28" t="e">
+        <v>-0.11185285745566016</v>
+      </c>
+      <c r="BE22" s="70">
+        <v>2678.5</v>
+      </c>
+      <c r="BF22" s="136">
+        <v>2256.85</v>
+      </c>
+      <c r="BG22" s="28">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BH22" s="79"/>
-      <c r="BI22" s="89"/>
-      <c r="BJ22" s="37" t="e">
+        <v>-0.15742019787194328</v>
+      </c>
+      <c r="BH22" s="79">
+        <v>1.1067</v>
+      </c>
+      <c r="BI22" s="137">
+        <v>1.1073</v>
+      </c>
+      <c r="BJ22" s="37">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>5.4215234480883162E-4</v>
       </c>
     </row>
     <row r="23" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="118"/>
+      <c r="A23" s="105"/>
       <c r="B23" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="53"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="20" t="e">
+      <c r="C23" s="53">
+        <v>94560.2</v>
+      </c>
+      <c r="D23" s="54">
+        <v>111035.48</v>
+      </c>
+      <c r="E23" s="20">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F23" s="62"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="24" t="e">
+        <v>0.17423059595897639</v>
+      </c>
+      <c r="F23" s="62">
+        <v>5881.63</v>
+      </c>
+      <c r="G23" s="63">
+        <v>5012.7299999999996</v>
+      </c>
+      <c r="H23" s="24">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I23" s="71"/>
-      <c r="J23" s="72"/>
-      <c r="K23" s="28" t="e">
+        <v>-0.14773115615909205</v>
+      </c>
+      <c r="I23" s="71">
+        <v>2618.1</v>
+      </c>
+      <c r="J23" s="72">
+        <v>2264.4899999999998</v>
+      </c>
+      <c r="K23" s="28">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L23" s="80"/>
-      <c r="M23" s="81"/>
-      <c r="N23" s="32" t="e">
+        <v>-0.13506359573736684</v>
+      </c>
+      <c r="L23" s="80">
+        <v>1.0355000000000001</v>
+      </c>
+      <c r="M23" s="81">
+        <v>1.1069</v>
+      </c>
+      <c r="N23" s="32">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O23" s="53"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="20" t="e">
+        <v>6.8952197006277069E-2</v>
+      </c>
+      <c r="O23" s="53">
+        <v>94560.2</v>
+      </c>
+      <c r="P23" s="54">
+        <v>94031.43</v>
+      </c>
+      <c r="Q23" s="20">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R23" s="62"/>
-      <c r="S23" s="63"/>
-      <c r="T23" s="24" t="e">
+        <v>-5.5918874960078774E-3</v>
+      </c>
+      <c r="R23" s="62">
+        <v>5881.63</v>
+      </c>
+      <c r="S23" s="63">
+        <v>5885.1</v>
+      </c>
+      <c r="T23" s="24">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U23" s="71"/>
-      <c r="V23" s="72"/>
-      <c r="W23" s="28" t="e">
+        <v>5.899725076212299E-4</v>
+      </c>
+      <c r="U23" s="71">
+        <v>2618.1</v>
+      </c>
+      <c r="V23" s="72">
+        <v>2618.61</v>
+      </c>
+      <c r="W23" s="28">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X23" s="80"/>
-      <c r="Y23" s="81"/>
-      <c r="Z23" s="37" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA23" s="53"/>
-      <c r="AB23" s="54"/>
-      <c r="AC23" s="20" t="e">
+        <v>1.9479775409656557E-4</v>
+      </c>
+      <c r="X23" s="80">
+        <v>1.0355000000000001</v>
+      </c>
+      <c r="Y23" s="81">
+        <v>1.0354000000000001</v>
+      </c>
+      <c r="Z23" s="32">
+        <f t="shared" si="20"/>
+        <v>-9.6571704490573619E-5</v>
+      </c>
+      <c r="AA23" s="53">
+        <v>94560.2</v>
+      </c>
+      <c r="AB23" s="54">
+        <v>113093.36</v>
+      </c>
+      <c r="AC23" s="20">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD23" s="62"/>
-      <c r="AE23" s="63"/>
-      <c r="AF23" s="24" t="e">
+        <v>0.19599324028502482</v>
+      </c>
+      <c r="AD23" s="62">
+        <v>5881.63</v>
+      </c>
+      <c r="AE23" s="63">
+        <v>5040.38</v>
+      </c>
+      <c r="AF23" s="24">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG23" s="71"/>
-      <c r="AH23" s="72"/>
-      <c r="AI23" s="28" t="e">
+        <v>-0.14303007839663495</v>
+      </c>
+      <c r="AG23" s="71">
+        <v>2618.1</v>
+      </c>
+      <c r="AH23" s="72">
+        <v>2273.2800000000002</v>
+      </c>
+      <c r="AI23" s="28">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ23" s="80"/>
-      <c r="AK23" s="81"/>
-      <c r="AL23" s="37" t="e">
+        <v>-0.13170619915205672</v>
+      </c>
+      <c r="AJ23" s="80">
+        <v>1.0355000000000001</v>
+      </c>
+      <c r="AK23" s="81">
+        <v>1.1062000000000001</v>
+      </c>
+      <c r="AL23" s="32">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM23" s="53"/>
-      <c r="AN23" s="54"/>
-      <c r="AO23" s="20" t="e">
+        <v>6.8276195074843046E-2</v>
+      </c>
+      <c r="AM23" s="53">
+        <v>94560.2</v>
+      </c>
+      <c r="AN23" s="54">
+        <v>63696.25</v>
+      </c>
+      <c r="AO23" s="20">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AP23" s="62"/>
-      <c r="AQ23" s="63"/>
-      <c r="AR23" s="24" t="e">
+        <v>-0.32639471997732661</v>
+      </c>
+      <c r="AP23" s="62">
+        <v>5881.63</v>
+      </c>
+      <c r="AQ23" s="63">
+        <v>5887.85</v>
+      </c>
+      <c r="AR23" s="24">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AS23" s="71"/>
-      <c r="AT23" s="72"/>
-      <c r="AU23" s="28" t="e">
+        <v>1.0575299704334096E-3</v>
+      </c>
+      <c r="AS23" s="71">
+        <v>2618.1</v>
+      </c>
+      <c r="AT23" s="72">
+        <v>2618.54</v>
+      </c>
+      <c r="AU23" s="28">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AV23" s="80"/>
-      <c r="AW23" s="81"/>
-      <c r="AX23" s="37" t="e">
+        <v>1.680608074558094E-4</v>
+      </c>
+      <c r="AV23" s="80">
+        <v>1.0355000000000001</v>
+      </c>
+      <c r="AW23" s="81">
+        <v>1.0357000000000001</v>
+      </c>
+      <c r="AX23" s="32">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AY23" s="53"/>
-      <c r="AZ23" s="54"/>
-      <c r="BA23" s="20" t="e">
+        <v>1.9314340898114724E-4</v>
+      </c>
+      <c r="AY23" s="53">
+        <v>94560.2</v>
+      </c>
+      <c r="AZ23" s="54">
+        <v>62812.84</v>
+      </c>
+      <c r="BA23" s="20">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BB23" s="62"/>
-      <c r="BC23" s="63"/>
-      <c r="BD23" s="24" t="e">
+        <v>-0.33573702255282878</v>
+      </c>
+      <c r="BB23" s="62">
+        <v>5881.63</v>
+      </c>
+      <c r="BC23" s="63">
+        <v>5362.26</v>
+      </c>
+      <c r="BD23" s="24">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BE23" s="71"/>
-      <c r="BF23" s="72"/>
-      <c r="BG23" s="28" t="e">
+        <v>-8.8303752531186067E-2</v>
+      </c>
+      <c r="BE23" s="71">
+        <v>2618.1</v>
+      </c>
+      <c r="BF23" s="72">
+        <v>2388.04</v>
+      </c>
+      <c r="BG23" s="28">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BH23" s="80"/>
-      <c r="BI23" s="81"/>
-      <c r="BJ23" s="37" t="e">
+        <v>-8.7872884916542507E-2</v>
+      </c>
+      <c r="BH23" s="80">
+        <v>1.0355000000000001</v>
+      </c>
+      <c r="BI23" s="81">
+        <v>1.1184000000000001</v>
+      </c>
+      <c r="BJ23" s="37">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>8.0057943022694325E-2</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A24" s="116" t="s">
+      <c r="A24" s="103" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="55"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="21" t="e">
+      <c r="C24" s="55">
+        <v>85164.2</v>
+      </c>
+      <c r="D24" s="56">
+        <v>118701.57</v>
+      </c>
+      <c r="E24" s="21">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F24" s="64"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="25" t="e">
+        <v>0.3937965717989485</v>
+      </c>
+      <c r="F24" s="64">
+        <v>5633.07</v>
+      </c>
+      <c r="G24" s="65">
+        <v>5964.96</v>
+      </c>
+      <c r="H24" s="25">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I24" s="73"/>
-      <c r="J24" s="74"/>
-      <c r="K24" s="29" t="e">
+        <v>5.8918138776901469E-2</v>
+      </c>
+      <c r="I24" s="73">
+        <v>3146</v>
+      </c>
+      <c r="J24" s="74">
+        <v>2676.51</v>
+      </c>
+      <c r="K24" s="29">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L24" s="82"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="33" t="e">
+        <v>-0.14923394787031144</v>
+      </c>
+      <c r="L24" s="82">
+        <v>1.0792999999999999</v>
+      </c>
+      <c r="M24" s="83">
+        <v>1.0354000000000001</v>
+      </c>
+      <c r="N24" s="33">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O24" s="55"/>
-      <c r="P24" s="56"/>
-      <c r="Q24" s="21" t="e">
+        <v>-4.0674511257296236E-2</v>
+      </c>
+      <c r="O24" s="55">
+        <v>85164.2</v>
+      </c>
+      <c r="P24" s="56">
+        <v>82781.820000000007</v>
+      </c>
+      <c r="Q24" s="21">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R24" s="64"/>
-      <c r="S24" s="65"/>
-      <c r="T24" s="25" t="e">
+        <v>-2.7973960889669486E-2</v>
+      </c>
+      <c r="R24" s="64">
+        <v>5633.07</v>
+      </c>
+      <c r="S24" s="65">
+        <v>5609.7</v>
+      </c>
+      <c r="T24" s="25">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U24" s="73"/>
-      <c r="V24" s="74"/>
-      <c r="W24" s="29" t="e">
+        <v>-4.148714644057307E-3</v>
+      </c>
+      <c r="U24" s="73">
+        <v>3146</v>
+      </c>
+      <c r="V24" s="74">
+        <v>3150.21</v>
+      </c>
+      <c r="W24" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X24" s="82"/>
-      <c r="Y24" s="83"/>
-      <c r="Z24" s="38" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA24" s="55"/>
-      <c r="AB24" s="56"/>
-      <c r="AC24" s="21" t="e">
+        <v>1.3382072472981679E-3</v>
+      </c>
+      <c r="X24" s="82">
+        <v>1.0792999999999999</v>
+      </c>
+      <c r="Y24" s="83">
+        <v>1.0817000000000001</v>
+      </c>
+      <c r="Z24" s="33">
+        <f t="shared" si="20"/>
+        <v>2.2236634855926805E-3</v>
+      </c>
+      <c r="AA24" s="55">
+        <v>85164.2</v>
+      </c>
+      <c r="AB24" s="56">
+        <v>118531.81</v>
+      </c>
+      <c r="AC24" s="21">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD24" s="64"/>
-      <c r="AE24" s="65"/>
-      <c r="AF24" s="25" t="e">
+        <v>0.39180324596485377</v>
+      </c>
+      <c r="AD24" s="64">
+        <v>5633.07</v>
+      </c>
+      <c r="AE24" s="65">
+        <v>5956.59</v>
+      </c>
+      <c r="AF24" s="25">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG24" s="73"/>
-      <c r="AH24" s="74"/>
-      <c r="AI24" s="29" t="e">
+        <v>5.7432270502585703E-2</v>
+      </c>
+      <c r="AG24" s="73">
+        <v>3146</v>
+      </c>
+      <c r="AH24" s="74">
+        <v>2677.36</v>
+      </c>
+      <c r="AI24" s="29">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ24" s="82"/>
-      <c r="AK24" s="83"/>
-      <c r="AL24" s="38" t="e">
+        <v>-0.14896376350921803</v>
+      </c>
+      <c r="AJ24" s="82">
+        <v>1.0792999999999999</v>
+      </c>
+      <c r="AK24" s="83">
+        <v>1.0350999999999999</v>
+      </c>
+      <c r="AL24" s="33">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM24" s="55"/>
-      <c r="AN24" s="56"/>
-      <c r="AO24" s="21" t="e">
+        <v>-4.0952469192995479E-2</v>
+      </c>
+      <c r="AM24" s="55">
+        <v>85164.2</v>
+      </c>
+      <c r="AN24" s="56">
+        <v>82653.070000000007</v>
+      </c>
+      <c r="AO24" s="21">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AP24" s="64"/>
-      <c r="AQ24" s="65"/>
-      <c r="AR24" s="25" t="e">
+        <v>-2.9485746358211433E-2</v>
+      </c>
+      <c r="AP24" s="64">
+        <v>5633.07</v>
+      </c>
+      <c r="AQ24" s="65">
+        <v>5613.96</v>
+      </c>
+      <c r="AR24" s="25">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AS24" s="73"/>
-      <c r="AT24" s="74"/>
-      <c r="AU24" s="29" t="e">
+        <v>-3.3924662750506691E-3</v>
+      </c>
+      <c r="AS24" s="73">
+        <v>3146</v>
+      </c>
+      <c r="AT24" s="74">
+        <v>3154.69</v>
+      </c>
+      <c r="AU24" s="29">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AV24" s="82"/>
-      <c r="AW24" s="83"/>
-      <c r="AX24" s="38" t="e">
+        <v>2.7622377622377797E-3</v>
+      </c>
+      <c r="AV24" s="82">
+        <v>1.0792999999999999</v>
+      </c>
+      <c r="AW24" s="83">
+        <v>1.0815999999999999</v>
+      </c>
+      <c r="AX24" s="33">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AY24" s="55"/>
-      <c r="AZ24" s="56"/>
-      <c r="BA24" s="21" t="e">
+        <v>2.1310108403594635E-3</v>
+      </c>
+      <c r="AY24" s="55">
+        <v>85164.2</v>
+      </c>
+      <c r="AZ24" s="56">
+        <v>112826.64</v>
+      </c>
+      <c r="BA24" s="21">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BB24" s="64"/>
-      <c r="BC24" s="65"/>
-      <c r="BD24" s="25" t="e">
+        <v>0.32481300828282311</v>
+      </c>
+      <c r="BB24" s="64">
+        <v>5633.07</v>
+      </c>
+      <c r="BC24" s="65">
+        <v>6201.37</v>
+      </c>
+      <c r="BD24" s="25">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BE24" s="73"/>
-      <c r="BF24" s="74"/>
-      <c r="BG24" s="29" t="e">
+        <v>0.10088637279494134</v>
+      </c>
+      <c r="BE24" s="73">
+        <v>3146</v>
+      </c>
+      <c r="BF24" s="74">
+        <v>2754.09</v>
+      </c>
+      <c r="BG24" s="29">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BH24" s="82"/>
-      <c r="BI24" s="83"/>
-      <c r="BJ24" s="38" t="e">
+        <v>-0.12457406230133498</v>
+      </c>
+      <c r="BH24" s="82">
+        <v>1.0792999999999999</v>
+      </c>
+      <c r="BI24" s="83">
+        <v>1.0331999999999999</v>
+      </c>
+      <c r="BJ24" s="38">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-4.2712869452422898E-2</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A25" s="117"/>
+      <c r="A25" s="104"/>
       <c r="B25" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="52"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="20" t="e">
+      <c r="C25" s="52">
+        <v>105694.3</v>
+      </c>
+      <c r="D25" s="134">
+        <v>150391.75</v>
+      </c>
+      <c r="E25" s="20">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F25" s="61"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="24" t="e">
+        <v>0.42289366597820316</v>
+      </c>
+      <c r="F25" s="61">
+        <v>6198.01</v>
+      </c>
+      <c r="G25" s="135">
+        <v>6048.59</v>
+      </c>
+      <c r="H25" s="24">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I25" s="70"/>
-      <c r="J25" s="88"/>
-      <c r="K25" s="28" t="e">
+        <v>-2.4107737806166828E-2</v>
+      </c>
+      <c r="I25" s="70">
+        <v>3349.8</v>
+      </c>
+      <c r="J25" s="136">
+        <v>2736.32</v>
+      </c>
+      <c r="K25" s="28">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L25" s="79"/>
-      <c r="M25" s="89"/>
-      <c r="N25" s="32" t="e">
+        <v>-0.18313929189802375</v>
+      </c>
+      <c r="L25" s="79">
+        <v>1.1807000000000001</v>
+      </c>
+      <c r="M25" s="137">
+        <v>1.0354000000000001</v>
+      </c>
+      <c r="N25" s="32">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O25" s="52"/>
-      <c r="P25" s="86"/>
-      <c r="Q25" s="20" t="e">
+        <v>-0.12306258998898956</v>
+      </c>
+      <c r="O25" s="52">
+        <v>105694.3</v>
+      </c>
+      <c r="P25" s="134">
+        <v>107303.54</v>
+      </c>
+      <c r="Q25" s="20">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R25" s="61"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="24" t="e">
+        <v>1.522541896772097E-2</v>
+      </c>
+      <c r="R25" s="61">
+        <v>6198.01</v>
+      </c>
+      <c r="S25" s="135">
+        <v>6203.02</v>
+      </c>
+      <c r="T25" s="24">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U25" s="70"/>
-      <c r="V25" s="88"/>
-      <c r="W25" s="28" t="e">
+        <v>8.0832396204591765E-4</v>
+      </c>
+      <c r="U25" s="70">
+        <v>3349.8</v>
+      </c>
+      <c r="V25" s="136">
+        <v>3308.87</v>
+      </c>
+      <c r="W25" s="28">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X25" s="79"/>
-      <c r="Y25" s="89"/>
-      <c r="Z25" s="37" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA25" s="52"/>
-      <c r="AB25" s="86"/>
-      <c r="AC25" s="20" t="e">
+        <v>-1.2218639918801209E-2</v>
+      </c>
+      <c r="X25" s="79">
+        <v>1.1807000000000001</v>
+      </c>
+      <c r="Y25" s="137">
+        <v>1.1786000000000001</v>
+      </c>
+      <c r="Z25" s="32">
+        <f t="shared" si="20"/>
+        <v>-1.7786059117472605E-3</v>
+      </c>
+      <c r="AA25" s="52">
+        <v>105694.3</v>
+      </c>
+      <c r="AB25" s="134">
+        <v>149133.73000000001</v>
+      </c>
+      <c r="AC25" s="20">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD25" s="61"/>
-      <c r="AE25" s="87"/>
-      <c r="AF25" s="24" t="e">
+        <v>0.41099122658459353</v>
+      </c>
+      <c r="AD25" s="61">
+        <v>6198.01</v>
+      </c>
+      <c r="AE25" s="135">
+        <v>6035.81</v>
+      </c>
+      <c r="AF25" s="24">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG25" s="70"/>
-      <c r="AH25" s="88"/>
-      <c r="AI25" s="28" t="e">
+        <v>-2.6169689948870655E-2</v>
+      </c>
+      <c r="AG25" s="70">
+        <v>3349.8</v>
+      </c>
+      <c r="AH25" s="136">
+        <v>2743.04</v>
+      </c>
+      <c r="AI25" s="28">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ25" s="79"/>
-      <c r="AK25" s="89"/>
-      <c r="AL25" s="37" t="e">
+        <v>-0.18113320198220795</v>
+      </c>
+      <c r="AJ25" s="79">
+        <v>1.1807000000000001</v>
+      </c>
+      <c r="AK25" s="137">
+        <v>1.0359</v>
+      </c>
+      <c r="AL25" s="32">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM25" s="52"/>
-      <c r="AN25" s="86"/>
-      <c r="AO25" s="20" t="e">
+        <v>-0.12263911239095454</v>
+      </c>
+      <c r="AM25" s="52">
+        <v>105694.3</v>
+      </c>
+      <c r="AN25" s="134">
+        <v>107476.83</v>
+      </c>
+      <c r="AO25" s="20">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AP25" s="61"/>
-      <c r="AQ25" s="87"/>
-      <c r="AR25" s="24" t="e">
+        <v>1.686495865907621E-2</v>
+      </c>
+      <c r="AP25" s="61">
+        <v>6198.01</v>
+      </c>
+      <c r="AQ25" s="135">
+        <v>6204.19</v>
+      </c>
+      <c r="AR25" s="24">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AS25" s="70"/>
-      <c r="AT25" s="88"/>
-      <c r="AU25" s="28" t="e">
+        <v>9.9709422863134803E-4</v>
+      </c>
+      <c r="AS25" s="70">
+        <v>3349.8</v>
+      </c>
+      <c r="AT25" s="136">
+        <v>3310.75</v>
+      </c>
+      <c r="AU25" s="28">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AV25" s="79"/>
-      <c r="AW25" s="89"/>
-      <c r="AX25" s="37" t="e">
+        <v>-1.1657412382828879E-2</v>
+      </c>
+      <c r="AV25" s="79">
+        <v>1.1807000000000001</v>
+      </c>
+      <c r="AW25" s="137">
+        <v>1.1788000000000001</v>
+      </c>
+      <c r="AX25" s="32">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AY25" s="52"/>
-      <c r="AZ25" s="86"/>
-      <c r="BA25" s="20" t="e">
+        <v>-1.6092148725332536E-3</v>
+      </c>
+      <c r="AY25" s="52">
+        <v>105694.3</v>
+      </c>
+      <c r="AZ25" s="134">
+        <v>131330.5</v>
+      </c>
+      <c r="BA25" s="20">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BB25" s="61"/>
-      <c r="BC25" s="87"/>
-      <c r="BD25" s="24" t="e">
+        <v>0.24255044974043063</v>
+      </c>
+      <c r="BB25" s="61">
+        <v>6198.01</v>
+      </c>
+      <c r="BC25" s="135">
+        <v>6427.06</v>
+      </c>
+      <c r="BD25" s="24">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BE25" s="70"/>
-      <c r="BF25" s="88"/>
-      <c r="BG25" s="28" t="e">
+        <v>3.6955409881558786E-2</v>
+      </c>
+      <c r="BE25" s="70">
+        <v>3349.8</v>
+      </c>
+      <c r="BF25" s="136">
+        <v>2926.5</v>
+      </c>
+      <c r="BG25" s="28">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BH25" s="79"/>
-      <c r="BI25" s="89"/>
-      <c r="BJ25" s="37" t="e">
+        <v>-0.12636575317929433</v>
+      </c>
+      <c r="BH25" s="79">
+        <v>1.1807000000000001</v>
+      </c>
+      <c r="BI25" s="137">
+        <v>1.0367999999999999</v>
+      </c>
+      <c r="BJ25" s="37">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-0.12187685271449152</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A26" s="117"/>
+      <c r="A26" s="104"/>
       <c r="B26" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="52"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="20" t="e">
+      <c r="C26" s="52">
+        <v>118576.2</v>
+      </c>
+      <c r="D26" s="134">
+        <v>191038.51</v>
+      </c>
+      <c r="E26" s="20">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F26" s="61"/>
-      <c r="G26" s="87"/>
-      <c r="H26" s="24" t="e">
+        <v>0.61110332427586656</v>
+      </c>
+      <c r="F26" s="61">
+        <v>6711.2</v>
+      </c>
+      <c r="G26" s="135">
+        <v>6134.33</v>
+      </c>
+      <c r="H26" s="24">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I26" s="70"/>
-      <c r="J26" s="88"/>
-      <c r="K26" s="28" t="e">
+        <v>-8.5956311836929297E-2</v>
+      </c>
+      <c r="I26" s="70">
+        <v>3897.5</v>
+      </c>
+      <c r="J26" s="136">
+        <v>2798.15</v>
+      </c>
+      <c r="K26" s="28">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L26" s="79"/>
-      <c r="M26" s="89"/>
-      <c r="N26" s="32" t="e">
+        <v>-0.28206542655548428</v>
+      </c>
+      <c r="L26" s="79">
+        <v>1.173</v>
+      </c>
+      <c r="M26" s="137">
+        <v>1.0355000000000001</v>
+      </c>
+      <c r="N26" s="32">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O26" s="52"/>
-      <c r="P26" s="86"/>
-      <c r="Q26" s="20" t="e">
+        <v>-0.11722080136402382</v>
+      </c>
+      <c r="O26" s="52">
+        <v>118576.2</v>
+      </c>
+      <c r="P26" s="134">
+        <v>114009.09</v>
+      </c>
+      <c r="Q26" s="20">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R26" s="61"/>
-      <c r="S26" s="87"/>
-      <c r="T26" s="24" t="e">
+        <v>-3.8516245249889947E-2</v>
+      </c>
+      <c r="R26" s="61">
+        <v>6711.2</v>
+      </c>
+      <c r="S26" s="135">
+        <v>6687.09</v>
+      </c>
+      <c r="T26" s="24">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U26" s="70"/>
-      <c r="V26" s="88"/>
-      <c r="W26" s="28" t="e">
+        <v>-3.5925020860650366E-3</v>
+      </c>
+      <c r="U26" s="70">
+        <v>3897.5</v>
+      </c>
+      <c r="V26" s="136">
+        <v>3873.16</v>
+      </c>
+      <c r="W26" s="28">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X26" s="79"/>
-      <c r="Y26" s="89"/>
-      <c r="Z26" s="37" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA26" s="52"/>
-      <c r="AB26" s="86"/>
-      <c r="AC26" s="20" t="e">
+        <v>-6.2450288646568684E-3</v>
+      </c>
+      <c r="X26" s="79">
+        <v>1.173</v>
+      </c>
+      <c r="Y26" s="137">
+        <v>1.1734</v>
+      </c>
+      <c r="Z26" s="32">
+        <f t="shared" si="20"/>
+        <v>3.410059676043955E-4</v>
+      </c>
+      <c r="AA26" s="52">
+        <v>118576.2</v>
+      </c>
+      <c r="AB26" s="134">
+        <v>188503.41</v>
+      </c>
+      <c r="AC26" s="20">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD26" s="61"/>
-      <c r="AE26" s="87"/>
-      <c r="AF26" s="24" t="e">
+        <v>0.58972382316181504</v>
+      </c>
+      <c r="AD26" s="61">
+        <v>6711.2</v>
+      </c>
+      <c r="AE26" s="135">
+        <v>6122.65</v>
+      </c>
+      <c r="AF26" s="24">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG26" s="70"/>
-      <c r="AH26" s="88"/>
-      <c r="AI26" s="28" t="e">
+        <v>-8.7696686136607485E-2</v>
+      </c>
+      <c r="AG26" s="70">
+        <v>3897.5</v>
+      </c>
+      <c r="AH26" s="136">
+        <v>2809.11</v>
+      </c>
+      <c r="AI26" s="28">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ26" s="79"/>
-      <c r="AK26" s="89"/>
-      <c r="AL26" s="37" t="e">
+        <v>-0.27925336754329694</v>
+      </c>
+      <c r="AJ26" s="79">
+        <v>1.173</v>
+      </c>
+      <c r="AK26" s="137">
+        <v>1.0370999999999999</v>
+      </c>
+      <c r="AL26" s="32">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM26" s="52"/>
-      <c r="AN26" s="86"/>
-      <c r="AO26" s="20" t="e">
+        <v>-0.11585677749360625</v>
+      </c>
+      <c r="AM26" s="52">
+        <v>118576.2</v>
+      </c>
+      <c r="AN26" s="134">
+        <v>114414.37</v>
+      </c>
+      <c r="AO26" s="20">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AP26" s="61"/>
-      <c r="AQ26" s="87"/>
-      <c r="AR26" s="24" t="e">
+        <v>-3.509835869255383E-2</v>
+      </c>
+      <c r="AP26" s="61">
+        <v>6711.2</v>
+      </c>
+      <c r="AQ26" s="135">
+        <v>6691.34</v>
+      </c>
+      <c r="AR26" s="24">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AS26" s="70"/>
-      <c r="AT26" s="88"/>
-      <c r="AU26" s="28" t="e">
+        <v>-2.9592323280485866E-3</v>
+      </c>
+      <c r="AS26" s="70">
+        <v>3897.5</v>
+      </c>
+      <c r="AT26" s="136">
+        <v>3870.65</v>
+      </c>
+      <c r="AU26" s="28">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AV26" s="79"/>
-      <c r="AW26" s="89"/>
-      <c r="AX26" s="37" t="e">
+        <v>-6.8890314304040816E-3</v>
+      </c>
+      <c r="AV26" s="79">
+        <v>1.173</v>
+      </c>
+      <c r="AW26" s="137">
+        <v>1.1735</v>
+      </c>
+      <c r="AX26" s="32">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AY26" s="52"/>
-      <c r="AZ26" s="86"/>
-      <c r="BA26" s="20" t="e">
+        <v>4.262574595054944E-4</v>
+      </c>
+      <c r="AY26" s="52">
+        <v>118576.2</v>
+      </c>
+      <c r="AZ26" s="134">
+        <v>156050.74</v>
+      </c>
+      <c r="BA26" s="20">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BB26" s="61"/>
-      <c r="BC26" s="87"/>
-      <c r="BD26" s="24" t="e">
+        <v>0.31603761969096661</v>
+      </c>
+      <c r="BB26" s="61">
+        <v>6711.2</v>
+      </c>
+      <c r="BC26" s="135">
+        <v>6690.16</v>
+      </c>
+      <c r="BD26" s="24">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BE26" s="70"/>
-      <c r="BF26" s="88"/>
-      <c r="BG26" s="28" t="e">
+        <v>-3.1350578138037853E-3</v>
+      </c>
+      <c r="BE26" s="70">
+        <v>3897.5</v>
+      </c>
+      <c r="BF26" s="136">
+        <v>3133.09</v>
+      </c>
+      <c r="BG26" s="28">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BH26" s="79"/>
-      <c r="BI26" s="89"/>
-      <c r="BJ26" s="37" t="e">
+        <v>-0.19612828736369464</v>
+      </c>
+      <c r="BH26" s="79">
+        <v>1.173</v>
+      </c>
+      <c r="BI26" s="137">
+        <v>1.0449999999999999</v>
+      </c>
+      <c r="BJ26" s="37">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-0.10912190963341868</v>
       </c>
     </row>
     <row r="27" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="118"/>
+      <c r="A27" s="105"/>
       <c r="B27" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="22" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F27" s="66"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="26" t="e">
+      <c r="C27" s="57">
+        <v>88812.1</v>
+      </c>
+      <c r="D27" s="58">
+        <v>242670.96</v>
+      </c>
+      <c r="E27" s="22">
+        <f>(D27-C27)/C27</f>
+        <v>1.732408759617214</v>
+      </c>
+      <c r="F27" s="66">
+        <v>6845.5</v>
+      </c>
+      <c r="G27" s="67">
+        <v>6221.28</v>
+      </c>
+      <c r="H27" s="26">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I27" s="75"/>
-      <c r="J27" s="76"/>
-      <c r="K27" s="30" t="e">
+        <v>-9.1186911109488025E-2</v>
+      </c>
+      <c r="I27" s="75">
+        <v>4361.55</v>
+      </c>
+      <c r="J27" s="76">
+        <v>2861.37</v>
+      </c>
+      <c r="K27" s="30">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L27" s="84"/>
-      <c r="M27" s="85"/>
-      <c r="N27" s="34" t="e">
+        <v>-0.34395570382088941</v>
+      </c>
+      <c r="L27" s="84">
+        <v>1.1746000000000001</v>
+      </c>
+      <c r="M27" s="85">
+        <v>1.0356000000000001</v>
+      </c>
+      <c r="N27" s="34">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O27" s="57"/>
-      <c r="P27" s="58"/>
-      <c r="Q27" s="22" t="e">
+        <v>-0.11833815767069641</v>
+      </c>
+      <c r="O27" s="57">
+        <v>88812.1</v>
+      </c>
+      <c r="P27" s="58">
+        <v>87723.76</v>
+      </c>
+      <c r="Q27" s="22">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R27" s="66"/>
-      <c r="S27" s="67"/>
-      <c r="T27" s="26" t="e">
+        <v>-1.225441127954424E-2</v>
+      </c>
+      <c r="R27" s="66">
+        <v>6845.5</v>
+      </c>
+      <c r="S27" s="67">
+        <v>6851</v>
+      </c>
+      <c r="T27" s="26">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U27" s="75"/>
-      <c r="V27" s="76"/>
-      <c r="W27" s="30" t="e">
+        <v>8.0344752026878974E-4</v>
+      </c>
+      <c r="U27" s="75">
+        <v>4361.55</v>
+      </c>
+      <c r="V27" s="76">
+        <v>4387.7700000000004</v>
+      </c>
+      <c r="W27" s="30">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X27" s="84"/>
-      <c r="Y27" s="85"/>
-      <c r="Z27" s="39" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA27" s="57"/>
-      <c r="AB27" s="58"/>
-      <c r="AC27" s="22" t="e">
+        <v>6.0116243078722599E-3</v>
+      </c>
+      <c r="X27" s="84">
+        <v>1.1746000000000001</v>
+      </c>
+      <c r="Y27" s="85">
+        <v>1.1746000000000001</v>
+      </c>
+      <c r="Z27" s="34">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AA27" s="57">
+        <v>88812.1</v>
+      </c>
+      <c r="AB27" s="58">
+        <v>237401.93</v>
+      </c>
+      <c r="AC27" s="22">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD27" s="66"/>
-      <c r="AE27" s="67"/>
-      <c r="AF27" s="26" t="e">
+        <v>1.6730809202800065</v>
+      </c>
+      <c r="AD27" s="66">
+        <v>6845.5</v>
+      </c>
+      <c r="AE27" s="67">
+        <v>6218.15</v>
+      </c>
+      <c r="AF27" s="26">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG27" s="75"/>
-      <c r="AH27" s="76"/>
-      <c r="AI27" s="30" t="e">
+        <v>-9.1644145789204642E-2</v>
+      </c>
+      <c r="AG27" s="75">
+        <v>4361.55</v>
+      </c>
+      <c r="AH27" s="76">
+        <v>2882.8</v>
+      </c>
+      <c r="AI27" s="30">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ27" s="84"/>
-      <c r="AK27" s="85"/>
-      <c r="AL27" s="39" t="e">
+        <v>-0.33904231293920739</v>
+      </c>
+      <c r="AJ27" s="84">
+        <v>1.1746000000000001</v>
+      </c>
+      <c r="AK27" s="85">
+        <v>1.0383</v>
+      </c>
+      <c r="AL27" s="34">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM27" s="57"/>
-      <c r="AN27" s="58"/>
-      <c r="AO27" s="22" t="e">
+        <v>-0.11603950280946712</v>
+      </c>
+      <c r="AM27" s="57">
+        <v>88812.1</v>
+      </c>
+      <c r="AN27" s="58">
+        <v>87769.46</v>
+      </c>
+      <c r="AO27" s="22">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AP27" s="66"/>
-      <c r="AQ27" s="67"/>
-      <c r="AR27" s="26" t="e">
+        <v>-1.1739841755796782E-2</v>
+      </c>
+      <c r="AP27" s="66">
+        <v>6845.5</v>
+      </c>
+      <c r="AQ27" s="67">
+        <v>6851.81</v>
+      </c>
+      <c r="AR27" s="26">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AS27" s="75"/>
-      <c r="AT27" s="76"/>
-      <c r="AU27" s="30" t="e">
+        <v>9.2177342779934269E-4</v>
+      </c>
+      <c r="AS27" s="75">
+        <v>4361.55</v>
+      </c>
+      <c r="AT27" s="76">
+        <v>4397.17</v>
+      </c>
+      <c r="AU27" s="30">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AV27" s="84"/>
-      <c r="AW27" s="85"/>
-      <c r="AX27" s="39" t="e">
+        <v>8.166821428161981E-3</v>
+      </c>
+      <c r="AV27" s="84">
+        <v>1.1746000000000001</v>
+      </c>
+      <c r="AW27" s="85">
+        <v>1.1747000000000001</v>
+      </c>
+      <c r="AX27" s="34">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AY27" s="57"/>
-      <c r="AZ27" s="58"/>
-      <c r="BA27" s="22" t="e">
+        <v>8.5135365230707457E-5</v>
+      </c>
+      <c r="AY27" s="57">
+        <v>88812.1</v>
+      </c>
+      <c r="AZ27" s="58">
+        <v>179924.52</v>
+      </c>
+      <c r="BA27" s="22">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BB27" s="66"/>
-      <c r="BC27" s="67"/>
-      <c r="BD27" s="26" t="e">
+        <v>1.0259009752049548</v>
+      </c>
+      <c r="BB27" s="66">
+        <v>6845.5</v>
+      </c>
+      <c r="BC27" s="67">
+        <v>7061</v>
+      </c>
+      <c r="BD27" s="26">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BE27" s="75"/>
-      <c r="BF27" s="76"/>
-      <c r="BG27" s="30" t="e">
+        <v>3.1480534657804399E-2</v>
+      </c>
+      <c r="BE27" s="75">
+        <v>4361.55</v>
+      </c>
+      <c r="BF27" s="76">
+        <v>3428.53</v>
+      </c>
+      <c r="BG27" s="30">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BH27" s="84"/>
-      <c r="BI27" s="85"/>
-      <c r="BJ27" s="39" t="e">
+        <v>-0.21391936352902063</v>
+      </c>
+      <c r="BH27" s="84">
+        <v>1.1746000000000001</v>
+      </c>
+      <c r="BI27" s="85">
+        <v>1.0553999999999999</v>
+      </c>
+      <c r="BJ27" s="39">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>-0.10148135535501464</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.35">
@@ -7250,141 +8241,141 @@
         <v>41</v>
       </c>
       <c r="E28" s="20" cm="1">
-        <f t="array" ref="E28">AVERAGE(ABS(E4:E15))</f>
-        <v>1.6611418247179177</v>
+        <f t="array" ref="E28">AVERAGE(ABS(E4:E27))</f>
+        <v>1.0265439941037653</v>
       </c>
       <c r="G28" t="s">
         <v>41</v>
       </c>
       <c r="H28" s="24" cm="1">
-        <f t="array" ref="H28">AVERAGE(ABS(H4:H15))</f>
-        <v>0.16562650636596546</v>
+        <f t="array" ref="H28">AVERAGE(ABS(H4:H27))</f>
+        <v>0.130167169295241</v>
       </c>
       <c r="J28" t="s">
         <v>41</v>
       </c>
       <c r="K28" s="28" cm="1">
-        <f t="array" ref="K28">AVERAGE(ABS(K4:K15))</f>
-        <v>0.10722202342334754</v>
+        <f t="array" ref="K28">AVERAGE(ABS(K4:K27))</f>
+        <v>0.11815919350437008</v>
       </c>
       <c r="M28" t="s">
         <v>41</v>
       </c>
       <c r="N28" s="35" cm="1">
-        <f t="array" ref="N28">AVERAGE(ABS(N4:N15))</f>
-        <v>5.9682965378486989E-2</v>
+        <f t="array" ref="N28">AVERAGE(ABS(N4:N27))</f>
+        <v>5.4821890430214487E-2</v>
       </c>
       <c r="P28" t="s">
         <v>41</v>
       </c>
       <c r="Q28" s="20" cm="1">
-        <f t="array" ref="Q28">AVERAGE(ABS(Q4:Q15))</f>
-        <v>2.6171126308932747E-2</v>
+        <f t="array" ref="Q28">AVERAGE(ABS(Q4:Q27))</f>
+        <v>2.3603105615269012E-2</v>
       </c>
       <c r="S28" t="s">
         <v>41</v>
       </c>
       <c r="T28" s="24" cm="1">
-        <f t="array" ref="T28">AVERAGE(ABS(T4:T15))</f>
-        <v>8.5484478771713241E-3</v>
+        <f t="array" ref="T28">AVERAGE(ABS(T4:T27))</f>
+        <v>5.3669333445252694E-3</v>
       </c>
       <c r="V28" t="s">
         <v>41</v>
       </c>
       <c r="W28" s="28" cm="1">
-        <f t="array" ref="W28">AVERAGE(ABS(W4:W15))</f>
-        <v>3.1791066851724887E-3</v>
+        <f t="array" ref="W28">AVERAGE(ABS(W4:W27))</f>
+        <v>4.0144838116363381E-3</v>
       </c>
       <c r="Y28" t="s">
         <v>41</v>
       </c>
       <c r="Z28" s="35" cm="1">
-        <f t="array" ref="Z28">AVERAGE(ABS(Z4:Z15))</f>
-        <v>1.9053262849441227E-3</v>
+        <f t="array" ref="Z28">AVERAGE(ABS(Z4:Z27))</f>
+        <v>1.7264471176856864E-3</v>
       </c>
       <c r="AB28" t="s">
         <v>41</v>
       </c>
       <c r="AC28" s="20" cm="1">
-        <f t="array" ref="AC28">AVERAGE(ABS(AC4:AC15))</f>
-        <v>1.5702437267527654</v>
+        <f t="array" ref="AC28">AVERAGE(ABS(AC4:AC27))</f>
+        <v>0.97926702621680883</v>
       </c>
       <c r="AE28" t="s">
         <v>41</v>
       </c>
       <c r="AF28" s="24" cm="1">
-        <f t="array" ref="AF28">AVERAGE(ABS(AF4:AF15))</f>
-        <v>0.1640354173885189</v>
+        <f t="array" ref="AF28">AVERAGE(ABS(AF4:AF27))</f>
+        <v>0.12912372015400433</v>
       </c>
       <c r="AH28" t="s">
         <v>41</v>
       </c>
       <c r="AI28" s="28" cm="1">
-        <f t="array" ref="AI28">AVERAGE(ABS(AI4:AI15))</f>
-        <v>0.10536782143871931</v>
+        <f t="array" ref="AI28">AVERAGE(ABS(AI4:AI27))</f>
+        <v>0.11658479721638716</v>
       </c>
       <c r="AK28" t="s">
         <v>41</v>
       </c>
       <c r="AL28" s="35" cm="1">
-        <f t="array" ref="AL28">AVERAGE(ABS(AL4:AL15))</f>
-        <v>5.8787022517720826E-2</v>
+        <f t="array" ref="AL28">AVERAGE(ABS(AL4:AL27))</f>
+        <v>5.4183547798500049E-2</v>
       </c>
       <c r="AN28" t="s">
         <v>41</v>
       </c>
       <c r="AO28" s="20" cm="1">
-        <f t="array" ref="AO28">AVERAGE(ABS(AO4:AO15))</f>
-        <v>2.4423915874920311E-2</v>
+        <f t="array" ref="AO28">AVERAGE(ABS(AO4:AO27))</f>
+        <v>3.6161156765879422E-2</v>
       </c>
       <c r="AQ28" t="s">
         <v>41</v>
       </c>
       <c r="AR28" s="24" cm="1">
-        <f t="array" ref="AR28">AVERAGE(ABS(AR4:AR15))</f>
-        <v>8.9070923434570615E-3</v>
+        <f t="array" ref="AR28">AVERAGE(ABS(AR4:AR27))</f>
+        <v>5.5213967295835919E-3</v>
       </c>
       <c r="AT28" t="s">
         <v>41</v>
       </c>
       <c r="AU28" s="28" cm="1">
-        <f t="array" ref="AU28">AVERAGE(ABS(AU4:AU15))</f>
-        <v>3.3766136751378823E-3</v>
+        <f t="array" ref="AU28">AVERAGE(ABS(AU4:AU27))</f>
+        <v>4.3725639207581333E-3</v>
       </c>
       <c r="AW28" t="s">
         <v>41</v>
       </c>
       <c r="AX28" s="35" cm="1">
-        <f t="array" ref="AX28">AVERAGE(ABS(AX4:AX15))</f>
-        <v>1.9288789392539083E-3</v>
+        <f t="array" ref="AX28">AVERAGE(ABS(AX4:AX27))</f>
+        <v>1.7571768166273812E-3</v>
       </c>
       <c r="AZ28" t="s">
         <v>41</v>
       </c>
       <c r="BA28" s="20" cm="1">
-        <f t="array" ref="BA28">AVERAGE(ABS(BA4:BA15))</f>
-        <v>0.94916744185995283</v>
+        <f t="array" ref="BA28">AVERAGE(ABS(BA4:BA27))</f>
+        <v>0.69414892117823801</v>
       </c>
       <c r="BC28" t="s">
         <v>41</v>
       </c>
       <c r="BD28" s="24" cm="1">
-        <f t="array" ref="BD28">AVERAGE(ABS(BD4:BD15))</f>
-        <v>0.16437372396588582</v>
+        <f t="array" ref="BD28">AVERAGE(ABS(BD4:BD27))</f>
+        <v>0.12555312369212876</v>
       </c>
       <c r="BF28" t="s">
         <v>41</v>
       </c>
       <c r="BG28" s="28" cm="1">
-        <f t="array" ref="BG28">AVERAGE(ABS(BG4:BG15))</f>
-        <v>0.10165541517862074</v>
+        <f t="array" ref="BG28">AVERAGE(ABS(BG4:BG27))</f>
+        <v>0.10299876208610644</v>
       </c>
       <c r="BI28" t="s">
         <v>41</v>
       </c>
       <c r="BJ28" s="35" cm="1">
-        <f t="array" ref="BJ28">AVERAGE(ABS(BJ4:BJ15))</f>
-        <v>6.2353531524908447E-2</v>
+        <f t="array" ref="BJ28">AVERAGE(ABS(BJ4:BJ27))</f>
+        <v>5.9392464248066379E-2</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.35">
@@ -7392,140 +8383,140 @@
         <v>42</v>
       </c>
       <c r="E29" s="20" cm="1">
-        <f t="array" ref="E29">MAX(ABS(E4:E15))</f>
+        <f t="array" ref="E29">MAX(ABS(E4:E27))</f>
         <v>7.6732308766186872</v>
       </c>
       <c r="G29" t="s">
         <v>42</v>
       </c>
       <c r="H29" s="24" cm="1">
-        <f t="array" ref="H29">MAX(ABS(H4:H15))</f>
+        <f t="array" ref="H29">MAX(ABS(H4:H27))</f>
         <v>0.38433799454487655</v>
       </c>
       <c r="J29" t="s">
         <v>42</v>
       </c>
       <c r="K29" s="28" cm="1">
-        <f t="array" ref="K29">MAX(ABS(K4:K15))</f>
-        <v>0.17100264486655448</v>
+        <f t="array" ref="K29">MAX(ABS(K4:K27))</f>
+        <v>0.34395570382088941</v>
       </c>
       <c r="M29" t="s">
         <v>42</v>
       </c>
       <c r="N29" s="35" cm="1">
-        <f t="array" ref="N29">MAX(ABS(N4:N15))</f>
+        <f t="array" ref="N29">MAX(ABS(N4:N27))</f>
         <v>0.16399632615573023</v>
       </c>
       <c r="P29" t="s">
         <v>42</v>
       </c>
       <c r="Q29" s="20" cm="1">
-        <f t="array" ref="Q29">MAX(ABS(Q4:Q15))</f>
+        <f t="array" ref="Q29">MAX(ABS(Q4:Q27))</f>
         <v>8.8091222531466742E-2</v>
       </c>
       <c r="S29" t="s">
         <v>42</v>
       </c>
       <c r="T29" s="24" cm="1">
-        <f t="array" ref="T29">MAX(ABS(T4:T15))</f>
+        <f t="array" ref="T29">MAX(ABS(T4:T27))</f>
         <v>4.8249342238413206E-2</v>
       </c>
       <c r="V29" t="s">
         <v>42</v>
       </c>
       <c r="W29" s="28" cm="1">
-        <f t="array" ref="W29">MAX(ABS(W4:W15))</f>
-        <v>1.1725377830215119E-2</v>
+        <f t="array" ref="W29">MAX(ABS(W4:W27))</f>
+        <v>1.9582350060109541E-2</v>
       </c>
       <c r="Y29" t="s">
         <v>42</v>
       </c>
       <c r="Z29" s="35" cm="1">
-        <f t="array" ref="Z29">MAX(ABS(Z4:Z15))</f>
-        <v>6.0207991242473445E-3</v>
+        <f t="array" ref="Z29">MAX(ABS(Z4:Z27))</f>
+        <v>6.0540345170325546E-3</v>
       </c>
       <c r="AB29" t="s">
         <v>42</v>
       </c>
       <c r="AC29" s="20" cm="1">
-        <f t="array" ref="AC29">MAX(ABS(AC4:AC15))</f>
+        <f t="array" ref="AC29">MAX(ABS(AC4:AC27))</f>
         <v>6.9922345111442734</v>
       </c>
       <c r="AE29" t="s">
         <v>42</v>
       </c>
       <c r="AF29" s="24" cm="1">
-        <f t="array" ref="AF29">MAX(ABS(AF4:AF15))</f>
+        <f t="array" ref="AF29">MAX(ABS(AF4:AF27))</f>
         <v>0.38206223749309753</v>
       </c>
       <c r="AH29" t="s">
         <v>42</v>
       </c>
       <c r="AI29" s="28" cm="1">
-        <f t="array" ref="AI29">MAX(ABS(AI4:AI15))</f>
-        <v>0.16969824477037762</v>
+        <f t="array" ref="AI29">MAX(ABS(AI4:AI27))</f>
+        <v>0.33904231293920739</v>
       </c>
       <c r="AK29" t="s">
         <v>42</v>
       </c>
       <c r="AL29" s="35" cm="1">
-        <f t="array" ref="AL29">MAX(ABS(AL4:AL15))</f>
+        <f t="array" ref="AL29">MAX(ABS(AL4:AL27))</f>
         <v>0.16226145525053581</v>
       </c>
       <c r="AN29" t="s">
         <v>42</v>
       </c>
       <c r="AO29" s="20" cm="1">
-        <f t="array" ref="AO29">MAX(ABS(AO4:AO15))</f>
-        <v>9.1288788269015125E-2</v>
+        <f t="array" ref="AO29">MAX(ABS(AO4:AO27))</f>
+        <v>0.32639471997732661</v>
       </c>
       <c r="AQ29" t="s">
         <v>42</v>
       </c>
       <c r="AR29" s="24" cm="1">
-        <f t="array" ref="AR29">MAX(ABS(AR4:AR15))</f>
+        <f t="array" ref="AR29">MAX(ABS(AR4:AR27))</f>
         <v>5.2252580449301818E-2</v>
       </c>
       <c r="AT29" t="s">
         <v>42</v>
       </c>
       <c r="AU29" s="28" cm="1">
-        <f t="array" ref="AU29">MAX(ABS(AU4:AU15))</f>
-        <v>1.2477121790513988E-2</v>
+        <f t="array" ref="AU29">MAX(ABS(AU4:AU27))</f>
+        <v>1.9324101696424636E-2</v>
       </c>
       <c r="AW29" t="s">
         <v>42</v>
       </c>
       <c r="AX29" s="35" cm="1">
-        <f t="array" ref="AX29">MAX(ABS(AX4:AX15))</f>
-        <v>5.5646779784710764E-3</v>
+        <f t="array" ref="AX29">MAX(ABS(AX4:AX27))</f>
+        <v>6.3251106894369703E-3</v>
       </c>
       <c r="AZ29" t="s">
         <v>42</v>
       </c>
       <c r="BA29" s="20" cm="1">
-        <f t="array" ref="BA29">MAX(ABS(BA4:BA15))</f>
+        <f t="array" ref="BA29">MAX(ABS(BA4:BA27))</f>
         <v>3.0942395176430946</v>
       </c>
       <c r="BC29" t="s">
         <v>42</v>
       </c>
       <c r="BD29" s="24" cm="1">
-        <f t="array" ref="BD29">MAX(ABS(BD4:BD15))</f>
+        <f t="array" ref="BD29">MAX(ABS(BD4:BD27))</f>
         <v>0.49589192385138414</v>
       </c>
       <c r="BF29" t="s">
         <v>42</v>
       </c>
       <c r="BG29" s="28" cm="1">
-        <f t="array" ref="BG29">MAX(ABS(BG4:BG15))</f>
-        <v>0.20413039767878474</v>
+        <f t="array" ref="BG29">MAX(ABS(BG4:BG27))</f>
+        <v>0.21391936352902063</v>
       </c>
       <c r="BI29" t="s">
         <v>42</v>
       </c>
       <c r="BJ29" s="35" cm="1">
-        <f t="array" ref="BJ29">MAX(ABS(BJ4:BJ15))</f>
+        <f t="array" ref="BJ29">MAX(ABS(BJ4:BJ27))</f>
         <v>0.14225941422594141</v>
       </c>
     </row>
@@ -7534,145 +8525,145 @@
         <v>43</v>
       </c>
       <c r="E30" s="20" cm="1">
-        <f t="array" ref="E30">MEDIAN(ABS(E4:E15))</f>
-        <v>0.51634870970263202</v>
+        <f t="array" ref="E30">MEDIAN(ABS(E4:E27))</f>
+        <v>0.41983749811006715</v>
       </c>
       <c r="G30" t="s">
         <v>43</v>
       </c>
       <c r="H30" s="24" cm="1">
-        <f t="array" ref="H30">MEDIAN(ABS(H4:H15))</f>
-        <v>0.10992366401344419</v>
+        <f t="array" ref="H30">MEDIAN(ABS(H4:H27))</f>
+        <v>0.1059274728571802</v>
       </c>
       <c r="J30" t="s">
         <v>43</v>
       </c>
       <c r="K30" s="28" cm="1">
-        <f t="array" ref="K30">MEDIAN(ABS(K4:K15))</f>
+        <f t="array" ref="K30">MEDIAN(ABS(K4:K27))</f>
         <v>0.11830693207104818</v>
       </c>
       <c r="M30" t="s">
         <v>43</v>
       </c>
       <c r="N30" s="35" cm="1">
-        <f t="array" ref="N30">MEDIAN(ABS(N4:N15))</f>
-        <v>5.1211303216619583E-2</v>
+        <f t="array" ref="N30">MEDIAN(ABS(N4:N27))</f>
+        <v>3.9997552868563199E-2</v>
       </c>
       <c r="P30" t="s">
         <v>43</v>
       </c>
       <c r="Q30" s="20" cm="1">
-        <f t="array" ref="Q30">MEDIAN(ABS(Q4:Q15))</f>
+        <f t="array" ref="Q30">MEDIAN(ABS(Q4:Q27))</f>
         <v>1.7710703419741569E-2</v>
       </c>
       <c r="S30" t="s">
         <v>43</v>
       </c>
       <c r="T30" s="24" cm="1">
-        <f t="array" ref="T30">MEDIAN(ABS(T4:T15))</f>
-        <v>5.4378113932103678E-3</v>
+        <f t="array" ref="T30">MEDIAN(ABS(T4:T27))</f>
+        <v>2.0949115606919092E-3</v>
       </c>
       <c r="V30" t="s">
         <v>43</v>
       </c>
       <c r="W30" s="28" cm="1">
-        <f t="array" ref="W30">MEDIAN(ABS(W4:W15))</f>
-        <v>5.8454390976198892E-4</v>
+        <f t="array" ref="W30">MEDIAN(ABS(W4:W27))</f>
+        <v>8.064907145073903E-4</v>
       </c>
       <c r="Y30" t="s">
         <v>43</v>
       </c>
       <c r="Z30" s="35" cm="1">
-        <f t="array" ref="Z30">MEDIAN(ABS(Z4:Z15))</f>
-        <v>1.2823093760877093E-3</v>
+        <f t="array" ref="Z30">MEDIAN(ABS(Z4:Z27))</f>
+        <v>9.6594817899362071E-4</v>
       </c>
       <c r="AB30" t="s">
         <v>43</v>
       </c>
       <c r="AC30" s="20" cm="1">
-        <f t="array" ref="AC30">MEDIAN(ABS(AC4:AC15))</f>
-        <v>0.51326167449697335</v>
+        <f t="array" ref="AC30">MEDIAN(ABS(AC4:AC27))</f>
+        <v>0.40139723627472368</v>
       </c>
       <c r="AE30" t="s">
         <v>43</v>
       </c>
       <c r="AF30" s="24" cm="1">
-        <f t="array" ref="AF30">MEDIAN(ABS(AF4:AF15))</f>
-        <v>0.10796255386100254</v>
+        <f t="array" ref="AF30">MEDIAN(ABS(AF4:AF27))</f>
+        <v>0.10515400358281086</v>
       </c>
       <c r="AH30" t="s">
         <v>43</v>
       </c>
       <c r="AI30" s="28" cm="1">
-        <f t="array" ref="AI30">MEDIAN(ABS(AI4:AI15))</f>
+        <f t="array" ref="AI30">MEDIAN(ABS(AI4:AI27))</f>
         <v>0.11726474127652055</v>
       </c>
       <c r="AK30" t="s">
         <v>43</v>
       </c>
       <c r="AL30" s="35" cm="1">
-        <f t="array" ref="AL30">MEDIAN(ABS(AL4:AL15))</f>
-        <v>5.0437286415175135E-2</v>
+        <f t="array" ref="AL30">MEDIAN(ABS(AL4:AL27))</f>
+        <v>4.0051606146391597E-2</v>
       </c>
       <c r="AN30" t="s">
         <v>43</v>
       </c>
       <c r="AO30" s="20" cm="1">
-        <f t="array" ref="AO30">MEDIAN(ABS(AO4:AO15))</f>
-        <v>1.534650254126837E-2</v>
+        <f t="array" ref="AO30">MEDIAN(ABS(AO4:AO27))</f>
+        <v>2.040183594553692E-2</v>
       </c>
       <c r="AQ30" t="s">
         <v>43</v>
       </c>
       <c r="AR30" s="24" cm="1">
-        <f t="array" ref="AR30">MEDIAN(ABS(AR4:AR15))</f>
-        <v>5.7222820021436173E-3</v>
+        <f t="array" ref="AR30">MEDIAN(ABS(AR4:AR27))</f>
+        <v>2.0007344745063432E-3</v>
       </c>
       <c r="AT30" t="s">
         <v>43</v>
       </c>
       <c r="AU30" s="28" cm="1">
-        <f t="array" ref="AU30">MEDIAN(ABS(AU4:AU15))</f>
-        <v>8.745224848384749E-4</v>
+        <f t="array" ref="AU30">MEDIAN(ABS(AU4:AU27))</f>
+        <v>1.71684161731505E-3</v>
       </c>
       <c r="AW30" t="s">
         <v>43</v>
       </c>
       <c r="AX30" s="35" cm="1">
-        <f t="array" ref="AX30">MEDIAN(ABS(AX4:AX15))</f>
-        <v>1.2976024608704082E-3</v>
+        <f t="array" ref="AX30">MEDIAN(ABS(AX4:AX27))</f>
+        <v>9.9561042899793317E-4</v>
       </c>
       <c r="AZ30" t="s">
         <v>43</v>
       </c>
       <c r="BA30" s="20" cm="1">
-        <f t="array" ref="BA30">MEDIAN(ABS(BA4:BA15))</f>
-        <v>0.40983941105209465</v>
+        <f t="array" ref="BA30">MEDIAN(ABS(BA4:BA27))</f>
+        <v>0.36219911585111586</v>
       </c>
       <c r="BC30" t="s">
         <v>43</v>
       </c>
       <c r="BD30" s="24" cm="1">
-        <f t="array" ref="BD30">MEDIAN(ABS(BD4:BD15))</f>
-        <v>7.2088074131250957E-2</v>
+        <f t="array" ref="BD30">MEDIAN(ABS(BD4:BD27))</f>
+        <v>8.7038114651152534E-2</v>
       </c>
       <c r="BF30" t="s">
         <v>43</v>
       </c>
       <c r="BG30" s="28" cm="1">
-        <f t="array" ref="BG30">MEDIAN(ABS(BG4:BG15))</f>
-        <v>0.10866908687211838</v>
+        <f t="array" ref="BG30">MEDIAN(ABS(BG4:BG27))</f>
+        <v>9.712213307782841E-2</v>
       </c>
       <c r="BI30" t="s">
         <v>43</v>
       </c>
       <c r="BJ30" s="35" cm="1">
-        <f t="array" ref="BJ30">MEDIAN(ABS(BJ4:BJ15))</f>
-        <v>5.501908283851055E-2</v>
+        <f t="array" ref="BJ30">MEDIAN(ABS(BJ4:BJ27))</f>
+        <v>4.4835329387642134E-2</v>
       </c>
     </row>
     <row r="37" spans="5:16" x14ac:dyDescent="0.35">
-      <c r="E37" s="90"/>
+      <c r="E37" s="86"/>
     </row>
     <row r="38" spans="5:16" x14ac:dyDescent="0.35">
       <c r="P38" t="s">
@@ -7681,28 +8672,6 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="AY1:BJ1"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AM1:AX1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="AA1:AL1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="AJ2:AL2"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="X2:Z2"/>
     <mergeCell ref="C1:N1"/>
@@ -7715,6 +8684,28 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AA1:AL1"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="AM1:AX1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="AY1:BJ1"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BH2:BJ2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7759,100 +8750,100 @@
       <c r="A2" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="90">
+      <c r="B2" s="86">
         <f>'ARIMA DATA'!E28</f>
-        <v>1.6611418247179177</v>
-      </c>
-      <c r="C2" s="90">
+        <v>1.0265439941037653</v>
+      </c>
+      <c r="C2" s="86">
         <f>'ARIMA DATA'!Q28</f>
-        <v>2.6171126308932747E-2</v>
-      </c>
-      <c r="D2" s="90">
+        <v>2.3603105615269012E-2</v>
+      </c>
+      <c r="D2" s="86">
         <f>'ARIMA DATA'!AC28</f>
-        <v>1.5702437267527654</v>
-      </c>
-      <c r="E2" s="90">
+        <v>0.97926702621680883</v>
+      </c>
+      <c r="E2" s="86">
         <f>'ARIMA DATA'!AO28</f>
-        <v>2.4423915874920311E-2</v>
-      </c>
-      <c r="F2" s="90">
+        <v>3.6161156765879422E-2</v>
+      </c>
+      <c r="F2" s="86">
         <f>'ARIMA DATA'!BA28</f>
-        <v>0.94916744185995283</v>
+        <v>0.69414892117823801</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="90">
+      <c r="B3" s="86">
         <f>'ARIMA DATA'!H28</f>
-        <v>0.16562650636596546</v>
-      </c>
-      <c r="C3" s="90">
+        <v>0.130167169295241</v>
+      </c>
+      <c r="C3" s="86">
         <f>'ARIMA DATA'!T28</f>
-        <v>8.5484478771713241E-3</v>
-      </c>
-      <c r="D3" s="90">
+        <v>5.3669333445252694E-3</v>
+      </c>
+      <c r="D3" s="86">
         <f>'ARIMA DATA'!AF28</f>
-        <v>0.1640354173885189</v>
-      </c>
-      <c r="E3" s="90">
+        <v>0.12912372015400433</v>
+      </c>
+      <c r="E3" s="86">
         <f>'ARIMA DATA'!AR28</f>
-        <v>8.9070923434570615E-3</v>
-      </c>
-      <c r="F3" s="90">
+        <v>5.5213967295835919E-3</v>
+      </c>
+      <c r="F3" s="86">
         <f>'ARIMA DATA'!BD28</f>
-        <v>0.16437372396588582</v>
+        <v>0.12555312369212876</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B4" s="90">
+      <c r="B4" s="86">
         <v>0</v>
       </c>
-      <c r="C4" s="90">
+      <c r="C4" s="86">
         <v>0</v>
       </c>
-      <c r="D4" s="90">
+      <c r="D4" s="86">
         <v>0</v>
       </c>
-      <c r="E4" s="90">
+      <c r="E4" s="86">
         <v>0</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="86">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B5" s="90">
+      <c r="B5" s="86">
         <v>0</v>
       </c>
-      <c r="C5" s="90">
+      <c r="C5" s="86">
         <v>0</v>
       </c>
-      <c r="D5" s="90">
+      <c r="D5" s="86">
         <v>0</v>
       </c>
-      <c r="E5" s="90">
+      <c r="E5" s="86">
         <v>0</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="86">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B6" s="90">
+      <c r="B6" s="86">
         <v>0</v>
       </c>
-      <c r="C6" s="90">
+      <c r="C6" s="86">
         <v>0</v>
       </c>
-      <c r="D6" s="90">
+      <c r="D6" s="86">
         <v>0</v>
       </c>
-      <c r="E6" s="90">
+      <c r="E6" s="86">
         <v>0</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="86">
         <v>0</v>
       </c>
     </row>
@@ -7860,50 +8851,50 @@
       <c r="A7" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="90">
+      <c r="B7" s="86">
         <f>'ARIMA DATA'!K28</f>
-        <v>0.10722202342334754</v>
-      </c>
-      <c r="C7" s="90">
+        <v>0.11815919350437008</v>
+      </c>
+      <c r="C7" s="86">
         <f>'ARIMA DATA'!W28</f>
-        <v>3.1791066851724887E-3</v>
-      </c>
-      <c r="D7" s="90">
+        <v>4.0144838116363381E-3</v>
+      </c>
+      <c r="D7" s="86">
         <f>'ARIMA DATA'!AI28</f>
-        <v>0.10536782143871931</v>
-      </c>
-      <c r="E7" s="90">
+        <v>0.11658479721638716</v>
+      </c>
+      <c r="E7" s="86">
         <f>'ARIMA DATA'!AU28</f>
-        <v>3.3766136751378823E-3</v>
-      </c>
-      <c r="F7" s="90">
+        <v>4.3725639207581333E-3</v>
+      </c>
+      <c r="F7" s="86">
         <f>'ARIMA DATA'!BG28</f>
-        <v>0.10165541517862074</v>
+        <v>0.10299876208610644</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="90">
+      <c r="B8" s="86">
         <f>'ARIMA DATA'!N28</f>
-        <v>5.9682965378486989E-2</v>
-      </c>
-      <c r="C8" s="90">
+        <v>5.4821890430214487E-2</v>
+      </c>
+      <c r="C8" s="86">
         <f>'ARIMA DATA'!Z28</f>
-        <v>1.9053262849441227E-3</v>
-      </c>
-      <c r="D8" s="90">
+        <v>1.7264471176856864E-3</v>
+      </c>
+      <c r="D8" s="86">
         <f>'ARIMA DATA'!AL28</f>
-        <v>5.8787022517720826E-2</v>
-      </c>
-      <c r="E8" s="90">
+        <v>5.4183547798500049E-2</v>
+      </c>
+      <c r="E8" s="86">
         <f>'ARIMA DATA'!AX28</f>
-        <v>1.9288789392539083E-3</v>
-      </c>
-      <c r="F8" s="90">
+        <v>1.7571768166273812E-3</v>
+      </c>
+      <c r="F8" s="86">
         <f>'ARIMA DATA'!BJ28</f>
-        <v>6.2353531524908447E-2</v>
+        <v>5.9392464248066379E-2</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -7930,23 +8921,23 @@
       <c r="A11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="90">
+      <c r="B11" s="86">
         <f>'ARIMA DATA'!E29</f>
         <v>7.6732308766186872</v>
       </c>
-      <c r="C11" s="90">
+      <c r="C11" s="86">
         <f>'ARIMA DATA'!Q29</f>
         <v>8.8091222531466742E-2</v>
       </c>
-      <c r="D11" s="90">
+      <c r="D11" s="86">
         <f>'ARIMA DATA'!AC29</f>
         <v>6.9922345111442734</v>
       </c>
-      <c r="E11" s="90">
+      <c r="E11" s="86">
         <f>'ARIMA DATA'!AO29</f>
-        <v>9.1288788269015125E-2</v>
-      </c>
-      <c r="F11" s="90">
+        <v>0.32639471997732661</v>
+      </c>
+      <c r="F11" s="86">
         <f>'ARIMA DATA'!BA29</f>
         <v>3.0942395176430946</v>
       </c>
@@ -7955,23 +8946,23 @@
       <c r="A12" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="90">
+      <c r="B12" s="86">
         <f>'ARIMA DATA'!H29</f>
         <v>0.38433799454487655</v>
       </c>
-      <c r="C12" s="90">
+      <c r="C12" s="86">
         <f>'ARIMA DATA'!T29</f>
         <v>4.8249342238413206E-2</v>
       </c>
-      <c r="D12" s="90">
+      <c r="D12" s="86">
         <f>'ARIMA DATA'!AF29</f>
         <v>0.38206223749309753</v>
       </c>
-      <c r="E12" s="90">
+      <c r="E12" s="86">
         <f>'ARIMA DATA'!AR29</f>
         <v>5.2252580449301818E-2</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="86">
         <f>'ARIMA DATA'!BD29</f>
         <v>0.49589192385138414</v>
       </c>
@@ -7980,48 +8971,48 @@
       <c r="A13" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="90">
+      <c r="B13" s="86">
         <f>'ARIMA DATA'!K29</f>
-        <v>0.17100264486655448</v>
-      </c>
-      <c r="C13" s="90">
+        <v>0.34395570382088941</v>
+      </c>
+      <c r="C13" s="86">
         <f>'ARIMA DATA'!W29</f>
-        <v>1.1725377830215119E-2</v>
-      </c>
-      <c r="D13" s="90">
+        <v>1.9582350060109541E-2</v>
+      </c>
+      <c r="D13" s="86">
         <f>'ARIMA DATA'!AI29</f>
-        <v>0.16969824477037762</v>
-      </c>
-      <c r="E13" s="90">
+        <v>0.33904231293920739</v>
+      </c>
+      <c r="E13" s="86">
         <f>'ARIMA DATA'!AU29</f>
-        <v>1.2477121790513988E-2</v>
-      </c>
-      <c r="F13" s="90">
+        <v>1.9324101696424636E-2</v>
+      </c>
+      <c r="F13" s="86">
         <f>'ARIMA DATA'!BG29</f>
-        <v>0.20413039767878474</v>
+        <v>0.21391936352902063</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="90">
+      <c r="B14" s="86">
         <f>'ARIMA DATA'!N29</f>
         <v>0.16399632615573023</v>
       </c>
-      <c r="C14" s="90">
+      <c r="C14" s="86">
         <f>'ARIMA DATA'!Z29</f>
-        <v>6.0207991242473445E-3</v>
-      </c>
-      <c r="D14" s="90">
+        <v>6.0540345170325546E-3</v>
+      </c>
+      <c r="D14" s="86">
         <f>'ARIMA DATA'!AL29</f>
         <v>0.16226145525053581</v>
       </c>
-      <c r="E14" s="90">
+      <c r="E14" s="86">
         <f>'ARIMA DATA'!AX29</f>
-        <v>5.5646779784710764E-3</v>
-      </c>
-      <c r="F14" s="90">
+        <v>6.3251106894369703E-3</v>
+      </c>
+      <c r="F14" s="86">
         <f>'ARIMA DATA'!BJ29</f>
         <v>0.14225941422594141</v>
       </c>
@@ -8050,100 +9041,100 @@
       <c r="A17" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="90">
+      <c r="B17" s="86">
         <f>'ARIMA DATA'!E30</f>
-        <v>0.51634870970263202</v>
-      </c>
-      <c r="C17" s="90">
+        <v>0.41983749811006715</v>
+      </c>
+      <c r="C17" s="86">
         <f>'ARIMA DATA'!Q30</f>
         <v>1.7710703419741569E-2</v>
       </c>
-      <c r="D17" s="90">
+      <c r="D17" s="86">
         <f>'ARIMA DATA'!AC30</f>
-        <v>0.51326167449697335</v>
-      </c>
-      <c r="E17" s="90">
+        <v>0.40139723627472368</v>
+      </c>
+      <c r="E17" s="86">
         <f>'ARIMA DATA'!AO30</f>
-        <v>1.534650254126837E-2</v>
-      </c>
-      <c r="F17" s="90">
+        <v>2.040183594553692E-2</v>
+      </c>
+      <c r="F17" s="86">
         <f>'ARIMA DATA'!BA30</f>
-        <v>0.40983941105209465</v>
+        <v>0.36219911585111586</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="90">
+      <c r="B18" s="86">
         <f>'ARIMA DATA'!H30</f>
-        <v>0.10992366401344419</v>
-      </c>
-      <c r="C18" s="90">
+        <v>0.1059274728571802</v>
+      </c>
+      <c r="C18" s="86">
         <f>'ARIMA DATA'!T30</f>
-        <v>5.4378113932103678E-3</v>
-      </c>
-      <c r="D18" s="90">
+        <v>2.0949115606919092E-3</v>
+      </c>
+      <c r="D18" s="86">
         <f>'ARIMA DATA'!AF30</f>
-        <v>0.10796255386100254</v>
-      </c>
-      <c r="E18" s="90">
+        <v>0.10515400358281086</v>
+      </c>
+      <c r="E18" s="86">
         <f>'ARIMA DATA'!AR30</f>
-        <v>5.7222820021436173E-3</v>
-      </c>
-      <c r="F18" s="90">
+        <v>2.0007344745063432E-3</v>
+      </c>
+      <c r="F18" s="86">
         <f>'ARIMA DATA'!BD30</f>
-        <v>7.2088074131250957E-2</v>
+        <v>8.7038114651152534E-2</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="90">
+      <c r="B19" s="86">
         <f>'ARIMA DATA'!K30</f>
         <v>0.11830693207104818</v>
       </c>
-      <c r="C19" s="90">
+      <c r="C19" s="86">
         <f>'ARIMA DATA'!W30</f>
-        <v>5.8454390976198892E-4</v>
-      </c>
-      <c r="D19" s="90">
+        <v>8.064907145073903E-4</v>
+      </c>
+      <c r="D19" s="86">
         <f>'ARIMA DATA'!AI30</f>
         <v>0.11726474127652055</v>
       </c>
-      <c r="E19" s="90">
+      <c r="E19" s="86">
         <f>'ARIMA DATA'!AU30</f>
-        <v>8.745224848384749E-4</v>
-      </c>
-      <c r="F19" s="90">
+        <v>1.71684161731505E-3</v>
+      </c>
+      <c r="F19" s="86">
         <f>'ARIMA DATA'!BG30</f>
-        <v>0.10866908687211838</v>
+        <v>9.712213307782841E-2</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="90">
+      <c r="B20" s="86">
         <f>'ARIMA DATA'!N30</f>
-        <v>5.1211303216619583E-2</v>
-      </c>
-      <c r="C20" s="90">
+        <v>3.9997552868563199E-2</v>
+      </c>
+      <c r="C20" s="86">
         <f>'ARIMA DATA'!Z30</f>
-        <v>1.2823093760877093E-3</v>
-      </c>
-      <c r="D20" s="90">
+        <v>9.6594817899362071E-4</v>
+      </c>
+      <c r="D20" s="86">
         <f>'ARIMA DATA'!AL30</f>
-        <v>5.0437286415175135E-2</v>
-      </c>
-      <c r="E20" s="90">
+        <v>4.0051606146391597E-2</v>
+      </c>
+      <c r="E20" s="86">
         <f>'ARIMA DATA'!AX30</f>
-        <v>1.2976024608704082E-3</v>
-      </c>
-      <c r="F20" s="90">
+        <v>9.9561042899793317E-4</v>
+      </c>
+      <c r="F20" s="86">
         <f>'ARIMA DATA'!BJ30</f>
-        <v>5.501908283851055E-2</v>
+        <v>4.4835329387642134E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Desktop\ANO 3\ANO 3 SEM 2\PIC\Financial-Markets-Prediction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3506A505-C5E0-4320-B997-64C9714DC4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0A0D12-495C-4BA2-B07A-92867993A59E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARIMA DATA" sheetId="1" r:id="rId1"/>
     <sheet name="ARIMA ANALYSIS" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -60,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="53">
   <si>
     <t>Tipo</t>
   </si>
@@ -180,9 +179,6 @@
   </si>
   <si>
     <t>EUR/USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h </t>
   </si>
   <si>
     <t>ABS AVG</t>
@@ -926,6 +922,135 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -948,135 +1073,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2592,16 +2588,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>179393</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>354018</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>94693</xdr:rowOff>
+      <xdr:rowOff>102629</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>417763</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>66842</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>119063</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2892,7 +2888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BJ38"/>
+  <dimension ref="A1:BJ37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
@@ -2913,192 +2909,192 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="120" t="s">
+      <c r="B1" s="102"/>
+      <c r="C1" s="95" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="123" t="s">
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
+      <c r="U1" s="99"/>
+      <c r="V1" s="99"/>
+      <c r="W1" s="99"/>
+      <c r="X1" s="99"/>
+      <c r="Y1" s="99"/>
+      <c r="Z1" s="100"/>
+      <c r="AA1" s="109" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB1" s="110"/>
+      <c r="AC1" s="110"/>
+      <c r="AD1" s="110"/>
+      <c r="AE1" s="110"/>
+      <c r="AF1" s="110"/>
+      <c r="AG1" s="110"/>
+      <c r="AH1" s="110"/>
+      <c r="AI1" s="110"/>
+      <c r="AJ1" s="110"/>
+      <c r="AK1" s="110"/>
+      <c r="AL1" s="111"/>
+      <c r="AM1" s="122" t="s">
+        <v>47</v>
+      </c>
+      <c r="AN1" s="123"/>
+      <c r="AO1" s="123"/>
+      <c r="AP1" s="123"/>
+      <c r="AQ1" s="123"/>
+      <c r="AR1" s="123"/>
+      <c r="AS1" s="123"/>
+      <c r="AT1" s="123"/>
+      <c r="AU1" s="123"/>
+      <c r="AV1" s="123"/>
+      <c r="AW1" s="123"/>
+      <c r="AX1" s="124"/>
+      <c r="AY1" s="130" t="s">
         <v>46</v>
       </c>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="125"/>
-      <c r="AA1" s="108" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB1" s="109"/>
-      <c r="AC1" s="109"/>
-      <c r="AD1" s="109"/>
-      <c r="AE1" s="109"/>
-      <c r="AF1" s="109"/>
-      <c r="AG1" s="109"/>
-      <c r="AH1" s="109"/>
-      <c r="AI1" s="109"/>
-      <c r="AJ1" s="109"/>
-      <c r="AK1" s="109"/>
-      <c r="AL1" s="110"/>
-      <c r="AM1" s="95" t="s">
-        <v>48</v>
-      </c>
-      <c r="AN1" s="96"/>
-      <c r="AO1" s="96"/>
-      <c r="AP1" s="96"/>
-      <c r="AQ1" s="96"/>
-      <c r="AR1" s="96"/>
-      <c r="AS1" s="96"/>
-      <c r="AT1" s="96"/>
-      <c r="AU1" s="96"/>
-      <c r="AV1" s="96"/>
-      <c r="AW1" s="96"/>
-      <c r="AX1" s="97"/>
-      <c r="AY1" s="87" t="s">
-        <v>47</v>
-      </c>
-      <c r="AZ1" s="88"/>
-      <c r="BA1" s="88"/>
-      <c r="BB1" s="88"/>
-      <c r="BC1" s="88"/>
-      <c r="BD1" s="88"/>
-      <c r="BE1" s="88"/>
-      <c r="BF1" s="88"/>
-      <c r="BG1" s="88"/>
-      <c r="BH1" s="88"/>
-      <c r="BI1" s="88"/>
-      <c r="BJ1" s="89"/>
+      <c r="AZ1" s="131"/>
+      <c r="BA1" s="131"/>
+      <c r="BB1" s="131"/>
+      <c r="BC1" s="131"/>
+      <c r="BD1" s="131"/>
+      <c r="BE1" s="131"/>
+      <c r="BF1" s="131"/>
+      <c r="BG1" s="131"/>
+      <c r="BH1" s="131"/>
+      <c r="BI1" s="131"/>
+      <c r="BJ1" s="132"/>
     </row>
     <row r="2" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="101" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="133" t="s">
+      <c r="B2" s="102"/>
+      <c r="C2" s="108" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="128" t="s">
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="128" t="s">
+      <c r="G2" s="104"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="103" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="129"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="128" t="s">
+      <c r="J2" s="104"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="129"/>
-      <c r="N2" s="131"/>
-      <c r="O2" s="132" t="s">
+      <c r="M2" s="104"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="107" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="117"/>
-      <c r="Q2" s="118"/>
-      <c r="R2" s="116" t="s">
+      <c r="P2" s="92"/>
+      <c r="Q2" s="93"/>
+      <c r="R2" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="117"/>
-      <c r="T2" s="118"/>
-      <c r="U2" s="116" t="s">
+      <c r="S2" s="92"/>
+      <c r="T2" s="93"/>
+      <c r="U2" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="V2" s="117"/>
-      <c r="W2" s="118"/>
-      <c r="X2" s="116" t="s">
+      <c r="V2" s="92"/>
+      <c r="W2" s="93"/>
+      <c r="X2" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="Y2" s="117"/>
-      <c r="Z2" s="119"/>
-      <c r="AA2" s="111" t="s">
+      <c r="Y2" s="92"/>
+      <c r="Z2" s="94"/>
+      <c r="AA2" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="112"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="114" t="s">
+      <c r="AB2" s="113"/>
+      <c r="AC2" s="114"/>
+      <c r="AD2" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="112"/>
-      <c r="AF2" s="113"/>
-      <c r="AG2" s="114" t="s">
+      <c r="AE2" s="113"/>
+      <c r="AF2" s="114"/>
+      <c r="AG2" s="115" t="s">
         <v>38</v>
       </c>
-      <c r="AH2" s="112"/>
-      <c r="AI2" s="113"/>
-      <c r="AJ2" s="114" t="s">
+      <c r="AH2" s="113"/>
+      <c r="AI2" s="114"/>
+      <c r="AJ2" s="115" t="s">
         <v>39</v>
       </c>
-      <c r="AK2" s="112"/>
-      <c r="AL2" s="115"/>
-      <c r="AM2" s="98" t="s">
+      <c r="AK2" s="113"/>
+      <c r="AL2" s="116"/>
+      <c r="AM2" s="125" t="s">
         <v>35</v>
       </c>
-      <c r="AN2" s="99"/>
-      <c r="AO2" s="100"/>
-      <c r="AP2" s="101" t="s">
+      <c r="AN2" s="126"/>
+      <c r="AO2" s="127"/>
+      <c r="AP2" s="128" t="s">
         <v>36</v>
       </c>
-      <c r="AQ2" s="99"/>
-      <c r="AR2" s="100"/>
-      <c r="AS2" s="101" t="s">
+      <c r="AQ2" s="126"/>
+      <c r="AR2" s="127"/>
+      <c r="AS2" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="AT2" s="99"/>
-      <c r="AU2" s="100"/>
-      <c r="AV2" s="101" t="s">
+      <c r="AT2" s="126"/>
+      <c r="AU2" s="127"/>
+      <c r="AV2" s="128" t="s">
         <v>39</v>
       </c>
-      <c r="AW2" s="99"/>
-      <c r="AX2" s="102"/>
-      <c r="AY2" s="90" t="s">
+      <c r="AW2" s="126"/>
+      <c r="AX2" s="129"/>
+      <c r="AY2" s="133" t="s">
         <v>35</v>
       </c>
-      <c r="AZ2" s="91"/>
-      <c r="BA2" s="92"/>
-      <c r="BB2" s="93" t="s">
+      <c r="AZ2" s="134"/>
+      <c r="BA2" s="135"/>
+      <c r="BB2" s="136" t="s">
         <v>36</v>
       </c>
-      <c r="BC2" s="91"/>
-      <c r="BD2" s="92"/>
-      <c r="BE2" s="93" t="s">
+      <c r="BC2" s="134"/>
+      <c r="BD2" s="135"/>
+      <c r="BE2" s="136" t="s">
         <v>38</v>
       </c>
-      <c r="BF2" s="91"/>
-      <c r="BG2" s="92"/>
-      <c r="BH2" s="93" t="s">
+      <c r="BF2" s="134"/>
+      <c r="BG2" s="135"/>
+      <c r="BH2" s="136" t="s">
         <v>39</v>
       </c>
-      <c r="BI2" s="91"/>
-      <c r="BJ2" s="94"/>
+      <c r="BI2" s="134"/>
+      <c r="BJ2" s="137"/>
     </row>
     <row r="3" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="107"/>
+      <c r="B3" s="121"/>
       <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
@@ -3281,7 +3277,7 @@
       </c>
     </row>
     <row r="4" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A4" s="103" t="s">
+      <c r="A4" s="117" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -3489,24 +3485,24 @@
       </c>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A5" s="104"/>
+      <c r="A5" s="118"/>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="52">
         <v>9229.9</v>
       </c>
-      <c r="D5" s="134">
+      <c r="D5" s="87">
         <v>13076.75</v>
       </c>
       <c r="E5" s="20">
         <f>(D5-C5)/C5</f>
         <v>0.41678133024193115</v>
       </c>
-      <c r="F5" s="135">
+      <c r="F5" s="88">
         <v>3115.9</v>
       </c>
-      <c r="G5" s="135">
+      <c r="G5" s="88">
         <v>3295.31</v>
       </c>
       <c r="H5" s="24">
@@ -3516,7 +3512,7 @@
       <c r="I5" s="70">
         <v>1779.9</v>
       </c>
-      <c r="J5" s="136">
+      <c r="J5" s="89">
         <v>1587.4</v>
       </c>
       <c r="K5" s="28">
@@ -3526,7 +3522,7 @@
       <c r="L5" s="79">
         <v>1.125</v>
       </c>
-      <c r="M5" s="137">
+      <c r="M5" s="90">
         <v>1.1234999999999999</v>
       </c>
       <c r="N5" s="32">
@@ -3536,17 +3532,17 @@
       <c r="O5" s="52">
         <v>9229.9</v>
       </c>
-      <c r="P5" s="134">
+      <c r="P5" s="87">
         <v>9152.48</v>
       </c>
       <c r="Q5" s="20">
         <f>(P5-O5)/O5</f>
         <v>-8.3879565325734925E-3</v>
       </c>
-      <c r="R5" s="135">
+      <c r="R5" s="88">
         <v>3115.9</v>
       </c>
-      <c r="S5" s="135">
+      <c r="S5" s="88">
         <v>3096</v>
       </c>
       <c r="T5" s="24">
@@ -3556,7 +3552,7 @@
       <c r="U5" s="70">
         <v>1779.9</v>
       </c>
-      <c r="V5" s="136">
+      <c r="V5" s="89">
         <v>1800.77</v>
       </c>
       <c r="W5" s="28">
@@ -3566,7 +3562,7 @@
       <c r="X5" s="79">
         <v>1.125</v>
       </c>
-      <c r="Y5" s="137">
+      <c r="Y5" s="90">
         <v>1.1231</v>
       </c>
       <c r="Z5" s="37">
@@ -3576,17 +3572,17 @@
       <c r="AA5" s="52">
         <v>9229.9</v>
       </c>
-      <c r="AB5" s="134">
+      <c r="AB5" s="87">
         <v>12768.7</v>
       </c>
       <c r="AC5" s="20">
         <f>(AB5-AA5)/AA5</f>
         <v>0.38340610407480052</v>
       </c>
-      <c r="AD5" s="135">
+      <c r="AD5" s="88">
         <v>3115.9</v>
       </c>
-      <c r="AE5" s="135">
+      <c r="AE5" s="88">
         <v>3295</v>
       </c>
       <c r="AF5" s="24">
@@ -3596,7 +3592,7 @@
       <c r="AG5" s="70">
         <v>1779.9</v>
       </c>
-      <c r="AH5" s="136">
+      <c r="AH5" s="89">
         <v>1589.24</v>
       </c>
       <c r="AI5" s="28">
@@ -3606,7 +3602,7 @@
       <c r="AJ5" s="79">
         <v>1.125</v>
       </c>
-      <c r="AK5" s="137">
+      <c r="AK5" s="90">
         <v>1.1232</v>
       </c>
       <c r="AL5" s="37">
@@ -3616,17 +3612,17 @@
       <c r="AM5" s="52">
         <v>9229.9</v>
       </c>
-      <c r="AN5" s="134">
+      <c r="AN5" s="87">
         <v>9143.9599999999991</v>
       </c>
       <c r="AO5" s="20">
         <f>(AN5-AM5)/AM5</f>
         <v>-9.3110434565922186E-3</v>
       </c>
-      <c r="AP5" s="135">
+      <c r="AP5" s="88">
         <v>3115.9</v>
       </c>
-      <c r="AQ5" s="135">
+      <c r="AQ5" s="88">
         <v>3094.3</v>
       </c>
       <c r="AR5" s="24">
@@ -3636,7 +3632,7 @@
       <c r="AS5" s="70">
         <v>1779.9</v>
       </c>
-      <c r="AT5" s="136">
+      <c r="AT5" s="89">
         <v>1801.02</v>
       </c>
       <c r="AU5" s="28">
@@ -3646,7 +3642,7 @@
       <c r="AV5" s="79">
         <v>1.125</v>
       </c>
-      <c r="AW5" s="137">
+      <c r="AW5" s="90">
         <v>1.1232</v>
       </c>
       <c r="AX5" s="37">
@@ -3656,17 +3652,17 @@
       <c r="AY5" s="52">
         <v>9229.9</v>
       </c>
-      <c r="AZ5" s="134">
+      <c r="AZ5" s="87">
         <v>7011.87</v>
       </c>
       <c r="BA5" s="20">
         <f>(AZ5-AY5)/AY5</f>
         <v>-0.24030921245083911</v>
       </c>
-      <c r="BB5" s="135">
+      <c r="BB5" s="88">
         <v>3115.9</v>
       </c>
-      <c r="BC5" s="135">
+      <c r="BC5" s="88">
         <v>3297.88</v>
       </c>
       <c r="BD5" s="24">
@@ -3676,7 +3672,7 @@
       <c r="BE5" s="70">
         <v>1779.9</v>
       </c>
-      <c r="BF5" s="136">
+      <c r="BF5" s="89">
         <v>1601.16</v>
       </c>
       <c r="BG5" s="28">
@@ -3686,7 +3682,7 @@
       <c r="BH5" s="79">
         <v>1.125</v>
       </c>
-      <c r="BI5" s="137">
+      <c r="BI5" s="90">
         <v>1.0956999999999999</v>
       </c>
       <c r="BJ5" s="37">
@@ -3695,14 +3691,14 @@
       </c>
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A6" s="104"/>
+      <c r="A6" s="118"/>
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="52">
         <v>10620.5</v>
       </c>
-      <c r="D6" s="134">
+      <c r="D6" s="87">
         <v>17613.099999999999</v>
       </c>
       <c r="E6" s="20">
@@ -3712,7 +3708,7 @@
       <c r="F6" s="61">
         <v>3380.8</v>
       </c>
-      <c r="G6" s="135">
+      <c r="G6" s="88">
         <v>3328.59</v>
       </c>
       <c r="H6" s="24">
@@ -3722,7 +3718,7 @@
       <c r="I6" s="70">
         <v>1912.3</v>
       </c>
-      <c r="J6" s="136">
+      <c r="J6" s="89">
         <v>1620.75</v>
       </c>
       <c r="K6" s="28">
@@ -3732,7 +3728,7 @@
       <c r="L6" s="79">
         <v>1.1747000000000001</v>
       </c>
-      <c r="M6" s="137">
+      <c r="M6" s="90">
         <v>1.1247</v>
       </c>
       <c r="N6" s="32">
@@ -3742,7 +3738,7 @@
       <c r="O6" s="52">
         <v>10620.5</v>
       </c>
-      <c r="P6" s="134">
+      <c r="P6" s="87">
         <v>10791.47</v>
       </c>
       <c r="Q6" s="20">
@@ -3752,7 +3748,7 @@
       <c r="R6" s="61">
         <v>3380.8</v>
       </c>
-      <c r="S6" s="135">
+      <c r="S6" s="88">
         <v>3361.39</v>
       </c>
       <c r="T6" s="24">
@@ -3762,7 +3758,7 @@
       <c r="U6" s="70">
         <v>1912.3</v>
       </c>
-      <c r="V6" s="136">
+      <c r="V6" s="89">
         <v>1892.64</v>
       </c>
       <c r="W6" s="28">
@@ -3772,7 +3768,7 @@
       <c r="X6" s="79">
         <v>1.1747000000000001</v>
       </c>
-      <c r="Y6" s="137">
+      <c r="Y6" s="90">
         <v>1.1719999999999999</v>
       </c>
       <c r="Z6" s="37">
@@ -3782,7 +3778,7 @@
       <c r="AA6" s="52">
         <v>10620.5</v>
       </c>
-      <c r="AB6" s="134">
+      <c r="AB6" s="87">
         <v>17024.11</v>
       </c>
       <c r="AC6" s="20">
@@ -3792,7 +3788,7 @@
       <c r="AD6" s="61">
         <v>3380.8</v>
       </c>
-      <c r="AE6" s="135">
+      <c r="AE6" s="88">
         <v>3327.08</v>
       </c>
       <c r="AF6" s="24">
@@ -3802,7 +3798,7 @@
       <c r="AG6" s="70">
         <v>1912.3</v>
       </c>
-      <c r="AH6" s="136">
+      <c r="AH6" s="89">
         <v>1626.89</v>
       </c>
       <c r="AI6" s="28">
@@ -3812,7 +3808,7 @@
       <c r="AJ6" s="79">
         <v>1.1747000000000001</v>
       </c>
-      <c r="AK6" s="137">
+      <c r="AK6" s="90">
         <v>1.1251</v>
       </c>
       <c r="AL6" s="37">
@@ -3822,7 +3818,7 @@
       <c r="AM6" s="52">
         <v>10620.5</v>
       </c>
-      <c r="AN6" s="134">
+      <c r="AN6" s="87">
         <v>10811.04</v>
       </c>
       <c r="AO6" s="20">
@@ -3832,7 +3828,7 @@
       <c r="AP6" s="61">
         <v>3380.8</v>
       </c>
-      <c r="AQ6" s="135">
+      <c r="AQ6" s="88">
         <v>3358.77</v>
       </c>
       <c r="AR6" s="24">
@@ -3842,7 +3838,7 @@
       <c r="AS6" s="70">
         <v>1912.3</v>
       </c>
-      <c r="AT6" s="136">
+      <c r="AT6" s="89">
         <v>1888.44</v>
       </c>
       <c r="AU6" s="28">
@@ -3852,7 +3848,7 @@
       <c r="AV6" s="79">
         <v>1.1747000000000001</v>
       </c>
-      <c r="AW6" s="137">
+      <c r="AW6" s="90">
         <v>1.1727000000000001</v>
       </c>
       <c r="AX6" s="37">
@@ -3862,7 +3858,7 @@
       <c r="AY6" s="52">
         <v>10620.5</v>
       </c>
-      <c r="AZ6" s="134">
+      <c r="AZ6" s="87">
         <v>7549.37</v>
       </c>
       <c r="BA6" s="20">
@@ -3872,7 +3868,7 @@
       <c r="BB6" s="61">
         <v>3380.8</v>
       </c>
-      <c r="BC6" s="135">
+      <c r="BC6" s="88">
         <v>3354.58</v>
       </c>
       <c r="BD6" s="24">
@@ -3882,7 +3878,7 @@
       <c r="BE6" s="70">
         <v>1912.3</v>
       </c>
-      <c r="BF6" s="136">
+      <c r="BF6" s="89">
         <v>1688.72</v>
       </c>
       <c r="BG6" s="28">
@@ -3892,7 +3888,7 @@
       <c r="BH6" s="79">
         <v>1.1747000000000001</v>
       </c>
-      <c r="BI6" s="137">
+      <c r="BI6" s="90">
         <v>1.0964</v>
       </c>
       <c r="BJ6" s="37">
@@ -3901,7 +3897,7 @@
       </c>
     </row>
     <row r="7" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="105"/>
+      <c r="A7" s="119"/>
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -4107,7 +4103,7 @@
       </c>
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="117" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -4315,24 +4311,24 @@
       </c>
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A9" s="104"/>
+      <c r="A9" s="118"/>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="52">
         <v>33543.599999999999</v>
       </c>
-      <c r="D9" s="134">
+      <c r="D9" s="87">
         <v>52360.58</v>
       </c>
       <c r="E9" s="20">
-        <f t="shared" ref="E9:E27" si="0">(D9-C9)/C9</f>
+        <f t="shared" ref="E9:E26" si="0">(D9-C9)/C9</f>
         <v>0.56097079621746038</v>
       </c>
       <c r="F9" s="61">
         <v>4319.8999999999996</v>
       </c>
-      <c r="G9" s="135">
+      <c r="G9" s="88">
         <v>3839.61</v>
       </c>
       <c r="H9" s="24">
@@ -4342,7 +4338,7 @@
       <c r="I9" s="70">
         <v>1776.8</v>
       </c>
-      <c r="J9" s="136">
+      <c r="J9" s="89">
         <v>1980.93</v>
       </c>
       <c r="K9" s="28">
@@ -4352,7 +4348,7 @@
       <c r="L9" s="79">
         <v>1.1848000000000001</v>
       </c>
-      <c r="M9" s="137">
+      <c r="M9" s="90">
         <v>1.2262999999999999</v>
       </c>
       <c r="N9" s="32">
@@ -4362,7 +4358,7 @@
       <c r="O9" s="52">
         <v>33543.599999999999</v>
       </c>
-      <c r="P9" s="134">
+      <c r="P9" s="87">
         <v>35154.36</v>
       </c>
       <c r="Q9" s="20">
@@ -4372,7 +4368,7 @@
       <c r="R9" s="61">
         <v>4319.8999999999996</v>
       </c>
-      <c r="S9" s="135">
+      <c r="S9" s="88">
         <v>4297.72</v>
       </c>
       <c r="T9" s="24">
@@ -4382,7 +4378,7 @@
       <c r="U9" s="70">
         <v>1776.8</v>
       </c>
-      <c r="V9" s="136">
+      <c r="V9" s="89">
         <v>1771.76</v>
       </c>
       <c r="W9" s="28">
@@ -4392,17 +4388,17 @@
       <c r="X9" s="79">
         <v>1.1848000000000001</v>
       </c>
-      <c r="Y9" s="137">
+      <c r="Y9" s="90">
         <v>1.1855</v>
       </c>
       <c r="Z9" s="37">
-        <f t="shared" ref="Z9:Z27" si="7">(Y9-X9)/X9</f>
+        <f t="shared" ref="Z9:Z14" si="7">(Y9-X9)/X9</f>
         <v>5.9081701552998213E-4</v>
       </c>
       <c r="AA9" s="52">
         <v>33543.599999999999</v>
       </c>
-      <c r="AB9" s="134">
+      <c r="AB9" s="87">
         <v>52320.87</v>
       </c>
       <c r="AC9" s="20">
@@ -4412,7 +4408,7 @@
       <c r="AD9" s="61">
         <v>4319.8999999999996</v>
       </c>
-      <c r="AE9" s="135">
+      <c r="AE9" s="88">
         <v>3843</v>
       </c>
       <c r="AF9" s="24">
@@ -4422,7 +4418,7 @@
       <c r="AG9" s="70">
         <v>1776.8</v>
       </c>
-      <c r="AH9" s="136">
+      <c r="AH9" s="89">
         <v>1978.43</v>
       </c>
       <c r="AI9" s="28">
@@ -4432,7 +4428,7 @@
       <c r="AJ9" s="79">
         <v>1.1848000000000001</v>
       </c>
-      <c r="AK9" s="137">
+      <c r="AK9" s="90">
         <v>1.2257</v>
       </c>
       <c r="AL9" s="37">
@@ -4442,7 +4438,7 @@
       <c r="AM9" s="52">
         <v>33543.599999999999</v>
       </c>
-      <c r="AN9" s="134">
+      <c r="AN9" s="87">
         <v>35273.660000000003</v>
       </c>
       <c r="AO9" s="20">
@@ -4452,7 +4448,7 @@
       <c r="AP9" s="61">
         <v>4319.8999999999996</v>
       </c>
-      <c r="AQ9" s="135">
+      <c r="AQ9" s="88">
         <v>4298.6099999999997</v>
       </c>
       <c r="AR9" s="24">
@@ -4462,7 +4458,7 @@
       <c r="AS9" s="70">
         <v>1776.8</v>
       </c>
-      <c r="AT9" s="136">
+      <c r="AT9" s="89">
         <v>1771.59</v>
       </c>
       <c r="AU9" s="28">
@@ -4472,7 +4468,7 @@
       <c r="AV9" s="79">
         <v>1.1848000000000001</v>
       </c>
-      <c r="AW9" s="137">
+      <c r="AW9" s="90">
         <v>1.1849000000000001</v>
       </c>
       <c r="AX9" s="37">
@@ -4482,7 +4478,7 @@
       <c r="AY9" s="52">
         <v>33543.599999999999</v>
       </c>
-      <c r="AZ9" s="134">
+      <c r="AZ9" s="87">
         <v>49554.71</v>
       </c>
       <c r="BA9" s="20">
@@ -4492,7 +4488,7 @@
       <c r="BB9" s="61">
         <v>4319.8999999999996</v>
       </c>
-      <c r="BC9" s="135">
+      <c r="BC9" s="88">
         <v>4107.6000000000004</v>
       </c>
       <c r="BD9" s="24">
@@ -4502,7 +4498,7 @@
       <c r="BE9" s="70">
         <v>1776.8</v>
       </c>
-      <c r="BF9" s="136">
+      <c r="BF9" s="89">
         <v>2064.7800000000002</v>
       </c>
       <c r="BG9" s="28">
@@ -4512,7 +4508,7 @@
       <c r="BH9" s="79">
         <v>1.1848000000000001</v>
       </c>
-      <c r="BI9" s="137">
+      <c r="BI9" s="90">
         <v>1.2362</v>
       </c>
       <c r="BJ9" s="37">
@@ -4521,14 +4517,14 @@
       </c>
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A10" s="104"/>
+      <c r="A10" s="118"/>
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="52">
         <v>48146</v>
       </c>
-      <c r="D10" s="134">
+      <c r="D10" s="87">
         <v>70857.75</v>
       </c>
       <c r="E10" s="20">
@@ -4538,7 +4534,7 @@
       <c r="F10" s="61">
         <v>4357</v>
       </c>
-      <c r="G10" s="135">
+      <c r="G10" s="88">
         <v>3883.54</v>
       </c>
       <c r="H10" s="24">
@@ -4548,7 +4544,7 @@
       <c r="I10" s="70">
         <v>1757.7</v>
       </c>
-      <c r="J10" s="136">
+      <c r="J10" s="89">
         <v>2025.77</v>
       </c>
       <c r="K10" s="28">
@@ -4558,7 +4554,7 @@
       <c r="L10" s="79">
         <v>1.1594</v>
       </c>
-      <c r="M10" s="137">
+      <c r="M10" s="90">
         <v>1.2287999999999999</v>
       </c>
       <c r="N10" s="32">
@@ -4568,7 +4564,7 @@
       <c r="O10" s="52">
         <v>48146</v>
       </c>
-      <c r="P10" s="134">
+      <c r="P10" s="87">
         <v>43904.76</v>
       </c>
       <c r="Q10" s="20">
@@ -4578,7 +4574,7 @@
       <c r="R10" s="61">
         <v>4357</v>
       </c>
-      <c r="S10" s="135">
+      <c r="S10" s="88">
         <v>4312.01</v>
       </c>
       <c r="T10" s="24">
@@ -4588,7 +4584,7 @@
       <c r="U10" s="70">
         <v>1757.7</v>
       </c>
-      <c r="V10" s="136">
+      <c r="V10" s="89">
         <v>1756.18</v>
       </c>
       <c r="W10" s="28">
@@ -4598,7 +4594,7 @@
       <c r="X10" s="79">
         <v>1.1594</v>
       </c>
-      <c r="Y10" s="137">
+      <c r="Y10" s="90">
         <v>1.1579999999999999</v>
       </c>
       <c r="Z10" s="37">
@@ -4608,7 +4604,7 @@
       <c r="AA10" s="52">
         <v>48146</v>
       </c>
-      <c r="AB10" s="134">
+      <c r="AB10" s="87">
         <v>70617.490000000005</v>
       </c>
       <c r="AC10" s="20">
@@ -4618,7 +4614,7 @@
       <c r="AD10" s="61">
         <v>4357</v>
       </c>
-      <c r="AE10" s="135">
+      <c r="AE10" s="88">
         <v>3897.21</v>
       </c>
       <c r="AF10" s="24">
@@ -4628,7 +4624,7 @@
       <c r="AG10" s="70">
         <v>1757.7</v>
       </c>
-      <c r="AH10" s="136">
+      <c r="AH10" s="89">
         <v>2020.66</v>
       </c>
       <c r="AI10" s="28">
@@ -4638,7 +4634,7 @@
       <c r="AJ10" s="79">
         <v>1.1594</v>
       </c>
-      <c r="AK10" s="137">
+      <c r="AK10" s="90">
         <v>1.2274</v>
       </c>
       <c r="AL10" s="37">
@@ -4648,7 +4644,7 @@
       <c r="AM10" s="52">
         <v>48146</v>
       </c>
-      <c r="AN10" s="134">
+      <c r="AN10" s="87">
         <v>43750.81</v>
       </c>
       <c r="AO10" s="20">
@@ -4658,7 +4654,7 @@
       <c r="AP10" s="61">
         <v>4357</v>
       </c>
-      <c r="AQ10" s="135">
+      <c r="AQ10" s="88">
         <v>4323.62</v>
       </c>
       <c r="AR10" s="24">
@@ -4668,7 +4664,7 @@
       <c r="AS10" s="70">
         <v>1757.7</v>
       </c>
-      <c r="AT10" s="136">
+      <c r="AT10" s="89">
         <v>1755.85</v>
       </c>
       <c r="AU10" s="28">
@@ -4678,7 +4674,7 @@
       <c r="AV10" s="79">
         <v>1.1594</v>
       </c>
-      <c r="AW10" s="137">
+      <c r="AW10" s="90">
         <v>1.157</v>
       </c>
       <c r="AX10" s="37">
@@ -4688,7 +4684,7 @@
       <c r="AY10" s="52">
         <v>48146</v>
       </c>
-      <c r="AZ10" s="134">
+      <c r="AZ10" s="87">
         <v>58153.93</v>
       </c>
       <c r="BA10" s="20">
@@ -4698,7 +4694,7 @@
       <c r="BB10" s="61">
         <v>4357</v>
       </c>
-      <c r="BC10" s="135">
+      <c r="BC10" s="88">
         <v>4335.79</v>
       </c>
       <c r="BD10" s="24">
@@ -4708,7 +4704,7 @@
       <c r="BE10" s="70">
         <v>1757.7</v>
       </c>
-      <c r="BF10" s="136">
+      <c r="BF10" s="89">
         <v>2116.5</v>
       </c>
       <c r="BG10" s="28">
@@ -4718,7 +4714,7 @@
       <c r="BH10" s="79">
         <v>1.1594</v>
       </c>
-      <c r="BI10" s="137">
+      <c r="BI10" s="90">
         <v>1.2437</v>
       </c>
       <c r="BJ10" s="37">
@@ -4727,7 +4723,7 @@
       </c>
     </row>
     <row r="11" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="105"/>
+      <c r="A11" s="119"/>
       <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
@@ -4933,7 +4929,7 @@
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="117" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -5141,14 +5137,14 @@
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A13" s="104"/>
+      <c r="A13" s="118"/>
       <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="52">
         <v>19262.900000000001</v>
       </c>
-      <c r="D13" s="134">
+      <c r="D13" s="87">
         <v>81272.17</v>
       </c>
       <c r="E13" s="20">
@@ -5158,7 +5154,7 @@
       <c r="F13" s="61">
         <v>3825.33</v>
       </c>
-      <c r="G13" s="135">
+      <c r="G13" s="88">
         <v>4896.72</v>
       </c>
       <c r="H13" s="24">
@@ -5168,7 +5164,7 @@
       <c r="I13" s="70">
         <v>1807.3</v>
       </c>
-      <c r="J13" s="136">
+      <c r="J13" s="89">
         <v>1907.09</v>
       </c>
       <c r="K13" s="28">
@@ -5178,7 +5174,7 @@
       <c r="L13" s="79">
         <v>1.0427999999999999</v>
       </c>
-      <c r="M13" s="137">
+      <c r="M13" s="90">
         <v>1.1393</v>
       </c>
       <c r="N13" s="32">
@@ -5188,7 +5184,7 @@
       <c r="O13" s="52">
         <v>19262.900000000001</v>
       </c>
-      <c r="P13" s="134">
+      <c r="P13" s="87">
         <v>19991.560000000001</v>
       </c>
       <c r="Q13" s="20">
@@ -5198,7 +5194,7 @@
       <c r="R13" s="61">
         <v>3825.33</v>
       </c>
-      <c r="S13" s="135">
+      <c r="S13" s="88">
         <v>3787.62</v>
       </c>
       <c r="T13" s="24">
@@ -5208,7 +5204,7 @@
       <c r="U13" s="70">
         <v>1807.3</v>
       </c>
-      <c r="V13" s="136">
+      <c r="V13" s="89">
         <v>1807.85</v>
       </c>
       <c r="W13" s="28">
@@ -5218,7 +5214,7 @@
       <c r="X13" s="79">
         <v>1.0427999999999999</v>
       </c>
-      <c r="Y13" s="137">
+      <c r="Y13" s="90">
         <v>1.0479000000000001</v>
       </c>
       <c r="Z13" s="37">
@@ -5228,7 +5224,7 @@
       <c r="AA13" s="52">
         <v>19262.900000000001</v>
       </c>
-      <c r="AB13" s="134">
+      <c r="AB13" s="87">
         <v>79741.679999999993</v>
       </c>
       <c r="AC13" s="20">
@@ -5238,7 +5234,7 @@
       <c r="AD13" s="61">
         <v>3825.33</v>
       </c>
-      <c r="AE13" s="135">
+      <c r="AE13" s="88">
         <v>4890.1000000000004</v>
       </c>
       <c r="AF13" s="24">
@@ -5248,7 +5244,7 @@
       <c r="AG13" s="70">
         <v>1807.3</v>
       </c>
-      <c r="AH13" s="136">
+      <c r="AH13" s="89">
         <v>1906.97</v>
       </c>
       <c r="AI13" s="28">
@@ -5258,7 +5254,7 @@
       <c r="AJ13" s="79">
         <v>1.0427999999999999</v>
       </c>
-      <c r="AK13" s="137">
+      <c r="AK13" s="90">
         <v>1.1384000000000001</v>
       </c>
       <c r="AL13" s="37">
@@ -5268,7 +5264,7 @@
       <c r="AM13" s="52">
         <v>19262.900000000001</v>
       </c>
-      <c r="AN13" s="134">
+      <c r="AN13" s="87">
         <v>19909.41</v>
       </c>
       <c r="AO13" s="20">
@@ -5278,7 +5274,7 @@
       <c r="AP13" s="61">
         <v>3825.33</v>
       </c>
-      <c r="AQ13" s="135">
+      <c r="AQ13" s="88">
         <v>3786.85</v>
       </c>
       <c r="AR13" s="24">
@@ -5288,7 +5284,7 @@
       <c r="AS13" s="70">
         <v>1807.3</v>
       </c>
-      <c r="AT13" s="136">
+      <c r="AT13" s="89">
         <v>1807.93</v>
       </c>
       <c r="AU13" s="28">
@@ -5298,7 +5294,7 @@
       <c r="AV13" s="79">
         <v>1.0427999999999999</v>
       </c>
-      <c r="AW13" s="137">
+      <c r="AW13" s="90">
         <v>1.0486</v>
       </c>
       <c r="AX13" s="37">
@@ -5308,7 +5304,7 @@
       <c r="AY13" s="52">
         <v>19262.900000000001</v>
       </c>
-      <c r="AZ13" s="134">
+      <c r="AZ13" s="87">
         <v>67559.95</v>
       </c>
       <c r="BA13" s="20">
@@ -5318,7 +5314,7 @@
       <c r="BB13" s="61">
         <v>3825.33</v>
       </c>
-      <c r="BC13" s="135">
+      <c r="BC13" s="88">
         <v>5243.09</v>
       </c>
       <c r="BD13" s="24">
@@ -5328,7 +5324,7 @@
       <c r="BE13" s="70">
         <v>1807.3</v>
       </c>
-      <c r="BF13" s="136">
+      <c r="BF13" s="89">
         <v>1892.46</v>
       </c>
       <c r="BG13" s="28">
@@ -5338,7 +5334,7 @@
       <c r="BH13" s="79">
         <v>1.0427999999999999</v>
       </c>
-      <c r="BI13" s="137">
+      <c r="BI13" s="90">
         <v>1.1371</v>
       </c>
       <c r="BJ13" s="37">
@@ -5347,14 +5343,14 @@
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A14" s="104"/>
+      <c r="A14" s="118"/>
       <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C14" s="52">
         <v>19311.900000000001</v>
       </c>
-      <c r="D14" s="134">
+      <c r="D14" s="87">
         <v>108232.08</v>
       </c>
       <c r="E14" s="20">
@@ -5364,7 +5360,7 @@
       <c r="F14" s="61">
         <v>3585.62</v>
       </c>
-      <c r="G14" s="135">
+      <c r="G14" s="88">
         <v>4963.71</v>
       </c>
       <c r="H14" s="24">
@@ -5374,7 +5370,7 @@
       <c r="I14" s="70">
         <v>1663.6</v>
       </c>
-      <c r="J14" s="136">
+      <c r="J14" s="89">
         <v>1948.08</v>
       </c>
       <c r="K14" s="28">
@@ -5384,7 +5380,7 @@
       <c r="L14" s="79">
         <v>0.97989999999999999</v>
       </c>
-      <c r="M14" s="137">
+      <c r="M14" s="90">
         <v>1.1406000000000001</v>
       </c>
       <c r="N14" s="32">
@@ -5394,7 +5390,7 @@
       <c r="O14" s="52">
         <v>19311.900000000001</v>
       </c>
-      <c r="P14" s="134">
+      <c r="P14" s="87">
         <v>19471.509999999998</v>
       </c>
       <c r="Q14" s="20">
@@ -5404,7 +5400,7 @@
       <c r="R14" s="61">
         <v>3585.62</v>
       </c>
-      <c r="S14" s="135">
+      <c r="S14" s="88">
         <v>3592.93</v>
       </c>
       <c r="T14" s="24">
@@ -5414,7 +5410,7 @@
       <c r="U14" s="70">
         <v>1663.6</v>
       </c>
-      <c r="V14" s="136">
+      <c r="V14" s="89">
         <v>1663.93</v>
       </c>
       <c r="W14" s="28">
@@ -5424,7 +5420,7 @@
       <c r="X14" s="79">
         <v>0.97989999999999999</v>
       </c>
-      <c r="Y14" s="137">
+      <c r="Y14" s="90">
         <v>0.98019999999999996</v>
       </c>
       <c r="Z14" s="37">
@@ -5434,7 +5430,7 @@
       <c r="AA14" s="52">
         <v>19311.900000000001</v>
       </c>
-      <c r="AB14" s="134">
+      <c r="AB14" s="87">
         <v>103914.82</v>
       </c>
       <c r="AC14" s="20">
@@ -5444,7 +5440,7 @@
       <c r="AD14" s="61">
         <v>3585.62</v>
       </c>
-      <c r="AE14" s="135">
+      <c r="AE14" s="88">
         <v>4955.55</v>
       </c>
       <c r="AF14" s="24">
@@ -5454,7 +5450,7 @@
       <c r="AG14" s="70">
         <v>1663.6</v>
       </c>
-      <c r="AH14" s="136">
+      <c r="AH14" s="89">
         <v>1945.91</v>
       </c>
       <c r="AI14" s="28">
@@ -5464,7 +5460,7 @@
       <c r="AJ14" s="79">
         <v>0.97989999999999999</v>
       </c>
-      <c r="AK14" s="137">
+      <c r="AK14" s="90">
         <v>1.1389</v>
       </c>
       <c r="AL14" s="37">
@@ -5474,7 +5470,7 @@
       <c r="AM14" s="52">
         <v>19311.900000000001</v>
       </c>
-      <c r="AN14" s="134">
+      <c r="AN14" s="87">
         <v>19388.490000000002</v>
       </c>
       <c r="AO14" s="20">
@@ -5484,7 +5480,7 @@
       <c r="AP14" s="61">
         <v>3585.62</v>
       </c>
-      <c r="AQ14" s="135">
+      <c r="AQ14" s="88">
         <v>3593.35</v>
       </c>
       <c r="AR14" s="24">
@@ -5494,7 +5490,7 @@
       <c r="AS14" s="70">
         <v>1663.6</v>
       </c>
-      <c r="AT14" s="136">
+      <c r="AT14" s="89">
         <v>1662.95</v>
       </c>
       <c r="AU14" s="28">
@@ -5504,7 +5500,7 @@
       <c r="AV14" s="79">
         <v>0.97989999999999999</v>
       </c>
-      <c r="AW14" s="137">
+      <c r="AW14" s="90">
         <v>0.9798</v>
       </c>
       <c r="AX14" s="37">
@@ -5514,7 +5510,7 @@
       <c r="AY14" s="52">
         <v>19311.900000000001</v>
       </c>
-      <c r="AZ14" s="134">
+      <c r="AZ14" s="87">
         <v>72169.69</v>
       </c>
       <c r="BA14" s="20">
@@ -5524,7 +5520,7 @@
       <c r="BB14" s="61">
         <v>3585.62</v>
       </c>
-      <c r="BC14" s="135">
+      <c r="BC14" s="88">
         <v>5363.7</v>
       </c>
       <c r="BD14" s="24">
@@ -5534,7 +5530,7 @@
       <c r="BE14" s="70">
         <v>1663.6</v>
       </c>
-      <c r="BF14" s="136">
+      <c r="BF14" s="89">
         <v>1867.68</v>
       </c>
       <c r="BG14" s="28">
@@ -5544,7 +5540,7 @@
       <c r="BH14" s="79">
         <v>0.97989999999999999</v>
       </c>
-      <c r="BI14" s="137">
+      <c r="BI14" s="90">
         <v>1.1193</v>
       </c>
       <c r="BJ14" s="37">
@@ -5553,7 +5549,7 @@
       </c>
     </row>
     <row r="15" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="105"/>
+      <c r="A15" s="119"/>
       <c r="B15" s="3" t="s">
         <v>22</v>
       </c>
@@ -5759,7 +5755,7 @@
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A16" s="103" t="s">
+      <c r="A16" s="117" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -5967,14 +5963,14 @@
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A17" s="104"/>
+      <c r="A17" s="118"/>
       <c r="B17" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="52">
         <v>30586.799999999999</v>
       </c>
-      <c r="D17" s="134">
+      <c r="D17" s="87">
         <v>26742.12</v>
       </c>
       <c r="E17" s="20">
@@ -5984,7 +5980,7 @@
       <c r="F17" s="61">
         <v>4450.38</v>
       </c>
-      <c r="G17" s="135">
+      <c r="G17" s="88">
         <v>3922.19</v>
       </c>
       <c r="H17" s="24">
@@ -5994,7 +5990,7 @@
       <c r="I17" s="70">
         <v>1917.9</v>
       </c>
-      <c r="J17" s="136">
+      <c r="J17" s="89">
         <v>1900.8</v>
       </c>
       <c r="K17" s="28">
@@ -6004,7 +6000,7 @@
       <c r="L17" s="79">
         <v>1.091</v>
       </c>
-      <c r="M17" s="137">
+      <c r="M17" s="90">
         <v>1.0711999999999999</v>
       </c>
       <c r="N17" s="32">
@@ -6014,7 +6010,7 @@
       <c r="O17" s="52">
         <v>30586.799999999999</v>
       </c>
-      <c r="P17" s="134">
+      <c r="P17" s="87">
         <v>30549.919999999998</v>
       </c>
       <c r="Q17" s="20">
@@ -6024,7 +6020,7 @@
       <c r="R17" s="61">
         <v>4450.38</v>
       </c>
-      <c r="S17" s="135">
+      <c r="S17" s="88">
         <v>4445.8900000000003</v>
       </c>
       <c r="T17" s="24">
@@ -6034,7 +6030,7 @@
       <c r="U17" s="70">
         <v>1917.9</v>
       </c>
-      <c r="V17" s="136">
+      <c r="V17" s="89">
         <v>1918.35</v>
       </c>
       <c r="W17" s="28">
@@ -6044,7 +6040,7 @@
       <c r="X17" s="79">
         <v>1.091</v>
       </c>
-      <c r="Y17" s="137">
+      <c r="Y17" s="90">
         <v>1.0908</v>
       </c>
       <c r="Z17" s="32">
@@ -6054,7 +6050,7 @@
       <c r="AA17" s="52">
         <v>30586.799999999999</v>
       </c>
-      <c r="AB17" s="134">
+      <c r="AB17" s="87">
         <v>27310.98</v>
       </c>
       <c r="AC17" s="20">
@@ -6064,7 +6060,7 @@
       <c r="AD17" s="61">
         <v>4450.38</v>
       </c>
-      <c r="AE17" s="135">
+      <c r="AE17" s="88">
         <v>3917.3</v>
       </c>
       <c r="AF17" s="24">
@@ -6074,7 +6070,7 @@
       <c r="AG17" s="70">
         <v>1917.9</v>
       </c>
-      <c r="AH17" s="136">
+      <c r="AH17" s="89">
         <v>1901.01</v>
       </c>
       <c r="AI17" s="28">
@@ -6084,7 +6080,7 @@
       <c r="AJ17" s="79">
         <v>1.091</v>
       </c>
-      <c r="AK17" s="137">
+      <c r="AK17" s="90">
         <v>1.0712999999999999</v>
       </c>
       <c r="AL17" s="32">
@@ -6094,7 +6090,7 @@
       <c r="AM17" s="52">
         <v>30586.799999999999</v>
       </c>
-      <c r="AN17" s="134">
+      <c r="AN17" s="87">
         <v>30468.25</v>
       </c>
       <c r="AO17" s="20">
@@ -6104,7 +6100,7 @@
       <c r="AP17" s="61">
         <v>4450.38</v>
       </c>
-      <c r="AQ17" s="135">
+      <c r="AQ17" s="88">
         <v>4449.25</v>
       </c>
       <c r="AR17" s="24">
@@ -6114,7 +6110,7 @@
       <c r="AS17" s="70">
         <v>1917.9</v>
       </c>
-      <c r="AT17" s="136">
+      <c r="AT17" s="89">
         <v>1918.81</v>
       </c>
       <c r="AU17" s="28">
@@ -6124,7 +6120,7 @@
       <c r="AV17" s="79">
         <v>1.091</v>
       </c>
-      <c r="AW17" s="137">
+      <c r="AW17" s="90">
         <v>1.091</v>
       </c>
       <c r="AX17" s="32">
@@ -6134,7 +6130,7 @@
       <c r="AY17" s="52">
         <v>30586.799999999999</v>
       </c>
-      <c r="AZ17" s="134">
+      <c r="AZ17" s="87">
         <v>14090.44</v>
       </c>
       <c r="BA17" s="20">
@@ -6144,7 +6140,7 @@
       <c r="BB17" s="61">
         <v>4450.38</v>
       </c>
-      <c r="BC17" s="135">
+      <c r="BC17" s="88">
         <v>3858.16</v>
       </c>
       <c r="BD17" s="24">
@@ -6154,7 +6150,7 @@
       <c r="BE17" s="70">
         <v>1917.9</v>
       </c>
-      <c r="BF17" s="136">
+      <c r="BF17" s="89">
         <v>1849.97</v>
       </c>
       <c r="BG17" s="28">
@@ -6164,7 +6160,7 @@
       <c r="BH17" s="79">
         <v>1.091</v>
       </c>
-      <c r="BI17" s="137">
+      <c r="BI17" s="90">
         <v>1.0405</v>
       </c>
       <c r="BJ17" s="37">
@@ -6173,14 +6169,14 @@
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A18" s="104"/>
+      <c r="A18" s="118"/>
       <c r="B18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="52">
         <v>27974.5</v>
       </c>
-      <c r="D18" s="134">
+      <c r="D18" s="87">
         <v>34085.5</v>
       </c>
       <c r="E18" s="20">
@@ -6190,7 +6186,7 @@
       <c r="F18" s="61">
         <v>4288.05</v>
       </c>
-      <c r="G18" s="135">
+      <c r="G18" s="88">
         <v>3964.1</v>
       </c>
       <c r="H18" s="24">
@@ -6200,7 +6196,7 @@
       <c r="I18" s="70">
         <v>1869.5</v>
       </c>
-      <c r="J18" s="136">
+      <c r="J18" s="89">
         <v>1939.78</v>
       </c>
       <c r="K18" s="28">
@@ -6210,7 +6206,7 @@
       <c r="L18" s="79">
         <v>1.0569999999999999</v>
       </c>
-      <c r="M18" s="137">
+      <c r="M18" s="90">
         <v>1.0716000000000001</v>
       </c>
       <c r="N18" s="32">
@@ -6220,7 +6216,7 @@
       <c r="O18" s="52">
         <v>27974.5</v>
       </c>
-      <c r="P18" s="134">
+      <c r="P18" s="87">
         <v>27044.13</v>
       </c>
       <c r="Q18" s="20">
@@ -6230,7 +6226,7 @@
       <c r="R18" s="61">
         <v>4288.05</v>
       </c>
-      <c r="S18" s="135">
+      <c r="S18" s="88">
         <v>4289.28</v>
       </c>
       <c r="T18" s="24">
@@ -6240,7 +6236,7 @@
       <c r="U18" s="70">
         <v>1869.5</v>
       </c>
-      <c r="V18" s="136">
+      <c r="V18" s="89">
         <v>1869.9</v>
       </c>
       <c r="W18" s="28">
@@ -6250,7 +6246,7 @@
       <c r="X18" s="79">
         <v>1.0569999999999999</v>
       </c>
-      <c r="Y18" s="137">
+      <c r="Y18" s="90">
         <v>1.0570999999999999</v>
       </c>
       <c r="Z18" s="32">
@@ -6260,7 +6256,7 @@
       <c r="AA18" s="52">
         <v>27974.5</v>
       </c>
-      <c r="AB18" s="134">
+      <c r="AB18" s="87">
         <v>35189.949999999997</v>
       </c>
       <c r="AC18" s="20">
@@ -6270,7 +6266,7 @@
       <c r="AD18" s="61">
         <v>4288.05</v>
       </c>
-      <c r="AE18" s="135">
+      <c r="AE18" s="88">
         <v>3968.35</v>
       </c>
       <c r="AF18" s="24">
@@ -6280,7 +6276,7 @@
       <c r="AG18" s="70">
         <v>1869.5</v>
       </c>
-      <c r="AH18" s="136">
+      <c r="AH18" s="89">
         <v>1940.1</v>
       </c>
       <c r="AI18" s="28">
@@ -6290,7 +6286,7 @@
       <c r="AJ18" s="79">
         <v>1.0569999999999999</v>
       </c>
-      <c r="AK18" s="137">
+      <c r="AK18" s="90">
         <v>1.0722</v>
       </c>
       <c r="AL18" s="32">
@@ -6300,7 +6296,7 @@
       <c r="AM18" s="52">
         <v>27974.5</v>
       </c>
-      <c r="AN18" s="134">
+      <c r="AN18" s="87">
         <v>26927.06</v>
       </c>
       <c r="AO18" s="20">
@@ -6310,7 +6306,7 @@
       <c r="AP18" s="61">
         <v>4288.05</v>
       </c>
-      <c r="AQ18" s="135">
+      <c r="AQ18" s="88">
         <v>4292.1099999999997</v>
       </c>
       <c r="AR18" s="24">
@@ -6320,7 +6316,7 @@
       <c r="AS18" s="70">
         <v>1869.5</v>
       </c>
-      <c r="AT18" s="136">
+      <c r="AT18" s="89">
         <v>1873.08</v>
       </c>
       <c r="AU18" s="28">
@@ -6330,7 +6326,7 @@
       <c r="AV18" s="79">
         <v>1.0569999999999999</v>
       </c>
-      <c r="AW18" s="137">
+      <c r="AW18" s="90">
         <v>1.0569</v>
       </c>
       <c r="AX18" s="32">
@@ -6340,7 +6336,7 @@
       <c r="AY18" s="52">
         <v>27974.5</v>
       </c>
-      <c r="AZ18" s="134">
+      <c r="AZ18" s="87">
         <v>13445.56</v>
       </c>
       <c r="BA18" s="20">
@@ -6350,7 +6346,7 @@
       <c r="BB18" s="61">
         <v>4288.05</v>
       </c>
-      <c r="BC18" s="135">
+      <c r="BC18" s="88">
         <v>3873.06</v>
       </c>
       <c r="BD18" s="24">
@@ -6360,7 +6356,7 @@
       <c r="BE18" s="70">
         <v>1869.5</v>
       </c>
-      <c r="BF18" s="136">
+      <c r="BF18" s="89">
         <v>1866.45</v>
       </c>
       <c r="BG18" s="28">
@@ -6370,7 +6366,7 @@
       <c r="BH18" s="79">
         <v>1.0569999999999999</v>
       </c>
-      <c r="BI18" s="137">
+      <c r="BI18" s="90">
         <v>1.0299</v>
       </c>
       <c r="BJ18" s="37">
@@ -6379,7 +6375,7 @@
       </c>
     </row>
     <row r="19" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="105"/>
+      <c r="A19" s="119"/>
       <c r="B19" s="3" t="s">
         <v>26</v>
       </c>
@@ -6585,7 +6581,7 @@
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="117" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -6793,14 +6789,14 @@
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="118"/>
       <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="52">
         <v>62890.1</v>
       </c>
-      <c r="D21" s="134">
+      <c r="D21" s="87">
         <v>68383.38</v>
       </c>
       <c r="E21" s="20">
@@ -6810,7 +6806,7 @@
       <c r="F21" s="61">
         <v>5475.09</v>
       </c>
-      <c r="G21" s="135">
+      <c r="G21" s="88">
         <v>4889.32</v>
       </c>
       <c r="H21" s="24">
@@ -6820,7 +6816,7 @@
       <c r="I21" s="70">
         <v>2338.9</v>
       </c>
-      <c r="J21" s="136">
+      <c r="J21" s="89">
         <v>2171.86</v>
       </c>
       <c r="K21" s="28">
@@ -6830,7 +6826,7 @@
       <c r="L21" s="79">
         <v>1.0738000000000001</v>
       </c>
-      <c r="M21" s="137">
+      <c r="M21" s="90">
         <v>1.1052999999999999</v>
       </c>
       <c r="N21" s="32">
@@ -6840,7 +6836,7 @@
       <c r="O21" s="52">
         <v>62890.1</v>
       </c>
-      <c r="P21" s="134">
+      <c r="P21" s="87">
         <v>62899.29</v>
       </c>
       <c r="Q21" s="20">
@@ -6850,7 +6846,7 @@
       <c r="R21" s="61">
         <v>5475.09</v>
       </c>
-      <c r="S21" s="135">
+      <c r="S21" s="88">
         <v>5460.88</v>
       </c>
       <c r="T21" s="24">
@@ -6860,7 +6856,7 @@
       <c r="U21" s="70">
         <v>2338.9</v>
       </c>
-      <c r="V21" s="136">
+      <c r="V21" s="89">
         <v>2337.15</v>
       </c>
       <c r="W21" s="28">
@@ -6870,7 +6866,7 @@
       <c r="X21" s="79">
         <v>1.0738000000000001</v>
       </c>
-      <c r="Y21" s="137">
+      <c r="Y21" s="90">
         <v>1.0712999999999999</v>
       </c>
       <c r="Z21" s="32">
@@ -6880,7 +6876,7 @@
       <c r="AA21" s="52">
         <v>62890.1</v>
       </c>
-      <c r="AB21" s="134">
+      <c r="AB21" s="87">
         <v>68781.67</v>
       </c>
       <c r="AC21" s="20">
@@ -6890,7 +6886,7 @@
       <c r="AD21" s="61">
         <v>5475.09</v>
       </c>
-      <c r="AE21" s="135">
+      <c r="AE21" s="88">
         <v>4899.67</v>
       </c>
       <c r="AF21" s="24">
@@ -6900,7 +6896,7 @@
       <c r="AG21" s="70">
         <v>2338.9</v>
       </c>
-      <c r="AH21" s="136">
+      <c r="AH21" s="89">
         <v>2173.4699999999998</v>
       </c>
       <c r="AI21" s="28">
@@ -6910,7 +6906,7 @@
       <c r="AJ21" s="79">
         <v>1.0738000000000001</v>
       </c>
-      <c r="AK21" s="137">
+      <c r="AK21" s="90">
         <v>1.1049</v>
       </c>
       <c r="AL21" s="32">
@@ -6920,7 +6916,7 @@
       <c r="AM21" s="52">
         <v>62890.1</v>
       </c>
-      <c r="AN21" s="134">
+      <c r="AN21" s="87">
         <v>62754.65</v>
       </c>
       <c r="AO21" s="20">
@@ -6930,7 +6926,7 @@
       <c r="AP21" s="61">
         <v>5475.09</v>
       </c>
-      <c r="AQ21" s="135">
+      <c r="AQ21" s="88">
         <v>5461.32</v>
       </c>
       <c r="AR21" s="24">
@@ -6940,7 +6936,7 @@
       <c r="AS21" s="70">
         <v>2338.9</v>
       </c>
-      <c r="AT21" s="136">
+      <c r="AT21" s="89">
         <v>2337.16</v>
       </c>
       <c r="AU21" s="28">
@@ -6950,7 +6946,7 @@
       <c r="AV21" s="79">
         <v>1.0738000000000001</v>
       </c>
-      <c r="AW21" s="137">
+      <c r="AW21" s="90">
         <v>1.0713999999999999</v>
       </c>
       <c r="AX21" s="32">
@@ -6960,7 +6956,7 @@
       <c r="AY21" s="52">
         <v>62890.1</v>
       </c>
-      <c r="AZ21" s="134">
+      <c r="AZ21" s="87">
         <v>46018.02</v>
       </c>
       <c r="BA21" s="20">
@@ -6970,7 +6966,7 @@
       <c r="BB21" s="61">
         <v>5475.09</v>
       </c>
-      <c r="BC21" s="135">
+      <c r="BC21" s="88">
         <v>4926.2</v>
       </c>
       <c r="BD21" s="24">
@@ -6980,7 +6976,7 @@
       <c r="BE21" s="70">
         <v>2338.9</v>
       </c>
-      <c r="BF21" s="136">
+      <c r="BF21" s="89">
         <v>2164.02</v>
       </c>
       <c r="BG21" s="28">
@@ -6990,7 +6986,7 @@
       <c r="BH21" s="79">
         <v>1.0738000000000001</v>
       </c>
-      <c r="BI21" s="137">
+      <c r="BI21" s="90">
         <v>1.0984</v>
       </c>
       <c r="BJ21" s="37">
@@ -6999,14 +6995,14 @@
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="118"/>
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="52">
         <v>60835.5</v>
       </c>
-      <c r="D22" s="134">
+      <c r="D22" s="87">
         <v>87137.72</v>
       </c>
       <c r="E22" s="20">
@@ -7016,7 +7012,7 @@
       <c r="F22" s="61">
         <v>5708.75</v>
       </c>
-      <c r="G22" s="135">
+      <c r="G22" s="88">
         <v>4950.6400000000003</v>
       </c>
       <c r="H22" s="24">
@@ -7026,7 +7022,7 @@
       <c r="I22" s="70">
         <v>2678.5</v>
       </c>
-      <c r="J22" s="136">
+      <c r="J22" s="89">
         <v>2217.69</v>
       </c>
       <c r="K22" s="28">
@@ -7036,7 +7032,7 @@
       <c r="L22" s="79">
         <v>1.1067</v>
       </c>
-      <c r="M22" s="137">
+      <c r="M22" s="90">
         <v>1.1061000000000001</v>
       </c>
       <c r="N22" s="32">
@@ -7046,7 +7042,7 @@
       <c r="O22" s="52">
         <v>60835.5</v>
       </c>
-      <c r="P22" s="134">
+      <c r="P22" s="87">
         <v>63717.07</v>
       </c>
       <c r="Q22" s="20">
@@ -7056,7 +7052,7 @@
       <c r="R22" s="61">
         <v>5708.75</v>
       </c>
-      <c r="S22" s="135">
+      <c r="S22" s="88">
         <v>5761.03</v>
       </c>
       <c r="T22" s="24">
@@ -7066,7 +7062,7 @@
       <c r="U22" s="70">
         <v>2678.5</v>
       </c>
-      <c r="V22" s="136">
+      <c r="V22" s="89">
         <v>2648.85</v>
       </c>
       <c r="W22" s="28">
@@ -7076,7 +7072,7 @@
       <c r="X22" s="79">
         <v>1.1067</v>
       </c>
-      <c r="Y22" s="137">
+      <c r="Y22" s="90">
         <v>1.1133999999999999</v>
       </c>
       <c r="Z22" s="32">
@@ -7086,7 +7082,7 @@
       <c r="AA22" s="52">
         <v>60835.5</v>
       </c>
-      <c r="AB22" s="134">
+      <c r="AB22" s="87">
         <v>87709.21</v>
       </c>
       <c r="AC22" s="20">
@@ -7096,7 +7092,7 @@
       <c r="AD22" s="61">
         <v>5708.75</v>
       </c>
-      <c r="AE22" s="135">
+      <c r="AE22" s="88">
         <v>4960.33</v>
       </c>
       <c r="AF22" s="24">
@@ -7106,7 +7102,7 @@
       <c r="AG22" s="70">
         <v>2678.5</v>
       </c>
-      <c r="AH22" s="136">
+      <c r="AH22" s="89">
         <v>2221.94</v>
       </c>
       <c r="AI22" s="28">
@@ -7116,7 +7112,7 @@
       <c r="AJ22" s="79">
         <v>1.1067</v>
       </c>
-      <c r="AK22" s="137">
+      <c r="AK22" s="90">
         <v>1.1054999999999999</v>
       </c>
       <c r="AL22" s="32">
@@ -7126,7 +7122,7 @@
       <c r="AM22" s="52">
         <v>60835.5</v>
       </c>
-      <c r="AN22" s="134">
+      <c r="AN22" s="87">
         <v>63512.62</v>
       </c>
       <c r="AO22" s="20">
@@ -7136,7 +7132,7 @@
       <c r="AP22" s="61">
         <v>5708.75</v>
       </c>
-      <c r="AQ22" s="135">
+      <c r="AQ22" s="88">
         <v>5765.81</v>
       </c>
       <c r="AR22" s="24">
@@ -7146,7 +7142,7 @@
       <c r="AS22" s="70">
         <v>2678.5</v>
       </c>
-      <c r="AT22" s="136">
+      <c r="AT22" s="89">
         <v>2649.99</v>
       </c>
       <c r="AU22" s="28">
@@ -7156,7 +7152,7 @@
       <c r="AV22" s="79">
         <v>1.1067</v>
       </c>
-      <c r="AW22" s="137">
+      <c r="AW22" s="90">
         <v>1.1136999999999999</v>
       </c>
       <c r="AX22" s="32">
@@ -7166,7 +7162,7 @@
       <c r="AY22" s="52">
         <v>60835.5</v>
       </c>
-      <c r="AZ22" s="134">
+      <c r="AZ22" s="87">
         <v>52969.62</v>
       </c>
       <c r="BA22" s="20">
@@ -7176,7 +7172,7 @@
       <c r="BB22" s="61">
         <v>5708.75</v>
       </c>
-      <c r="BC22" s="135">
+      <c r="BC22" s="88">
         <v>5070.21</v>
       </c>
       <c r="BD22" s="24">
@@ -7186,7 +7182,7 @@
       <c r="BE22" s="70">
         <v>2678.5</v>
       </c>
-      <c r="BF22" s="136">
+      <c r="BF22" s="89">
         <v>2256.85</v>
       </c>
       <c r="BG22" s="28">
@@ -7196,7 +7192,7 @@
       <c r="BH22" s="79">
         <v>1.1067</v>
       </c>
-      <c r="BI22" s="137">
+      <c r="BI22" s="90">
         <v>1.1073</v>
       </c>
       <c r="BJ22" s="37">
@@ -7205,7 +7201,7 @@
       </c>
     </row>
     <row r="23" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="105"/>
+      <c r="A23" s="119"/>
       <c r="B23" s="3" t="s">
         <v>30</v>
       </c>
@@ -7411,7 +7407,7 @@
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A24" s="103" t="s">
+      <c r="A24" s="117" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -7619,14 +7615,14 @@
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A25" s="104"/>
+      <c r="A25" s="118"/>
       <c r="B25" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C25" s="52">
         <v>105694.3</v>
       </c>
-      <c r="D25" s="134">
+      <c r="D25" s="87">
         <v>150391.75</v>
       </c>
       <c r="E25" s="20">
@@ -7636,7 +7632,7 @@
       <c r="F25" s="61">
         <v>6198.01</v>
       </c>
-      <c r="G25" s="135">
+      <c r="G25" s="88">
         <v>6048.59</v>
       </c>
       <c r="H25" s="24">
@@ -7646,7 +7642,7 @@
       <c r="I25" s="70">
         <v>3349.8</v>
       </c>
-      <c r="J25" s="136">
+      <c r="J25" s="89">
         <v>2736.32</v>
       </c>
       <c r="K25" s="28">
@@ -7656,7 +7652,7 @@
       <c r="L25" s="79">
         <v>1.1807000000000001</v>
       </c>
-      <c r="M25" s="137">
+      <c r="M25" s="90">
         <v>1.0354000000000001</v>
       </c>
       <c r="N25" s="32">
@@ -7666,7 +7662,7 @@
       <c r="O25" s="52">
         <v>105694.3</v>
       </c>
-      <c r="P25" s="134">
+      <c r="P25" s="87">
         <v>107303.54</v>
       </c>
       <c r="Q25" s="20">
@@ -7676,7 +7672,7 @@
       <c r="R25" s="61">
         <v>6198.01</v>
       </c>
-      <c r="S25" s="135">
+      <c r="S25" s="88">
         <v>6203.02</v>
       </c>
       <c r="T25" s="24">
@@ -7686,7 +7682,7 @@
       <c r="U25" s="70">
         <v>3349.8</v>
       </c>
-      <c r="V25" s="136">
+      <c r="V25" s="89">
         <v>3308.87</v>
       </c>
       <c r="W25" s="28">
@@ -7696,7 +7692,7 @@
       <c r="X25" s="79">
         <v>1.1807000000000001</v>
       </c>
-      <c r="Y25" s="137">
+      <c r="Y25" s="90">
         <v>1.1786000000000001</v>
       </c>
       <c r="Z25" s="32">
@@ -7706,7 +7702,7 @@
       <c r="AA25" s="52">
         <v>105694.3</v>
       </c>
-      <c r="AB25" s="134">
+      <c r="AB25" s="87">
         <v>149133.73000000001</v>
       </c>
       <c r="AC25" s="20">
@@ -7716,7 +7712,7 @@
       <c r="AD25" s="61">
         <v>6198.01</v>
       </c>
-      <c r="AE25" s="135">
+      <c r="AE25" s="88">
         <v>6035.81</v>
       </c>
       <c r="AF25" s="24">
@@ -7726,7 +7722,7 @@
       <c r="AG25" s="70">
         <v>3349.8</v>
       </c>
-      <c r="AH25" s="136">
+      <c r="AH25" s="89">
         <v>2743.04</v>
       </c>
       <c r="AI25" s="28">
@@ -7736,7 +7732,7 @@
       <c r="AJ25" s="79">
         <v>1.1807000000000001</v>
       </c>
-      <c r="AK25" s="137">
+      <c r="AK25" s="90">
         <v>1.0359</v>
       </c>
       <c r="AL25" s="32">
@@ -7746,7 +7742,7 @@
       <c r="AM25" s="52">
         <v>105694.3</v>
       </c>
-      <c r="AN25" s="134">
+      <c r="AN25" s="87">
         <v>107476.83</v>
       </c>
       <c r="AO25" s="20">
@@ -7756,7 +7752,7 @@
       <c r="AP25" s="61">
         <v>6198.01</v>
       </c>
-      <c r="AQ25" s="135">
+      <c r="AQ25" s="88">
         <v>6204.19</v>
       </c>
       <c r="AR25" s="24">
@@ -7766,7 +7762,7 @@
       <c r="AS25" s="70">
         <v>3349.8</v>
       </c>
-      <c r="AT25" s="136">
+      <c r="AT25" s="89">
         <v>3310.75</v>
       </c>
       <c r="AU25" s="28">
@@ -7776,7 +7772,7 @@
       <c r="AV25" s="79">
         <v>1.1807000000000001</v>
       </c>
-      <c r="AW25" s="137">
+      <c r="AW25" s="90">
         <v>1.1788000000000001</v>
       </c>
       <c r="AX25" s="32">
@@ -7786,7 +7782,7 @@
       <c r="AY25" s="52">
         <v>105694.3</v>
       </c>
-      <c r="AZ25" s="134">
+      <c r="AZ25" s="87">
         <v>131330.5</v>
       </c>
       <c r="BA25" s="20">
@@ -7796,7 +7792,7 @@
       <c r="BB25" s="61">
         <v>6198.01</v>
       </c>
-      <c r="BC25" s="135">
+      <c r="BC25" s="88">
         <v>6427.06</v>
       </c>
       <c r="BD25" s="24">
@@ -7806,7 +7802,7 @@
       <c r="BE25" s="70">
         <v>3349.8</v>
       </c>
-      <c r="BF25" s="136">
+      <c r="BF25" s="89">
         <v>2926.5</v>
       </c>
       <c r="BG25" s="28">
@@ -7816,7 +7812,7 @@
       <c r="BH25" s="79">
         <v>1.1807000000000001</v>
       </c>
-      <c r="BI25" s="137">
+      <c r="BI25" s="90">
         <v>1.0367999999999999</v>
       </c>
       <c r="BJ25" s="37">
@@ -7825,14 +7821,14 @@
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A26" s="104"/>
+      <c r="A26" s="118"/>
       <c r="B26" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C26" s="52">
         <v>118576.2</v>
       </c>
-      <c r="D26" s="134">
+      <c r="D26" s="87">
         <v>191038.51</v>
       </c>
       <c r="E26" s="20">
@@ -7842,7 +7838,7 @@
       <c r="F26" s="61">
         <v>6711.2</v>
       </c>
-      <c r="G26" s="135">
+      <c r="G26" s="88">
         <v>6134.33</v>
       </c>
       <c r="H26" s="24">
@@ -7852,7 +7848,7 @@
       <c r="I26" s="70">
         <v>3897.5</v>
       </c>
-      <c r="J26" s="136">
+      <c r="J26" s="89">
         <v>2798.15</v>
       </c>
       <c r="K26" s="28">
@@ -7862,7 +7858,7 @@
       <c r="L26" s="79">
         <v>1.173</v>
       </c>
-      <c r="M26" s="137">
+      <c r="M26" s="90">
         <v>1.0355000000000001</v>
       </c>
       <c r="N26" s="32">
@@ -7872,7 +7868,7 @@
       <c r="O26" s="52">
         <v>118576.2</v>
       </c>
-      <c r="P26" s="134">
+      <c r="P26" s="87">
         <v>114009.09</v>
       </c>
       <c r="Q26" s="20">
@@ -7882,7 +7878,7 @@
       <c r="R26" s="61">
         <v>6711.2</v>
       </c>
-      <c r="S26" s="135">
+      <c r="S26" s="88">
         <v>6687.09</v>
       </c>
       <c r="T26" s="24">
@@ -7892,7 +7888,7 @@
       <c r="U26" s="70">
         <v>3897.5</v>
       </c>
-      <c r="V26" s="136">
+      <c r="V26" s="89">
         <v>3873.16</v>
       </c>
       <c r="W26" s="28">
@@ -7902,7 +7898,7 @@
       <c r="X26" s="79">
         <v>1.173</v>
       </c>
-      <c r="Y26" s="137">
+      <c r="Y26" s="90">
         <v>1.1734</v>
       </c>
       <c r="Z26" s="32">
@@ -7912,7 +7908,7 @@
       <c r="AA26" s="52">
         <v>118576.2</v>
       </c>
-      <c r="AB26" s="134">
+      <c r="AB26" s="87">
         <v>188503.41</v>
       </c>
       <c r="AC26" s="20">
@@ -7922,7 +7918,7 @@
       <c r="AD26" s="61">
         <v>6711.2</v>
       </c>
-      <c r="AE26" s="135">
+      <c r="AE26" s="88">
         <v>6122.65</v>
       </c>
       <c r="AF26" s="24">
@@ -7932,7 +7928,7 @@
       <c r="AG26" s="70">
         <v>3897.5</v>
       </c>
-      <c r="AH26" s="136">
+      <c r="AH26" s="89">
         <v>2809.11</v>
       </c>
       <c r="AI26" s="28">
@@ -7942,7 +7938,7 @@
       <c r="AJ26" s="79">
         <v>1.173</v>
       </c>
-      <c r="AK26" s="137">
+      <c r="AK26" s="90">
         <v>1.0370999999999999</v>
       </c>
       <c r="AL26" s="32">
@@ -7952,7 +7948,7 @@
       <c r="AM26" s="52">
         <v>118576.2</v>
       </c>
-      <c r="AN26" s="134">
+      <c r="AN26" s="87">
         <v>114414.37</v>
       </c>
       <c r="AO26" s="20">
@@ -7962,7 +7958,7 @@
       <c r="AP26" s="61">
         <v>6711.2</v>
       </c>
-      <c r="AQ26" s="135">
+      <c r="AQ26" s="88">
         <v>6691.34</v>
       </c>
       <c r="AR26" s="24">
@@ -7972,7 +7968,7 @@
       <c r="AS26" s="70">
         <v>3897.5</v>
       </c>
-      <c r="AT26" s="136">
+      <c r="AT26" s="89">
         <v>3870.65</v>
       </c>
       <c r="AU26" s="28">
@@ -7982,7 +7978,7 @@
       <c r="AV26" s="79">
         <v>1.173</v>
       </c>
-      <c r="AW26" s="137">
+      <c r="AW26" s="90">
         <v>1.1735</v>
       </c>
       <c r="AX26" s="32">
@@ -7992,7 +7988,7 @@
       <c r="AY26" s="52">
         <v>118576.2</v>
       </c>
-      <c r="AZ26" s="134">
+      <c r="AZ26" s="87">
         <v>156050.74</v>
       </c>
       <c r="BA26" s="20">
@@ -8002,7 +7998,7 @@
       <c r="BB26" s="61">
         <v>6711.2</v>
       </c>
-      <c r="BC26" s="135">
+      <c r="BC26" s="88">
         <v>6690.16</v>
       </c>
       <c r="BD26" s="24">
@@ -8012,7 +8008,7 @@
       <c r="BE26" s="70">
         <v>3897.5</v>
       </c>
-      <c r="BF26" s="136">
+      <c r="BF26" s="89">
         <v>3133.09</v>
       </c>
       <c r="BG26" s="28">
@@ -8022,7 +8018,7 @@
       <c r="BH26" s="79">
         <v>1.173</v>
       </c>
-      <c r="BI26" s="137">
+      <c r="BI26" s="90">
         <v>1.0449999999999999</v>
       </c>
       <c r="BJ26" s="37">
@@ -8031,7 +8027,7 @@
       </c>
     </row>
     <row r="27" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="105"/>
+      <c r="A27" s="119"/>
       <c r="B27" s="3" t="s">
         <v>34</v>
       </c>
@@ -8238,140 +8234,140 @@
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.35">
       <c r="D28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E28" s="20" cm="1">
         <f t="array" ref="E28">AVERAGE(ABS(E4:E27))</f>
         <v>1.0265439941037653</v>
       </c>
       <c r="G28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H28" s="24" cm="1">
         <f t="array" ref="H28">AVERAGE(ABS(H4:H27))</f>
         <v>0.130167169295241</v>
       </c>
       <c r="J28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K28" s="28" cm="1">
         <f t="array" ref="K28">AVERAGE(ABS(K4:K27))</f>
         <v>0.11815919350437008</v>
       </c>
       <c r="M28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N28" s="35" cm="1">
         <f t="array" ref="N28">AVERAGE(ABS(N4:N27))</f>
         <v>5.4821890430214487E-2</v>
       </c>
       <c r="P28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q28" s="20" cm="1">
         <f t="array" ref="Q28">AVERAGE(ABS(Q4:Q27))</f>
         <v>2.3603105615269012E-2</v>
       </c>
       <c r="S28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T28" s="24" cm="1">
         <f t="array" ref="T28">AVERAGE(ABS(T4:T27))</f>
         <v>5.3669333445252694E-3</v>
       </c>
       <c r="V28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W28" s="28" cm="1">
         <f t="array" ref="W28">AVERAGE(ABS(W4:W27))</f>
         <v>4.0144838116363381E-3</v>
       </c>
       <c r="Y28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Z28" s="35" cm="1">
         <f t="array" ref="Z28">AVERAGE(ABS(Z4:Z27))</f>
         <v>1.7264471176856864E-3</v>
       </c>
       <c r="AB28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AC28" s="20" cm="1">
         <f t="array" ref="AC28">AVERAGE(ABS(AC4:AC27))</f>
         <v>0.97926702621680883</v>
       </c>
       <c r="AE28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AF28" s="24" cm="1">
         <f t="array" ref="AF28">AVERAGE(ABS(AF4:AF27))</f>
         <v>0.12912372015400433</v>
       </c>
       <c r="AH28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AI28" s="28" cm="1">
         <f t="array" ref="AI28">AVERAGE(ABS(AI4:AI27))</f>
         <v>0.11658479721638716</v>
       </c>
       <c r="AK28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AL28" s="35" cm="1">
         <f t="array" ref="AL28">AVERAGE(ABS(AL4:AL27))</f>
         <v>5.4183547798500049E-2</v>
       </c>
       <c r="AN28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AO28" s="20" cm="1">
         <f t="array" ref="AO28">AVERAGE(ABS(AO4:AO27))</f>
         <v>3.6161156765879422E-2</v>
       </c>
       <c r="AQ28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AR28" s="24" cm="1">
         <f t="array" ref="AR28">AVERAGE(ABS(AR4:AR27))</f>
         <v>5.5213967295835919E-3</v>
       </c>
       <c r="AT28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AU28" s="28" cm="1">
         <f t="array" ref="AU28">AVERAGE(ABS(AU4:AU27))</f>
         <v>4.3725639207581333E-3</v>
       </c>
       <c r="AW28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AX28" s="35" cm="1">
         <f t="array" ref="AX28">AVERAGE(ABS(AX4:AX27))</f>
         <v>1.7571768166273812E-3</v>
       </c>
       <c r="AZ28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BA28" s="20" cm="1">
         <f t="array" ref="BA28">AVERAGE(ABS(BA4:BA27))</f>
         <v>0.69414892117823801</v>
       </c>
       <c r="BC28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BD28" s="24" cm="1">
         <f t="array" ref="BD28">AVERAGE(ABS(BD4:BD27))</f>
         <v>0.12555312369212876</v>
       </c>
       <c r="BF28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BG28" s="28" cm="1">
         <f t="array" ref="BG28">AVERAGE(ABS(BG4:BG27))</f>
         <v>0.10299876208610644</v>
       </c>
       <c r="BI28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BJ28" s="35" cm="1">
         <f t="array" ref="BJ28">AVERAGE(ABS(BJ4:BJ27))</f>
@@ -8380,140 +8376,140 @@
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.35">
       <c r="D29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E29" s="20" cm="1">
         <f t="array" ref="E29">MAX(ABS(E4:E27))</f>
         <v>7.6732308766186872</v>
       </c>
       <c r="G29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H29" s="24" cm="1">
         <f t="array" ref="H29">MAX(ABS(H4:H27))</f>
         <v>0.38433799454487655</v>
       </c>
       <c r="J29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K29" s="28" cm="1">
         <f t="array" ref="K29">MAX(ABS(K4:K27))</f>
         <v>0.34395570382088941</v>
       </c>
       <c r="M29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N29" s="35" cm="1">
         <f t="array" ref="N29">MAX(ABS(N4:N27))</f>
         <v>0.16399632615573023</v>
       </c>
       <c r="P29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q29" s="20" cm="1">
         <f t="array" ref="Q29">MAX(ABS(Q4:Q27))</f>
         <v>8.8091222531466742E-2</v>
       </c>
       <c r="S29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T29" s="24" cm="1">
         <f t="array" ref="T29">MAX(ABS(T4:T27))</f>
         <v>4.8249342238413206E-2</v>
       </c>
       <c r="V29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W29" s="28" cm="1">
         <f t="array" ref="W29">MAX(ABS(W4:W27))</f>
         <v>1.9582350060109541E-2</v>
       </c>
       <c r="Y29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z29" s="35" cm="1">
         <f t="array" ref="Z29">MAX(ABS(Z4:Z27))</f>
         <v>6.0540345170325546E-3</v>
       </c>
       <c r="AB29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AC29" s="20" cm="1">
         <f t="array" ref="AC29">MAX(ABS(AC4:AC27))</f>
         <v>6.9922345111442734</v>
       </c>
       <c r="AE29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AF29" s="24" cm="1">
         <f t="array" ref="AF29">MAX(ABS(AF4:AF27))</f>
         <v>0.38206223749309753</v>
       </c>
       <c r="AH29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AI29" s="28" cm="1">
         <f t="array" ref="AI29">MAX(ABS(AI4:AI27))</f>
         <v>0.33904231293920739</v>
       </c>
       <c r="AK29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AL29" s="35" cm="1">
         <f t="array" ref="AL29">MAX(ABS(AL4:AL27))</f>
         <v>0.16226145525053581</v>
       </c>
       <c r="AN29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AO29" s="20" cm="1">
         <f t="array" ref="AO29">MAX(ABS(AO4:AO27))</f>
         <v>0.32639471997732661</v>
       </c>
       <c r="AQ29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AR29" s="24" cm="1">
         <f t="array" ref="AR29">MAX(ABS(AR4:AR27))</f>
         <v>5.2252580449301818E-2</v>
       </c>
       <c r="AT29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AU29" s="28" cm="1">
         <f t="array" ref="AU29">MAX(ABS(AU4:AU27))</f>
         <v>1.9324101696424636E-2</v>
       </c>
       <c r="AW29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AX29" s="35" cm="1">
         <f t="array" ref="AX29">MAX(ABS(AX4:AX27))</f>
         <v>6.3251106894369703E-3</v>
       </c>
       <c r="AZ29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="BA29" s="20" cm="1">
         <f t="array" ref="BA29">MAX(ABS(BA4:BA27))</f>
         <v>3.0942395176430946</v>
       </c>
       <c r="BC29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="BD29" s="24" cm="1">
         <f t="array" ref="BD29">MAX(ABS(BD4:BD27))</f>
         <v>0.49589192385138414</v>
       </c>
       <c r="BF29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="BG29" s="28" cm="1">
         <f t="array" ref="BG29">MAX(ABS(BG4:BG27))</f>
         <v>0.21391936352902063</v>
       </c>
       <c r="BI29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="BJ29" s="35" cm="1">
         <f t="array" ref="BJ29">MAX(ABS(BJ4:BJ27))</f>
@@ -8522,156 +8518,173 @@
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.35">
       <c r="D30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E30" s="20" cm="1">
         <f t="array" ref="E30">MEDIAN(ABS(E4:E27))</f>
         <v>0.41983749811006715</v>
       </c>
       <c r="G30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H30" s="24" cm="1">
         <f t="array" ref="H30">MEDIAN(ABS(H4:H27))</f>
         <v>0.1059274728571802</v>
       </c>
       <c r="J30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K30" s="28" cm="1">
         <f t="array" ref="K30">MEDIAN(ABS(K4:K27))</f>
         <v>0.11830693207104818</v>
       </c>
       <c r="M30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N30" s="35" cm="1">
         <f t="array" ref="N30">MEDIAN(ABS(N4:N27))</f>
         <v>3.9997552868563199E-2</v>
       </c>
       <c r="P30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q30" s="20" cm="1">
         <f t="array" ref="Q30">MEDIAN(ABS(Q4:Q27))</f>
         <v>1.7710703419741569E-2</v>
       </c>
       <c r="S30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="T30" s="24" cm="1">
         <f t="array" ref="T30">MEDIAN(ABS(T4:T27))</f>
         <v>2.0949115606919092E-3</v>
       </c>
       <c r="V30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W30" s="28" cm="1">
         <f t="array" ref="W30">MEDIAN(ABS(W4:W27))</f>
         <v>8.064907145073903E-4</v>
       </c>
       <c r="Y30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z30" s="35" cm="1">
         <f t="array" ref="Z30">MEDIAN(ABS(Z4:Z27))</f>
         <v>9.6594817899362071E-4</v>
       </c>
       <c r="AB30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AC30" s="20" cm="1">
         <f t="array" ref="AC30">MEDIAN(ABS(AC4:AC27))</f>
         <v>0.40139723627472368</v>
       </c>
       <c r="AE30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AF30" s="24" cm="1">
         <f t="array" ref="AF30">MEDIAN(ABS(AF4:AF27))</f>
         <v>0.10515400358281086</v>
       </c>
       <c r="AH30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AI30" s="28" cm="1">
         <f t="array" ref="AI30">MEDIAN(ABS(AI4:AI27))</f>
         <v>0.11726474127652055</v>
       </c>
       <c r="AK30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AL30" s="35" cm="1">
         <f t="array" ref="AL30">MEDIAN(ABS(AL4:AL27))</f>
         <v>4.0051606146391597E-2</v>
       </c>
       <c r="AN30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AO30" s="20" cm="1">
         <f t="array" ref="AO30">MEDIAN(ABS(AO4:AO27))</f>
         <v>2.040183594553692E-2</v>
       </c>
       <c r="AQ30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AR30" s="24" cm="1">
         <f t="array" ref="AR30">MEDIAN(ABS(AR4:AR27))</f>
         <v>2.0007344745063432E-3</v>
       </c>
       <c r="AT30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AU30" s="28" cm="1">
         <f t="array" ref="AU30">MEDIAN(ABS(AU4:AU27))</f>
         <v>1.71684161731505E-3</v>
       </c>
       <c r="AW30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AX30" s="35" cm="1">
         <f t="array" ref="AX30">MEDIAN(ABS(AX4:AX27))</f>
         <v>9.9561042899793317E-4</v>
       </c>
       <c r="AZ30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="BA30" s="20" cm="1">
         <f t="array" ref="BA30">MEDIAN(ABS(BA4:BA27))</f>
         <v>0.36219911585111586</v>
       </c>
       <c r="BC30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="BD30" s="24" cm="1">
         <f t="array" ref="BD30">MEDIAN(ABS(BD4:BD27))</f>
         <v>8.7038114651152534E-2</v>
       </c>
       <c r="BF30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="BG30" s="28" cm="1">
         <f t="array" ref="BG30">MEDIAN(ABS(BG4:BG27))</f>
         <v>9.712213307782841E-2</v>
       </c>
       <c r="BI30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="BJ30" s="35" cm="1">
         <f t="array" ref="BJ30">MEDIAN(ABS(BJ4:BJ27))</f>
         <v>4.4835329387642134E-2</v>
       </c>
     </row>
-    <row r="37" spans="5:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E37" s="86"/>
-    </row>
-    <row r="38" spans="5:16" x14ac:dyDescent="0.35">
-      <c r="P38" t="s">
-        <v>40</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="AY1:BJ1"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AM1:AX1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="AA1:AL1"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="AJ2:AL2"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="X2:Z2"/>
     <mergeCell ref="C1:N1"/>
@@ -8684,28 +8697,6 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AA1:AL1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="AM1:AX1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="AY1:BJ1"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BH2:BJ2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8728,22 +8719,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" t="s">
-        <v>46</v>
-      </c>
       <c r="D1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" t="s">
         <v>49</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>50</v>
-      </c>
-      <c r="F1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -8773,7 +8764,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" s="86">
         <f>'ARIMA DATA'!H28</f>
@@ -8899,22 +8890,22 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
         <v>45</v>
       </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
       <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
         <v>49</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>50</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -8944,7 +8935,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="86">
         <f>'ARIMA DATA'!H29</f>
@@ -9019,22 +9010,22 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
         <v>45</v>
       </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
       <c r="D16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" t="s">
         <v>49</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>50</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -9064,7 +9055,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18" s="86">
         <f>'ARIMA DATA'!H30</f>

--- a/Analysis.xlsx
+++ b/Analysis.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Desktop\ANO 3\ANO 3 SEM 2\PIC\Financial-Markets-Prediction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0A0D12-495C-4BA2-B07A-92867993A59E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFB9B78-B4D9-424E-BBE6-054E2264A67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARIMA DATA" sheetId="1" r:id="rId1"/>
-    <sheet name="ARIMA ANALYSIS" sheetId="2" r:id="rId2"/>
+    <sheet name="ARIMA FINAL" sheetId="3" r:id="rId2"/>
+    <sheet name="ARIMA ANALYSIS" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="86">
   <si>
     <t>Tipo</t>
   </si>
@@ -219,13 +220,113 @@
   <si>
     <t>MEDIANA</t>
   </si>
+  <si>
+    <t>Ordem</t>
+  </si>
+  <si>
+    <t>Ano previsto</t>
+  </si>
+  <si>
+    <t>1'Abril'20</t>
+  </si>
+  <si>
+    <t>1'Julho'20</t>
+  </si>
+  <si>
+    <t>1'Outubro'20</t>
+  </si>
+  <si>
+    <t>1'Janeiro'21</t>
+  </si>
+  <si>
+    <t>1'Abril'21</t>
+  </si>
+  <si>
+    <t>1'Julho'21</t>
+  </si>
+  <si>
+    <t>1'Outubro'21</t>
+  </si>
+  <si>
+    <t>1'Janeiro'22</t>
+  </si>
+  <si>
+    <t>1'Abril'22</t>
+  </si>
+  <si>
+    <t>1'Julho'22</t>
+  </si>
+  <si>
+    <t>1'Outubro'22</t>
+  </si>
+  <si>
+    <t>1'Janeiro'23</t>
+  </si>
+  <si>
+    <t>1'Abril'23</t>
+  </si>
+  <si>
+    <t>1'Julho'23</t>
+  </si>
+  <si>
+    <t>1'Outubro'23</t>
+  </si>
+  <si>
+    <t>1'Janeiro'24</t>
+  </si>
+  <si>
+    <t>1'Abril'24</t>
+  </si>
+  <si>
+    <t>1'Julho'24</t>
+  </si>
+  <si>
+    <t>1'Outubro'24</t>
+  </si>
+  <si>
+    <t>1'Janeiro'25</t>
+  </si>
+  <si>
+    <t>1'Abril'25</t>
+  </si>
+  <si>
+    <t>1'Julho'25</t>
+  </si>
+  <si>
+    <t>1'Outubro'25</t>
+  </si>
+  <si>
+    <t>1'Janeiro'26</t>
+  </si>
+  <si>
+    <t>1'Abril'26</t>
+  </si>
+  <si>
+    <t>1'Julho'26</t>
+  </si>
+  <si>
+    <t>1'Outubro'26</t>
+  </si>
+  <si>
+    <t>1'Janeiro'27</t>
+  </si>
+  <si>
+    <t>(3,0,2)</t>
+  </si>
+  <si>
+    <t>(1,0,0)</t>
+  </si>
+  <si>
+    <t>Monthly Model</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.000%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -257,7 +358,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -342,8 +443,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFA7A9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="29">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -659,12 +790,155 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -934,6 +1208,93 @@
     <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -988,91 +1349,229 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="15" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="15" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="15" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="18" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="18" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="18" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="17" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="19" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="19" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="19" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1084,16 +1583,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFCCCC"/>
+      <color rgb="FFFFA7A9"/>
+      <color rgb="FFFF7C80"/>
+      <color rgb="FF4CAF50"/>
+      <color rgb="FFFFC107"/>
       <color rgb="FFF33621"/>
-      <color rgb="FFFFC107"/>
-      <color rgb="FF4CAF50"/>
       <color rgb="FF22BDFF"/>
       <color rgb="FFAADAAC"/>
       <color rgb="FFFFE089"/>
       <color rgb="FFFBB6AF"/>
-      <color rgb="FFA3E3FF"/>
-      <color rgb="FFEF9B9B"/>
-      <color rgb="FFBE71F3"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2909,192 +3408,192 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="95" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="98" t="s">
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="100"/>
-      <c r="AA1" s="109" t="s">
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
+      <c r="X1" s="128"/>
+      <c r="Y1" s="128"/>
+      <c r="Z1" s="129"/>
+      <c r="AA1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="AB1" s="110"/>
-      <c r="AC1" s="110"/>
-      <c r="AD1" s="110"/>
-      <c r="AE1" s="110"/>
-      <c r="AF1" s="110"/>
-      <c r="AG1" s="110"/>
-      <c r="AH1" s="110"/>
-      <c r="AI1" s="110"/>
-      <c r="AJ1" s="110"/>
-      <c r="AK1" s="110"/>
-      <c r="AL1" s="111"/>
-      <c r="AM1" s="122" t="s">
+      <c r="AB1" s="113"/>
+      <c r="AC1" s="113"/>
+      <c r="AD1" s="113"/>
+      <c r="AE1" s="113"/>
+      <c r="AF1" s="113"/>
+      <c r="AG1" s="113"/>
+      <c r="AH1" s="113"/>
+      <c r="AI1" s="113"/>
+      <c r="AJ1" s="113"/>
+      <c r="AK1" s="113"/>
+      <c r="AL1" s="114"/>
+      <c r="AM1" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="AN1" s="123"/>
-      <c r="AO1" s="123"/>
-      <c r="AP1" s="123"/>
-      <c r="AQ1" s="123"/>
-      <c r="AR1" s="123"/>
-      <c r="AS1" s="123"/>
-      <c r="AT1" s="123"/>
-      <c r="AU1" s="123"/>
-      <c r="AV1" s="123"/>
-      <c r="AW1" s="123"/>
-      <c r="AX1" s="124"/>
-      <c r="AY1" s="130" t="s">
+      <c r="AN1" s="100"/>
+      <c r="AO1" s="100"/>
+      <c r="AP1" s="100"/>
+      <c r="AQ1" s="100"/>
+      <c r="AR1" s="100"/>
+      <c r="AS1" s="100"/>
+      <c r="AT1" s="100"/>
+      <c r="AU1" s="100"/>
+      <c r="AV1" s="100"/>
+      <c r="AW1" s="100"/>
+      <c r="AX1" s="101"/>
+      <c r="AY1" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="AZ1" s="131"/>
-      <c r="BA1" s="131"/>
-      <c r="BB1" s="131"/>
-      <c r="BC1" s="131"/>
-      <c r="BD1" s="131"/>
-      <c r="BE1" s="131"/>
-      <c r="BF1" s="131"/>
-      <c r="BG1" s="131"/>
-      <c r="BH1" s="131"/>
-      <c r="BI1" s="131"/>
-      <c r="BJ1" s="132"/>
+      <c r="AZ1" s="92"/>
+      <c r="BA1" s="92"/>
+      <c r="BB1" s="92"/>
+      <c r="BC1" s="92"/>
+      <c r="BD1" s="92"/>
+      <c r="BE1" s="92"/>
+      <c r="BF1" s="92"/>
+      <c r="BG1" s="92"/>
+      <c r="BH1" s="92"/>
+      <c r="BI1" s="92"/>
+      <c r="BJ1" s="93"/>
     </row>
     <row r="2" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="130" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="108" t="s">
+      <c r="B2" s="131"/>
+      <c r="C2" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="103" t="s">
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="132" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="104"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="103" t="s">
+      <c r="G2" s="133"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="104"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="103" t="s">
+      <c r="J2" s="133"/>
+      <c r="K2" s="134"/>
+      <c r="L2" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="104"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="107" t="s">
+      <c r="M2" s="133"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="136" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="93"/>
-      <c r="R2" s="91" t="s">
+      <c r="P2" s="121"/>
+      <c r="Q2" s="122"/>
+      <c r="R2" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="92"/>
-      <c r="T2" s="93"/>
-      <c r="U2" s="91" t="s">
+      <c r="S2" s="121"/>
+      <c r="T2" s="122"/>
+      <c r="U2" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="V2" s="92"/>
-      <c r="W2" s="93"/>
-      <c r="X2" s="91" t="s">
+      <c r="V2" s="121"/>
+      <c r="W2" s="122"/>
+      <c r="X2" s="120" t="s">
         <v>39</v>
       </c>
-      <c r="Y2" s="92"/>
-      <c r="Z2" s="94"/>
-      <c r="AA2" s="112" t="s">
+      <c r="Y2" s="121"/>
+      <c r="Z2" s="123"/>
+      <c r="AA2" s="115" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="114"/>
-      <c r="AD2" s="115" t="s">
+      <c r="AB2" s="116"/>
+      <c r="AC2" s="117"/>
+      <c r="AD2" s="118" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="113"/>
-      <c r="AF2" s="114"/>
-      <c r="AG2" s="115" t="s">
+      <c r="AE2" s="116"/>
+      <c r="AF2" s="117"/>
+      <c r="AG2" s="118" t="s">
         <v>38</v>
       </c>
-      <c r="AH2" s="113"/>
-      <c r="AI2" s="114"/>
-      <c r="AJ2" s="115" t="s">
+      <c r="AH2" s="116"/>
+      <c r="AI2" s="117"/>
+      <c r="AJ2" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="AK2" s="113"/>
-      <c r="AL2" s="116"/>
-      <c r="AM2" s="125" t="s">
+      <c r="AK2" s="116"/>
+      <c r="AL2" s="119"/>
+      <c r="AM2" s="102" t="s">
         <v>35</v>
       </c>
-      <c r="AN2" s="126"/>
-      <c r="AO2" s="127"/>
-      <c r="AP2" s="128" t="s">
+      <c r="AN2" s="103"/>
+      <c r="AO2" s="104"/>
+      <c r="AP2" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="AQ2" s="126"/>
-      <c r="AR2" s="127"/>
-      <c r="AS2" s="128" t="s">
+      <c r="AQ2" s="103"/>
+      <c r="AR2" s="104"/>
+      <c r="AS2" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="AT2" s="126"/>
-      <c r="AU2" s="127"/>
-      <c r="AV2" s="128" t="s">
+      <c r="AT2" s="103"/>
+      <c r="AU2" s="104"/>
+      <c r="AV2" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="AW2" s="126"/>
-      <c r="AX2" s="129"/>
-      <c r="AY2" s="133" t="s">
+      <c r="AW2" s="103"/>
+      <c r="AX2" s="106"/>
+      <c r="AY2" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="AZ2" s="134"/>
-      <c r="BA2" s="135"/>
-      <c r="BB2" s="136" t="s">
+      <c r="AZ2" s="95"/>
+      <c r="BA2" s="96"/>
+      <c r="BB2" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="BC2" s="134"/>
-      <c r="BD2" s="135"/>
-      <c r="BE2" s="136" t="s">
+      <c r="BC2" s="95"/>
+      <c r="BD2" s="96"/>
+      <c r="BE2" s="97" t="s">
         <v>38</v>
       </c>
-      <c r="BF2" s="134"/>
-      <c r="BG2" s="135"/>
-      <c r="BH2" s="136" t="s">
+      <c r="BF2" s="95"/>
+      <c r="BG2" s="96"/>
+      <c r="BH2" s="97" t="s">
         <v>39</v>
       </c>
-      <c r="BI2" s="134"/>
-      <c r="BJ2" s="137"/>
+      <c r="BI2" s="95"/>
+      <c r="BJ2" s="98"/>
     </row>
     <row r="3" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="120" t="s">
+      <c r="A3" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="121"/>
+      <c r="B3" s="111"/>
       <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
@@ -3277,7 +3776,7 @@
       </c>
     </row>
     <row r="4" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A4" s="117" t="s">
+      <c r="A4" s="107" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -3485,7 +3984,7 @@
       </c>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A5" s="118"/>
+      <c r="A5" s="108"/>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
@@ -3691,7 +4190,7 @@
       </c>
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A6" s="118"/>
+      <c r="A6" s="108"/>
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
@@ -3897,7 +4396,7 @@
       </c>
     </row>
     <row r="7" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="119"/>
+      <c r="A7" s="109"/>
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -4103,7 +4602,7 @@
       </c>
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A8" s="117" t="s">
+      <c r="A8" s="107" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -4311,7 +4810,7 @@
       </c>
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A9" s="118"/>
+      <c r="A9" s="108"/>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
@@ -4517,7 +5016,7 @@
       </c>
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A10" s="118"/>
+      <c r="A10" s="108"/>
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
@@ -4723,7 +5222,7 @@
       </c>
     </row>
     <row r="11" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="119"/>
+      <c r="A11" s="109"/>
       <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
@@ -4929,7 +5428,7 @@
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A12" s="117" t="s">
+      <c r="A12" s="107" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -5137,7 +5636,7 @@
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A13" s="118"/>
+      <c r="A13" s="108"/>
       <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
@@ -5343,7 +5842,7 @@
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A14" s="118"/>
+      <c r="A14" s="108"/>
       <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
@@ -5549,7 +6048,7 @@
       </c>
     </row>
     <row r="15" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="119"/>
+      <c r="A15" s="109"/>
       <c r="B15" s="3" t="s">
         <v>22</v>
       </c>
@@ -5755,7 +6254,7 @@
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A16" s="117" t="s">
+      <c r="A16" s="107" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -5963,7 +6462,7 @@
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A17" s="118"/>
+      <c r="A17" s="108"/>
       <c r="B17" s="2" t="s">
         <v>24</v>
       </c>
@@ -6169,7 +6668,7 @@
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A18" s="118"/>
+      <c r="A18" s="108"/>
       <c r="B18" s="2" t="s">
         <v>25</v>
       </c>
@@ -6375,7 +6874,7 @@
       </c>
     </row>
     <row r="19" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="119"/>
+      <c r="A19" s="109"/>
       <c r="B19" s="3" t="s">
         <v>26</v>
       </c>
@@ -6581,7 +7080,7 @@
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A20" s="117" t="s">
+      <c r="A20" s="107" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -6789,7 +7288,7 @@
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A21" s="118"/>
+      <c r="A21" s="108"/>
       <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
@@ -6995,7 +7494,7 @@
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A22" s="118"/>
+      <c r="A22" s="108"/>
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
@@ -7201,7 +7700,7 @@
       </c>
     </row>
     <row r="23" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="119"/>
+      <c r="A23" s="109"/>
       <c r="B23" s="3" t="s">
         <v>30</v>
       </c>
@@ -7407,7 +7906,7 @@
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A24" s="117" t="s">
+      <c r="A24" s="107" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -7615,7 +8114,7 @@
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A25" s="118"/>
+      <c r="A25" s="108"/>
       <c r="B25" s="2" t="s">
         <v>32</v>
       </c>
@@ -7821,7 +8320,7 @@
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A26" s="118"/>
+      <c r="A26" s="108"/>
       <c r="B26" s="2" t="s">
         <v>33</v>
       </c>
@@ -8027,7 +8526,7 @@
       </c>
     </row>
     <row r="27" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="119"/>
+      <c r="A27" s="109"/>
       <c r="B27" s="3" t="s">
         <v>34</v>
       </c>
@@ -8663,28 +9162,6 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="AY1:BJ1"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AM1:AX1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="AA1:AL1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="AJ2:AL2"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="X2:Z2"/>
     <mergeCell ref="C1:N1"/>
@@ -8697,6 +9174,28 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AA1:AL1"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="AM1:AX1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="AY1:BJ1"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BH2:BJ2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8707,6 +9206,1187 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83B9917-06D9-4C7A-9E6D-A3082C65B7AC}">
+  <dimension ref="A1:R30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="162"/>
+    <col min="2" max="2" width="16.26953125" style="162" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="162"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="211" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="212"/>
+      <c r="C1" s="138" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="141" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="143"/>
+      <c r="K1" s="144" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="147" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" s="148"/>
+      <c r="Q1" s="148"/>
+      <c r="R1" s="149"/>
+    </row>
+    <row r="2" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="209" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="210"/>
+      <c r="C2" s="163" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="165" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="166" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="167" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="168" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="167" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="168" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="169" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="170" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="169" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="170" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="171" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="172" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="171" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="172" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A3" s="108">
+        <v>2020</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="150" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="173">
+        <v>6526.17</v>
+      </c>
+      <c r="E3" s="174">
+        <v>6638.5</v>
+      </c>
+      <c r="F3" s="191">
+        <f>(D3-E3)/E3</f>
+        <v>-1.6920991187768311E-2</v>
+      </c>
+      <c r="G3" s="151" t="s">
+        <v>84</v>
+      </c>
+      <c r="H3" s="179">
+        <v>2474.9</v>
+      </c>
+      <c r="I3" s="180">
+        <v>2470.5</v>
+      </c>
+      <c r="J3" s="194">
+        <f>(H3-I3)/I3</f>
+        <v>1.7810159886662987E-3</v>
+      </c>
+      <c r="K3" s="152" t="s">
+        <v>84</v>
+      </c>
+      <c r="L3" s="185">
+        <v>1584.95</v>
+      </c>
+      <c r="M3" s="186">
+        <v>1584.1</v>
+      </c>
+      <c r="N3" s="197">
+        <f>(L3-M3)/M3</f>
+        <v>5.3658228647189977E-4</v>
+      </c>
+      <c r="O3" s="153" t="s">
+        <v>84</v>
+      </c>
+      <c r="P3" s="203">
+        <v>1.0962000000000001</v>
+      </c>
+      <c r="Q3" s="204">
+        <v>1.0962000000000001</v>
+      </c>
+      <c r="R3" s="200">
+        <f>(P3-Q3)/Q3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A4" s="108"/>
+      <c r="B4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="154"/>
+      <c r="D4" s="175">
+        <v>9233.2800000000007</v>
+      </c>
+      <c r="E4" s="176">
+        <v>9229.9</v>
+      </c>
+      <c r="F4" s="192">
+        <f>(D4-E4)/E4</f>
+        <v>3.6620115060845932E-4</v>
+      </c>
+      <c r="G4" s="155"/>
+      <c r="H4" s="181">
+        <v>3111.25</v>
+      </c>
+      <c r="I4" s="182">
+        <v>3115.9</v>
+      </c>
+      <c r="J4" s="195">
+        <f>(H4-I4)/I4</f>
+        <v>-1.4923457107096155E-3</v>
+      </c>
+      <c r="K4" s="156"/>
+      <c r="L4" s="187">
+        <v>1780.12</v>
+      </c>
+      <c r="M4" s="188">
+        <v>1779.9</v>
+      </c>
+      <c r="N4" s="198">
+        <f>(L4-M4)/M4</f>
+        <v>1.2360244957570644E-4</v>
+      </c>
+      <c r="O4" s="157"/>
+      <c r="P4" s="205">
+        <v>1.125</v>
+      </c>
+      <c r="Q4" s="206">
+        <v>1.125</v>
+      </c>
+      <c r="R4" s="201">
+        <f>(P4-Q4)/Q4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A5" s="108"/>
+      <c r="B5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="154"/>
+      <c r="D5" s="175">
+        <v>10635.95</v>
+      </c>
+      <c r="E5" s="176">
+        <v>10620.5</v>
+      </c>
+      <c r="F5" s="192">
+        <f>(D5-E5)/E5</f>
+        <v>1.4547337695966036E-3</v>
+      </c>
+      <c r="G5" s="155"/>
+      <c r="H5" s="181">
+        <v>3378.26</v>
+      </c>
+      <c r="I5" s="182">
+        <v>3380.8</v>
+      </c>
+      <c r="J5" s="195">
+        <f>(H5-I5)/I5</f>
+        <v>-7.5130146710836588E-4</v>
+      </c>
+      <c r="K5" s="156"/>
+      <c r="L5" s="187">
+        <v>1912.87</v>
+      </c>
+      <c r="M5" s="188">
+        <v>1912.3</v>
+      </c>
+      <c r="N5" s="198">
+        <f>(L5-M5)/M5</f>
+        <v>2.980703864456081E-4</v>
+      </c>
+      <c r="O5" s="157"/>
+      <c r="P5" s="205">
+        <v>1.1748000000000001</v>
+      </c>
+      <c r="Q5" s="206">
+        <v>1.1747000000000001</v>
+      </c>
+      <c r="R5" s="201">
+        <f>(P5-Q5)/Q5</f>
+        <v>8.5128117817305678E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="109"/>
+      <c r="B6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="158"/>
+      <c r="D6" s="177">
+        <v>29271.37</v>
+      </c>
+      <c r="E6" s="178">
+        <v>29359.9</v>
+      </c>
+      <c r="F6" s="193">
+        <f>(D6-E6)/E6</f>
+        <v>-3.0153372456991497E-3</v>
+      </c>
+      <c r="G6" s="159"/>
+      <c r="H6" s="183">
+        <v>3754.06</v>
+      </c>
+      <c r="I6" s="184">
+        <v>3756.1</v>
+      </c>
+      <c r="J6" s="196">
+        <f>(H6-I6)/I6</f>
+        <v>-5.4311653044380168E-4</v>
+      </c>
+      <c r="K6" s="160"/>
+      <c r="L6" s="189">
+        <v>1895.55</v>
+      </c>
+      <c r="M6" s="190">
+        <v>1895.1</v>
+      </c>
+      <c r="N6" s="199">
+        <f>(L6-M6)/M6</f>
+        <v>2.3745448788984512E-4</v>
+      </c>
+      <c r="O6" s="161"/>
+      <c r="P6" s="207">
+        <v>1.2213000000000001</v>
+      </c>
+      <c r="Q6" s="208">
+        <v>1.2213000000000001</v>
+      </c>
+      <c r="R6" s="202">
+        <f>(P6-Q6)/Q6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A7" s="107">
+        <v>2021</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="150"/>
+      <c r="D7" s="173"/>
+      <c r="E7" s="174"/>
+      <c r="F7" s="191" t="e">
+        <f t="shared" ref="F7:F30" si="0">(D7-E7)/E7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G7" s="151"/>
+      <c r="H7" s="179"/>
+      <c r="I7" s="180"/>
+      <c r="J7" s="194" t="e">
+        <f t="shared" ref="J7:J30" si="1">(H7-I7)/I7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K7" s="152"/>
+      <c r="L7" s="185"/>
+      <c r="M7" s="186"/>
+      <c r="N7" s="197" t="e">
+        <f t="shared" ref="N7:N30" si="2">(L7-M7)/M7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O7" s="153"/>
+      <c r="P7" s="203"/>
+      <c r="Q7" s="204"/>
+      <c r="R7" s="200" t="e">
+        <f t="shared" ref="R7:R30" si="3">(P7-Q7)/Q7</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A8" s="108"/>
+      <c r="B8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="154"/>
+      <c r="D8" s="175"/>
+      <c r="E8" s="176"/>
+      <c r="F8" s="192" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G8" s="155"/>
+      <c r="H8" s="181"/>
+      <c r="I8" s="182"/>
+      <c r="J8" s="195" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K8" s="156"/>
+      <c r="L8" s="187"/>
+      <c r="M8" s="188"/>
+      <c r="N8" s="198" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O8" s="157"/>
+      <c r="P8" s="205"/>
+      <c r="Q8" s="206"/>
+      <c r="R8" s="201" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A9" s="108"/>
+      <c r="B9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="154"/>
+      <c r="D9" s="175"/>
+      <c r="E9" s="176"/>
+      <c r="F9" s="192" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G9" s="155"/>
+      <c r="H9" s="181"/>
+      <c r="I9" s="182"/>
+      <c r="J9" s="195" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K9" s="156"/>
+      <c r="L9" s="187"/>
+      <c r="M9" s="188"/>
+      <c r="N9" s="198" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O9" s="157"/>
+      <c r="P9" s="205"/>
+      <c r="Q9" s="206"/>
+      <c r="R9" s="201" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="109"/>
+      <c r="B10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="158"/>
+      <c r="D10" s="177"/>
+      <c r="E10" s="178"/>
+      <c r="F10" s="193" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G10" s="159"/>
+      <c r="H10" s="183"/>
+      <c r="I10" s="184"/>
+      <c r="J10" s="196" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K10" s="160"/>
+      <c r="L10" s="189"/>
+      <c r="M10" s="190"/>
+      <c r="N10" s="199" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O10" s="161"/>
+      <c r="P10" s="207"/>
+      <c r="Q10" s="208"/>
+      <c r="R10" s="202" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A11" s="107">
+        <v>2022</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="150"/>
+      <c r="D11" s="173"/>
+      <c r="E11" s="174"/>
+      <c r="F11" s="191" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G11" s="151"/>
+      <c r="H11" s="179"/>
+      <c r="I11" s="180"/>
+      <c r="J11" s="194" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K11" s="152"/>
+      <c r="L11" s="185"/>
+      <c r="M11" s="186"/>
+      <c r="N11" s="197" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O11" s="153"/>
+      <c r="P11" s="203"/>
+      <c r="Q11" s="204"/>
+      <c r="R11" s="200" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A12" s="108"/>
+      <c r="B12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="154"/>
+      <c r="D12" s="175"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="192" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G12" s="155"/>
+      <c r="H12" s="181"/>
+      <c r="I12" s="182"/>
+      <c r="J12" s="195" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K12" s="156"/>
+      <c r="L12" s="187"/>
+      <c r="M12" s="188"/>
+      <c r="N12" s="198" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O12" s="157"/>
+      <c r="P12" s="205"/>
+      <c r="Q12" s="206"/>
+      <c r="R12" s="201" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A13" s="108"/>
+      <c r="B13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="154"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="192" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G13" s="155"/>
+      <c r="H13" s="181"/>
+      <c r="I13" s="182"/>
+      <c r="J13" s="195" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K13" s="156"/>
+      <c r="L13" s="187"/>
+      <c r="M13" s="188"/>
+      <c r="N13" s="198" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O13" s="157"/>
+      <c r="P13" s="205"/>
+      <c r="Q13" s="206"/>
+      <c r="R13" s="201" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="109"/>
+      <c r="B14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="158"/>
+      <c r="D14" s="177"/>
+      <c r="E14" s="178"/>
+      <c r="F14" s="193" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G14" s="159"/>
+      <c r="H14" s="183"/>
+      <c r="I14" s="184"/>
+      <c r="J14" s="196" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K14" s="160"/>
+      <c r="L14" s="189"/>
+      <c r="M14" s="190"/>
+      <c r="N14" s="199" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O14" s="161"/>
+      <c r="P14" s="207"/>
+      <c r="Q14" s="208"/>
+      <c r="R14" s="202" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A15" s="107">
+        <v>2023</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="150"/>
+      <c r="D15" s="173"/>
+      <c r="E15" s="174"/>
+      <c r="F15" s="191" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G15" s="151"/>
+      <c r="H15" s="179"/>
+      <c r="I15" s="180"/>
+      <c r="J15" s="194" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K15" s="152"/>
+      <c r="L15" s="185"/>
+      <c r="M15" s="186"/>
+      <c r="N15" s="197" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O15" s="153"/>
+      <c r="P15" s="203"/>
+      <c r="Q15" s="204"/>
+      <c r="R15" s="200" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A16" s="108"/>
+      <c r="B16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="154"/>
+      <c r="D16" s="175"/>
+      <c r="E16" s="176"/>
+      <c r="F16" s="192" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G16" s="155"/>
+      <c r="H16" s="181"/>
+      <c r="I16" s="182"/>
+      <c r="J16" s="195" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K16" s="156"/>
+      <c r="L16" s="187"/>
+      <c r="M16" s="188"/>
+      <c r="N16" s="198" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O16" s="157"/>
+      <c r="P16" s="205"/>
+      <c r="Q16" s="206"/>
+      <c r="R16" s="201" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A17" s="108"/>
+      <c r="B17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="154"/>
+      <c r="D17" s="175"/>
+      <c r="E17" s="176"/>
+      <c r="F17" s="192" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G17" s="155"/>
+      <c r="H17" s="181"/>
+      <c r="I17" s="182"/>
+      <c r="J17" s="195" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K17" s="156"/>
+      <c r="L17" s="187"/>
+      <c r="M17" s="188"/>
+      <c r="N17" s="198" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O17" s="157"/>
+      <c r="P17" s="205"/>
+      <c r="Q17" s="206"/>
+      <c r="R17" s="201" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="109"/>
+      <c r="B18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="158"/>
+      <c r="D18" s="177"/>
+      <c r="E18" s="178"/>
+      <c r="F18" s="193" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G18" s="159"/>
+      <c r="H18" s="183"/>
+      <c r="I18" s="184"/>
+      <c r="J18" s="196" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K18" s="160"/>
+      <c r="L18" s="189"/>
+      <c r="M18" s="190"/>
+      <c r="N18" s="199" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O18" s="161"/>
+      <c r="P18" s="207"/>
+      <c r="Q18" s="208"/>
+      <c r="R18" s="202" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A19" s="107">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="150"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="174"/>
+      <c r="F19" s="191" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G19" s="151"/>
+      <c r="H19" s="179"/>
+      <c r="I19" s="180"/>
+      <c r="J19" s="194" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K19" s="152"/>
+      <c r="L19" s="185"/>
+      <c r="M19" s="186"/>
+      <c r="N19" s="197" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O19" s="153"/>
+      <c r="P19" s="203"/>
+      <c r="Q19" s="204"/>
+      <c r="R19" s="200" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A20" s="108"/>
+      <c r="B20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="154"/>
+      <c r="D20" s="175"/>
+      <c r="E20" s="176"/>
+      <c r="F20" s="192" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G20" s="155"/>
+      <c r="H20" s="181"/>
+      <c r="I20" s="182"/>
+      <c r="J20" s="195" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K20" s="156"/>
+      <c r="L20" s="187"/>
+      <c r="M20" s="188"/>
+      <c r="N20" s="198" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O20" s="157"/>
+      <c r="P20" s="205"/>
+      <c r="Q20" s="206"/>
+      <c r="R20" s="201" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A21" s="108"/>
+      <c r="B21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="154"/>
+      <c r="D21" s="175"/>
+      <c r="E21" s="176"/>
+      <c r="F21" s="192" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G21" s="155"/>
+      <c r="H21" s="181"/>
+      <c r="I21" s="182"/>
+      <c r="J21" s="195" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K21" s="156"/>
+      <c r="L21" s="187"/>
+      <c r="M21" s="188"/>
+      <c r="N21" s="198" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O21" s="157"/>
+      <c r="P21" s="205"/>
+      <c r="Q21" s="206"/>
+      <c r="R21" s="201" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="109"/>
+      <c r="B22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="158"/>
+      <c r="D22" s="177"/>
+      <c r="E22" s="178"/>
+      <c r="F22" s="193" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G22" s="159"/>
+      <c r="H22" s="183"/>
+      <c r="I22" s="184"/>
+      <c r="J22" s="196" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K22" s="160"/>
+      <c r="L22" s="189"/>
+      <c r="M22" s="190"/>
+      <c r="N22" s="199" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O22" s="161"/>
+      <c r="P22" s="207"/>
+      <c r="Q22" s="208"/>
+      <c r="R22" s="202" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A23" s="107">
+        <v>2025</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="150"/>
+      <c r="D23" s="173"/>
+      <c r="E23" s="174"/>
+      <c r="F23" s="191" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G23" s="151"/>
+      <c r="H23" s="179"/>
+      <c r="I23" s="180"/>
+      <c r="J23" s="194" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K23" s="152"/>
+      <c r="L23" s="185"/>
+      <c r="M23" s="186"/>
+      <c r="N23" s="197" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O23" s="153"/>
+      <c r="P23" s="203"/>
+      <c r="Q23" s="204"/>
+      <c r="R23" s="200" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A24" s="108"/>
+      <c r="B24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="154"/>
+      <c r="D24" s="175"/>
+      <c r="E24" s="176"/>
+      <c r="F24" s="192" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G24" s="155"/>
+      <c r="H24" s="181"/>
+      <c r="I24" s="182"/>
+      <c r="J24" s="195" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K24" s="156"/>
+      <c r="L24" s="187"/>
+      <c r="M24" s="188"/>
+      <c r="N24" s="198" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O24" s="157"/>
+      <c r="P24" s="205"/>
+      <c r="Q24" s="206"/>
+      <c r="R24" s="201" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A25" s="108"/>
+      <c r="B25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="154"/>
+      <c r="D25" s="175"/>
+      <c r="E25" s="176"/>
+      <c r="F25" s="192" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G25" s="155"/>
+      <c r="H25" s="181"/>
+      <c r="I25" s="182"/>
+      <c r="J25" s="195" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K25" s="156"/>
+      <c r="L25" s="187"/>
+      <c r="M25" s="188"/>
+      <c r="N25" s="198" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O25" s="157"/>
+      <c r="P25" s="205"/>
+      <c r="Q25" s="206"/>
+      <c r="R25" s="201" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="109"/>
+      <c r="B26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="158"/>
+      <c r="D26" s="177"/>
+      <c r="E26" s="178"/>
+      <c r="F26" s="193" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G26" s="159"/>
+      <c r="H26" s="183"/>
+      <c r="I26" s="184"/>
+      <c r="J26" s="196" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K26" s="160"/>
+      <c r="L26" s="189"/>
+      <c r="M26" s="190"/>
+      <c r="N26" s="199" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O26" s="161"/>
+      <c r="P26" s="207"/>
+      <c r="Q26" s="208"/>
+      <c r="R26" s="202" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A27" s="107">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="150"/>
+      <c r="D27" s="173"/>
+      <c r="E27" s="174"/>
+      <c r="F27" s="191" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G27" s="151"/>
+      <c r="H27" s="179"/>
+      <c r="I27" s="180"/>
+      <c r="J27" s="194" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K27" s="152"/>
+      <c r="L27" s="185"/>
+      <c r="M27" s="186"/>
+      <c r="N27" s="197" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O27" s="153"/>
+      <c r="P27" s="203"/>
+      <c r="Q27" s="204"/>
+      <c r="R27" s="200" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A28" s="108"/>
+      <c r="B28" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" s="154"/>
+      <c r="D28" s="175"/>
+      <c r="E28" s="176"/>
+      <c r="F28" s="192" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G28" s="155"/>
+      <c r="H28" s="181"/>
+      <c r="I28" s="182"/>
+      <c r="J28" s="195" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K28" s="156"/>
+      <c r="L28" s="187"/>
+      <c r="M28" s="188"/>
+      <c r="N28" s="198" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O28" s="157"/>
+      <c r="P28" s="205"/>
+      <c r="Q28" s="206"/>
+      <c r="R28" s="201" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A29" s="108"/>
+      <c r="B29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="154"/>
+      <c r="D29" s="175"/>
+      <c r="E29" s="176"/>
+      <c r="F29" s="192" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G29" s="155"/>
+      <c r="H29" s="181"/>
+      <c r="I29" s="182"/>
+      <c r="J29" s="195" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K29" s="156"/>
+      <c r="L29" s="187"/>
+      <c r="M29" s="188"/>
+      <c r="N29" s="198" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O29" s="157"/>
+      <c r="P29" s="205"/>
+      <c r="Q29" s="206"/>
+      <c r="R29" s="201" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="109"/>
+      <c r="B30" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="158"/>
+      <c r="D30" s="177"/>
+      <c r="E30" s="178"/>
+      <c r="F30" s="193" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G30" s="159"/>
+      <c r="H30" s="183"/>
+      <c r="I30" s="184"/>
+      <c r="J30" s="196" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K30" s="160"/>
+      <c r="L30" s="189"/>
+      <c r="M30" s="190"/>
+      <c r="N30" s="199" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O30" s="161"/>
+      <c r="P30" s="207"/>
+      <c r="Q30" s="208"/>
+      <c r="R30" s="202" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="41">
+    <mergeCell ref="K27:K30"/>
+    <mergeCell ref="O27:O30"/>
+    <mergeCell ref="O3:O6"/>
+    <mergeCell ref="O7:O10"/>
+    <mergeCell ref="O11:O14"/>
+    <mergeCell ref="O15:O18"/>
+    <mergeCell ref="O19:O22"/>
+    <mergeCell ref="O23:O26"/>
+    <mergeCell ref="G15:G18"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="G23:G26"/>
+    <mergeCell ref="K3:K6"/>
+    <mergeCell ref="K7:K10"/>
+    <mergeCell ref="K11:K14"/>
+    <mergeCell ref="K15:K18"/>
+    <mergeCell ref="K19:K22"/>
+    <mergeCell ref="K23:K26"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="G27:G30"/>
+    <mergeCell ref="G3:G6"/>
+    <mergeCell ref="G7:G10"/>
+    <mergeCell ref="G11:G14"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF28AA62-1405-4D5D-A97C-46B53B01AB28}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
